--- a/data/nzd0264/nzd0264.xlsx
+++ b/data/nzd0264/nzd0264.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y324"/>
+  <dimension ref="A1:Y325"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26305,7 +26305,7 @@
         <v>305.95</v>
       </c>
       <c r="M323" t="n">
-        <v>272.71</v>
+        <v>266.98</v>
       </c>
       <c r="N323" t="n">
         <v>284.09</v>
@@ -26353,7 +26353,7 @@
         </is>
       </c>
       <c r="B324" t="n">
-        <v>358.6</v>
+        <v>350.11</v>
       </c>
       <c r="C324" t="n">
         <v>349.94</v>
@@ -26365,16 +26365,16 @@
         <v>394.06</v>
       </c>
       <c r="F324" t="n">
-        <v>320.23</v>
+        <v>307.01</v>
       </c>
       <c r="G324" t="n">
-        <v>336.23</v>
+        <v>327.92</v>
       </c>
       <c r="H324" t="n">
         <v>344.97</v>
       </c>
       <c r="I324" t="n">
-        <v>320.93</v>
+        <v>308.38</v>
       </c>
       <c r="J324" t="n">
         <v>314.91</v>
@@ -26386,7 +26386,7 @@
         <v>309.94</v>
       </c>
       <c r="M324" t="n">
-        <v>293.08</v>
+        <v>254.78</v>
       </c>
       <c r="N324" t="n">
         <v>299.81</v>
@@ -26395,10 +26395,10 @@
         <v>293.29</v>
       </c>
       <c r="P324" t="n">
-        <v>287.3</v>
+        <v>270.04</v>
       </c>
       <c r="Q324" t="n">
-        <v>316.29</v>
+        <v>300.82</v>
       </c>
       <c r="R324" t="n">
         <v>333.23</v>
@@ -26424,6 +26424,87 @@
       <c r="Y324" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:06:48+00:00</t>
+        </is>
+      </c>
+      <c r="B325" t="n">
+        <v>347.75</v>
+      </c>
+      <c r="C325" t="n">
+        <v>345.38</v>
+      </c>
+      <c r="D325" t="n">
+        <v>346.96</v>
+      </c>
+      <c r="E325" t="n">
+        <v>339.27</v>
+      </c>
+      <c r="F325" t="n">
+        <v>299.27</v>
+      </c>
+      <c r="G325" t="n">
+        <v>320.45</v>
+      </c>
+      <c r="H325" t="n">
+        <v>337.89</v>
+      </c>
+      <c r="I325" t="n">
+        <v>309.08</v>
+      </c>
+      <c r="J325" t="n">
+        <v>316.35</v>
+      </c>
+      <c r="K325" t="n">
+        <v>305.78</v>
+      </c>
+      <c r="L325" t="n">
+        <v>312.56</v>
+      </c>
+      <c r="M325" t="n">
+        <v>275.31</v>
+      </c>
+      <c r="N325" t="n">
+        <v>303.58</v>
+      </c>
+      <c r="O325" t="n">
+        <v>297.98</v>
+      </c>
+      <c r="P325" t="n">
+        <v>281.8</v>
+      </c>
+      <c r="Q325" t="n">
+        <v>308.44</v>
+      </c>
+      <c r="R325" t="n">
+        <v>336.74</v>
+      </c>
+      <c r="S325" t="n">
+        <v>362.59</v>
+      </c>
+      <c r="T325" t="n">
+        <v>369.75</v>
+      </c>
+      <c r="U325" t="n">
+        <v>343.43</v>
+      </c>
+      <c r="V325" t="n">
+        <v>310.12</v>
+      </c>
+      <c r="W325" t="n">
+        <v>343.4</v>
+      </c>
+      <c r="X325" t="n">
+        <v>344.91</v>
+      </c>
+      <c r="Y325" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -26438,7 +26519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B350"/>
+  <dimension ref="A1:B351"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29941,6 +30022,16 @@
       </c>
       <c r="B350" t="n">
         <v>-0.57</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B351" t="n">
+        <v>-0.71</v>
       </c>
     </row>
   </sheetData>
@@ -30109,28 +30200,28 @@
         <v>0.0285</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8091343200381673</v>
+        <v>0.7991799696545669</v>
       </c>
       <c r="J2" t="n">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K2" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1302096836656242</v>
+        <v>0.1278952284562126</v>
       </c>
       <c r="M2" t="n">
-        <v>12.17382164992908</v>
+        <v>12.17214735232015</v>
       </c>
       <c r="N2" t="n">
-        <v>233.6653885716886</v>
+        <v>233.2782140595929</v>
       </c>
       <c r="O2" t="n">
-        <v>15.28611751137903</v>
+        <v>15.27344800821324</v>
       </c>
       <c r="P2" t="n">
-        <v>335.5695975836539</v>
+        <v>335.6757213176773</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -30187,28 +30278,28 @@
         <v>0.0381</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2742784033061537</v>
+        <v>-0.266808259779433</v>
       </c>
       <c r="J3" t="n">
+        <v>324</v>
+      </c>
+      <c r="K3" t="n">
         <v>323</v>
       </c>
-      <c r="K3" t="n">
-        <v>322</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.01397494988951153</v>
+        <v>0.01328453802828944</v>
       </c>
       <c r="M3" t="n">
-        <v>11.97455855350323</v>
+        <v>11.96508894547524</v>
       </c>
       <c r="N3" t="n">
-        <v>286.0370419768666</v>
+        <v>285.6782809794555</v>
       </c>
       <c r="O3" t="n">
-        <v>16.91262965883386</v>
+        <v>16.9020200265961</v>
       </c>
       <c r="P3" t="n">
-        <v>339.3858348063628</v>
+        <v>339.3070042170338</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30265,28 +30356,28 @@
         <v>0.0304</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2184514415683733</v>
+        <v>-0.2092571972119531</v>
       </c>
       <c r="J4" t="n">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K4" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00771670214650233</v>
+        <v>0.007108458652190897</v>
       </c>
       <c r="M4" t="n">
-        <v>13.28963065659625</v>
+        <v>13.28547165604878</v>
       </c>
       <c r="N4" t="n">
-        <v>328.7650281450422</v>
+        <v>328.5314281202902</v>
       </c>
       <c r="O4" t="n">
-        <v>18.13187878144574</v>
+        <v>18.12543594290328</v>
       </c>
       <c r="P4" t="n">
-        <v>336.6200800025633</v>
+        <v>336.5224389259412</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30343,28 +30434,28 @@
         <v>0.0232</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6875825520417805</v>
+        <v>0.6850157233191434</v>
       </c>
       <c r="J5" t="n">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K5" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04886683320887253</v>
+        <v>0.04879114740179002</v>
       </c>
       <c r="M5" t="n">
-        <v>17.98012829130387</v>
+        <v>17.93631870761978</v>
       </c>
       <c r="N5" t="n">
-        <v>494.6124782050823</v>
+        <v>493.0339808541352</v>
       </c>
       <c r="O5" t="n">
-        <v>22.23988485143487</v>
+        <v>22.20436850833942</v>
       </c>
       <c r="P5" t="n">
-        <v>325.6952523180755</v>
+        <v>325.7225161327557</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30421,28 +30512,28 @@
         <v>0.0304</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3232176740761765</v>
+        <v>0.3054265166236513</v>
       </c>
       <c r="J6" t="n">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K6" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L6" t="n">
-        <v>0.007584559991494211</v>
+        <v>0.006804798924530786</v>
       </c>
       <c r="M6" t="n">
-        <v>19.6350600438862</v>
+        <v>19.6865043338184</v>
       </c>
       <c r="N6" t="n">
-        <v>734.1781008139146</v>
+        <v>733.1530323039716</v>
       </c>
       <c r="O6" t="n">
-        <v>27.09572107942349</v>
+        <v>27.07679878242573</v>
       </c>
       <c r="P6" t="n">
-        <v>308.8018606565178</v>
+        <v>308.9902542536747</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30499,28 +30590,28 @@
         <v>0.0311</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01056020381745238</v>
+        <v>0.0037376407000842</v>
       </c>
       <c r="J7" t="n">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K7" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L7" t="n">
-        <v>1.296650981996716e-05</v>
+        <v>1.635151921308697e-06</v>
       </c>
       <c r="M7" t="n">
-        <v>15.8664217133191</v>
+        <v>15.81763454050509</v>
       </c>
       <c r="N7" t="n">
-        <v>461.5820464000582</v>
+        <v>459.741913025713</v>
       </c>
       <c r="O7" t="n">
-        <v>21.48446057968545</v>
+        <v>21.44159306175063</v>
       </c>
       <c r="P7" t="n">
-        <v>323.6961015429316</v>
+        <v>323.7681679592029</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30577,28 +30668,28 @@
         <v>0.0451</v>
       </c>
       <c r="I8" t="n">
-        <v>0.07989824789374171</v>
+        <v>0.08307821826514562</v>
       </c>
       <c r="J8" t="n">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K8" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002871435711332637</v>
+        <v>0.003119012015061928</v>
       </c>
       <c r="M8" t="n">
-        <v>8.853858332027738</v>
+        <v>8.841261736674452</v>
       </c>
       <c r="N8" t="n">
-        <v>119.7107454515682</v>
+        <v>119.4347881449378</v>
       </c>
       <c r="O8" t="n">
-        <v>10.94124058101129</v>
+        <v>10.92862242668022</v>
       </c>
       <c r="P8" t="n">
-        <v>330.2389864144362</v>
+        <v>330.2054457138042</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -30655,28 +30746,28 @@
         <v>0.0388</v>
       </c>
       <c r="I9" t="n">
-        <v>0.126854664998007</v>
+        <v>0.1047615069577791</v>
       </c>
       <c r="J9" t="n">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K9" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002938143512946412</v>
+        <v>0.001991894471791933</v>
       </c>
       <c r="M9" t="n">
-        <v>12.31948190510754</v>
+        <v>12.43672919072174</v>
       </c>
       <c r="N9" t="n">
-        <v>295.8739891541948</v>
+        <v>298.692546807407</v>
       </c>
       <c r="O9" t="n">
-        <v>17.20098802843007</v>
+        <v>17.28272394061211</v>
       </c>
       <c r="P9" t="n">
-        <v>332.0834376450499</v>
+        <v>332.3160917523236</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -30733,28 +30824,28 @@
         <v>0.079</v>
       </c>
       <c r="I10" t="n">
-        <v>0.01969030827351667</v>
+        <v>0.01703541723656416</v>
       </c>
       <c r="J10" t="n">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K10" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L10" t="n">
-        <v>9.140693462139637e-05</v>
+        <v>6.879141016513657e-05</v>
       </c>
       <c r="M10" t="n">
-        <v>12.81735259949725</v>
+        <v>12.79406914748053</v>
       </c>
       <c r="N10" t="n">
-        <v>227.3627084403117</v>
+        <v>226.7185681570158</v>
       </c>
       <c r="O10" t="n">
-        <v>15.07855127126979</v>
+        <v>15.05717663298853</v>
       </c>
       <c r="P10" t="n">
-        <v>320.4715286355535</v>
+        <v>320.4997236753714</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -30811,28 +30902,28 @@
         <v>0.0864</v>
       </c>
       <c r="I11" t="n">
-        <v>0.02234137759930005</v>
+        <v>0.01672758844322109</v>
       </c>
       <c r="J11" t="n">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K11" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L11" t="n">
-        <v>9.684757561800872e-05</v>
+        <v>5.454520201997326e-05</v>
       </c>
       <c r="M11" t="n">
-        <v>13.76669021925298</v>
+        <v>13.75582578470833</v>
       </c>
       <c r="N11" t="n">
-        <v>277.5509774815264</v>
+        <v>276.981910434112</v>
       </c>
       <c r="O11" t="n">
-        <v>16.65986126837575</v>
+        <v>16.64277351988279</v>
       </c>
       <c r="P11" t="n">
-        <v>315.0136233850661</v>
+        <v>315.0730483633671</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -30889,28 +30980,28 @@
         <v>0.06569999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3476281244602721</v>
+        <v>0.3386691941881099</v>
       </c>
       <c r="J12" t="n">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K12" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="L12" t="n">
-        <v>0.02895555045275156</v>
+        <v>0.02759035254025954</v>
       </c>
       <c r="M12" t="n">
-        <v>12.18720883422543</v>
+        <v>12.21107983715318</v>
       </c>
       <c r="N12" t="n">
-        <v>219.4613377022372</v>
+        <v>219.4983227963959</v>
       </c>
       <c r="O12" t="n">
-        <v>14.81422754321795</v>
+        <v>14.81547578704092</v>
       </c>
       <c r="P12" t="n">
-        <v>318.8124603239726</v>
+        <v>318.9066716806345</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -30967,28 +31058,28 @@
         <v>0.0371</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.4968287987482495</v>
+        <v>-0.5410333533959212</v>
       </c>
       <c r="J13" t="n">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K13" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L13" t="n">
-        <v>0.01266768272934105</v>
+        <v>0.01490411812411008</v>
       </c>
       <c r="M13" t="n">
-        <v>27.37845363493133</v>
+        <v>27.58093433095527</v>
       </c>
       <c r="N13" t="n">
-        <v>1068.456691794195</v>
+        <v>1077.269191268018</v>
       </c>
       <c r="O13" t="n">
-        <v>32.68725580091107</v>
+        <v>32.82177922154766</v>
       </c>
       <c r="P13" t="n">
-        <v>318.3392956279311</v>
+        <v>318.7981222257248</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -31045,28 +31136,28 @@
         <v>0.07920000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3944117524488648</v>
+        <v>-0.3902358878466707</v>
       </c>
       <c r="J14" t="n">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K14" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L14" t="n">
-        <v>0.01823468614463131</v>
+        <v>0.01795118446518662</v>
       </c>
       <c r="M14" t="n">
-        <v>18.25059310177644</v>
+        <v>18.2170651232895</v>
       </c>
       <c r="N14" t="n">
-        <v>454.0028002604271</v>
+        <v>452.7543556883634</v>
       </c>
       <c r="O14" t="n">
-        <v>21.30734146392804</v>
+        <v>21.27802518299956</v>
       </c>
       <c r="P14" t="n">
-        <v>306.4786068540295</v>
+        <v>306.4346516227121</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -31123,28 +31214,28 @@
         <v>0.1073</v>
       </c>
       <c r="I15" t="n">
-        <v>0.05816728615403016</v>
+        <v>0.05340633417120386</v>
       </c>
       <c r="J15" t="n">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K15" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L15" t="n">
-        <v>0.000512414866916111</v>
+        <v>0.0004341998364341126</v>
       </c>
       <c r="M15" t="n">
-        <v>16.21433961801563</v>
+        <v>16.19091457717578</v>
       </c>
       <c r="N15" t="n">
-        <v>358.3542941168412</v>
+        <v>357.4508660922752</v>
       </c>
       <c r="O15" t="n">
-        <v>18.93024812612981</v>
+        <v>18.90637104502806</v>
       </c>
       <c r="P15" t="n">
-        <v>304.8304119309432</v>
+        <v>304.8805170099162</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -31201,28 +31292,28 @@
         <v>0.0534</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2576242284028517</v>
+        <v>0.2249873859383136</v>
       </c>
       <c r="J16" t="n">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K16" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L16" t="n">
-        <v>0.005958378491754512</v>
+        <v>0.004504916269361336</v>
       </c>
       <c r="M16" t="n">
-        <v>19.97341731504306</v>
+        <v>20.10969957615787</v>
       </c>
       <c r="N16" t="n">
-        <v>592.6566870037785</v>
+        <v>600.243483970499</v>
       </c>
       <c r="O16" t="n">
-        <v>24.34454121571772</v>
+        <v>24.49986701944521</v>
       </c>
       <c r="P16" t="n">
-        <v>314.6399909697831</v>
+        <v>314.987037758574</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -31279,28 +31370,28 @@
         <v>0.0428</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.7845898539307387</v>
+        <v>-0.7953408788824397</v>
       </c>
       <c r="J17" t="n">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K17" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L17" t="n">
-        <v>0.04691362291532419</v>
+        <v>0.04840834113770243</v>
       </c>
       <c r="M17" t="n">
-        <v>21.46028932793979</v>
+        <v>21.39962409449731</v>
       </c>
       <c r="N17" t="n">
-        <v>668.1391585109909</v>
+        <v>666.138897916864</v>
       </c>
       <c r="O17" t="n">
-        <v>25.84838792866957</v>
+        <v>25.809666753309</v>
       </c>
       <c r="P17" t="n">
-        <v>330.9875143309371</v>
+        <v>331.1016875058328</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -31357,28 +31448,28 @@
         <v>0.0478</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1560879177818042</v>
+        <v>-0.1482629501286956</v>
       </c>
       <c r="J18" t="n">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K18" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L18" t="n">
-        <v>0.01110108877753491</v>
+        <v>0.01003469389693079</v>
       </c>
       <c r="M18" t="n">
-        <v>8.540034317199238</v>
+        <v>8.542508530111348</v>
       </c>
       <c r="N18" t="n">
-        <v>115.9533284616572</v>
+        <v>116.1646826836454</v>
       </c>
       <c r="O18" t="n">
-        <v>10.76816272451606</v>
+        <v>10.77797210441952</v>
       </c>
       <c r="P18" t="n">
-        <v>327.1602640571208</v>
+        <v>327.0771668256455</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -31435,28 +31526,28 @@
         <v>0.0415</v>
       </c>
       <c r="I19" t="n">
-        <v>0.176765063311632</v>
+        <v>0.1834563145677875</v>
       </c>
       <c r="J19" t="n">
+        <v>324</v>
+      </c>
+      <c r="K19" t="n">
         <v>323</v>
       </c>
-      <c r="K19" t="n">
-        <v>322</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.02319952547955362</v>
+        <v>0.02493829602526543</v>
       </c>
       <c r="M19" t="n">
-        <v>6.355556598499671</v>
+        <v>6.364928669360019</v>
       </c>
       <c r="N19" t="n">
-        <v>70.89587877923852</v>
+        <v>71.09906007640842</v>
       </c>
       <c r="O19" t="n">
-        <v>8.419969048591479</v>
+        <v>8.432025858381152</v>
       </c>
       <c r="P19" t="n">
-        <v>346.2663212503609</v>
+        <v>346.1957101198004</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -31513,28 +31604,28 @@
         <v>0.0344</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.004469398363644899</v>
+        <v>0.009503700722427148</v>
       </c>
       <c r="J20" t="n">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K20" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L20" t="n">
-        <v>1.406345259236108e-05</v>
+        <v>6.243819679285778e-05</v>
       </c>
       <c r="M20" t="n">
-        <v>6.813738702154061</v>
+        <v>6.8766968020851</v>
       </c>
       <c r="N20" t="n">
-        <v>76.70199036105086</v>
+        <v>78.31379389345193</v>
       </c>
       <c r="O20" t="n">
-        <v>8.757967250512579</v>
+        <v>8.849508115904065</v>
       </c>
       <c r="P20" t="n">
-        <v>345.3499046634669</v>
+        <v>345.2025235628249</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -31591,28 +31682,28 @@
         <v>0.0304</v>
       </c>
       <c r="I21" t="n">
-        <v>0.193193165398529</v>
+        <v>0.2023317083492932</v>
       </c>
       <c r="J21" t="n">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K21" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L21" t="n">
-        <v>0.009254803103594722</v>
+        <v>0.0101624420373071</v>
       </c>
       <c r="M21" t="n">
-        <v>11.75225627076143</v>
+        <v>11.7672402788225</v>
       </c>
       <c r="N21" t="n">
-        <v>214.0343270468198</v>
+        <v>214.1494745867227</v>
       </c>
       <c r="O21" t="n">
-        <v>14.6299120655874</v>
+        <v>14.63384688271415</v>
       </c>
       <c r="P21" t="n">
-        <v>322.5148618387101</v>
+        <v>322.4178035667331</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -31669,28 +31760,28 @@
         <v>0.0447</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2389191223748176</v>
+        <v>0.2390761940379033</v>
       </c>
       <c r="J22" t="n">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K22" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L22" t="n">
-        <v>0.00901237045039549</v>
+        <v>0.009075229730465706</v>
       </c>
       <c r="M22" t="n">
-        <v>14.72889938862899</v>
+        <v>14.68402236350905</v>
       </c>
       <c r="N22" t="n">
-        <v>339.5727889334133</v>
+        <v>338.5184491477413</v>
       </c>
       <c r="O22" t="n">
-        <v>18.42750088681081</v>
+        <v>18.39887086610864</v>
       </c>
       <c r="P22" t="n">
-        <v>303.6455091323838</v>
+        <v>303.6438547926471</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -31747,28 +31838,28 @@
         <v>0.0592</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4688234721118304</v>
+        <v>0.4733342547757536</v>
       </c>
       <c r="J23" t="n">
+        <v>324</v>
+      </c>
+      <c r="K23" t="n">
         <v>323</v>
       </c>
-      <c r="K23" t="n">
-        <v>322</v>
-      </c>
       <c r="L23" t="n">
-        <v>0.1039894907226258</v>
+        <v>0.1061494533438253</v>
       </c>
       <c r="M23" t="n">
-        <v>7.924651421644002</v>
+        <v>7.918206137617352</v>
       </c>
       <c r="N23" t="n">
-        <v>102.0572143282415</v>
+        <v>101.9333328844236</v>
       </c>
       <c r="O23" t="n">
-        <v>10.10233707259075</v>
+        <v>10.09620388484819</v>
       </c>
       <c r="P23" t="n">
-        <v>323.3347880447216</v>
+        <v>323.2871868635048</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -31825,28 +31916,28 @@
         <v>0.07870000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1613272199622136</v>
+        <v>0.1617122412954854</v>
       </c>
       <c r="J24" t="n">
+        <v>324</v>
+      </c>
+      <c r="K24" t="n">
         <v>323</v>
       </c>
-      <c r="K24" t="n">
-        <v>322</v>
-      </c>
       <c r="L24" t="n">
-        <v>0.04259853625273891</v>
+        <v>0.04302610317568167</v>
       </c>
       <c r="M24" t="n">
-        <v>3.996661433153757</v>
+        <v>3.986102761988098</v>
       </c>
       <c r="N24" t="n">
-        <v>31.44330975547297</v>
+        <v>31.34735706333036</v>
       </c>
       <c r="O24" t="n">
-        <v>5.607433437453625</v>
+        <v>5.598871052572149</v>
       </c>
       <c r="P24" t="n">
-        <v>340.0554229083606</v>
+        <v>340.0513530583418</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -31888,7 +31979,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y324"/>
+  <dimension ref="A1:Y325"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72260,7 +72351,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>-38.577078271123455,174.63069040208637</t>
+          <t>-38.577079530242756,174.63075614895038</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
@@ -72332,7 +72423,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>-38.58477620485014,174.62942245788128</t>
+          <t>-38.58478093489683,174.6295197263247</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -72352,12 +72443,12 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>-38.58197775481238,174.63009307627615</t>
+          <t>-38.5819787015408,174.63024481518352</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>-38.58127158288484,174.62991331279713</t>
+          <t>-38.58127102261874,174.6300086942314</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -72367,7 +72458,7 @@
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t>-38.57986607973237,174.63009646909188</t>
+          <t>-38.57986523339935,174.63024051404562</t>
         </is>
       </c>
       <c r="J324" t="inlineStr">
@@ -72387,7 +72478,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>-38.5770737946877,174.63045667371384</t>
+          <t>-38.577082210966914,174.6308961335507</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -72402,12 +72493,12 @@
       </c>
       <c r="P324" t="inlineStr">
         <is>
-          <t>-38.574971741239374,174.63062854030636</t>
+          <t>-38.574976013047944,174.63082656247676</t>
         </is>
       </c>
       <c r="Q324" t="inlineStr">
         <is>
-          <t>-38.574269080818695,174.63033073404006</t>
+          <t>-38.57427533296099,174.6305081063048</t>
         </is>
       </c>
       <c r="R324" t="inlineStr">
@@ -72448,6 +72539,133 @@
       <c r="Y324" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:06:48+00:00</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>-38.58478224971283,174.62954676443323</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>-38.58408326991464,174.62964002288618</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>-38.583382082660286,174.629688027228</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>-38.58268310081056,174.6298425801515</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>-38.581979255736705,174.6303336547542</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>-38.581270518919695,174.63009443421743</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>-38.58056946242013,174.62989803349768</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>-38.57986528060986,174.630232479666</t>
+        </is>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>-38.57916352482317,174.63015280851573</t>
+        </is>
+      </c>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>-38.57846055907406,174.63027789690875</t>
+        </is>
+      </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>-38.577764441279605,174.6302037508922</t>
+        </is>
+      </c>
+      <c r="M325" t="inlineStr">
+        <is>
+          <t>-38.57707769978312,174.6306605693037</t>
+        </is>
+      </c>
+      <c r="N325" t="inlineStr">
+        <is>
+          <t>-38.57637121180955,174.6303713364393</t>
+        </is>
+      </c>
+      <c r="O325" t="inlineStr">
+        <is>
+          <t>-38.575670851295534,174.63047079784576</t>
+        </is>
+      </c>
+      <c r="P325" t="inlineStr">
+        <is>
+          <t>-38.574973102512615,174.63069164122845</t>
+        </is>
+      </c>
+      <c r="Q325" t="inlineStr">
+        <is>
+          <t>-38.57427225340035,174.63042073870955</t>
+        </is>
+      </c>
+      <c r="R325" t="inlineStr">
+        <is>
+          <t>-38.573564414664894,174.63016226733592</t>
+        </is>
+      </c>
+      <c r="S325" t="inlineStr">
+        <is>
+          <t>-38.572848721366896,174.62994085407814</t>
+        </is>
+      </c>
+      <c r="T325" t="inlineStr">
+        <is>
+          <t>-38.57214541585647,174.62993348660535</t>
+        </is>
+      </c>
+      <c r="U325" t="inlineStr">
+        <is>
+          <t>-38.5714564247236,174.63029226743046</t>
+        </is>
+      </c>
+      <c r="V325" t="inlineStr">
+        <is>
+          <t>-38.57075946265785,174.63070515511052</t>
+        </is>
+      </c>
+      <c r="W325" t="inlineStr">
+        <is>
+          <t>-38.57005127249985,174.6303537942414</t>
+        </is>
+      </c>
+      <c r="X325" t="inlineStr">
+        <is>
+          <t>-38.56934955587479,174.63037339635218</t>
+        </is>
+      </c>
+      <c r="Y325" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>

--- a/data/nzd0264/nzd0264.xlsx
+++ b/data/nzd0264/nzd0264.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y325"/>
+  <dimension ref="A1:Y326"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26437,22 +26437,22 @@
         <v>347.75</v>
       </c>
       <c r="C325" t="n">
-        <v>345.38</v>
+        <v>349.94</v>
       </c>
       <c r="D325" t="n">
-        <v>346.96</v>
+        <v>357.2</v>
       </c>
       <c r="E325" t="n">
-        <v>339.27</v>
+        <v>394.06</v>
       </c>
       <c r="F325" t="n">
-        <v>299.27</v>
+        <v>307.01</v>
       </c>
       <c r="G325" t="n">
-        <v>320.45</v>
+        <v>327.92</v>
       </c>
       <c r="H325" t="n">
-        <v>337.89</v>
+        <v>344.97</v>
       </c>
       <c r="I325" t="n">
         <v>309.08</v>
@@ -26503,6 +26503,87 @@
         <v>344.91</v>
       </c>
       <c r="Y325" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-16 22:06:48+00:00</t>
+        </is>
+      </c>
+      <c r="B326" t="n">
+        <v>348.62</v>
+      </c>
+      <c r="C326" t="n">
+        <v>388.97</v>
+      </c>
+      <c r="D326" t="n">
+        <v>395.97</v>
+      </c>
+      <c r="E326" t="n">
+        <v>495.53</v>
+      </c>
+      <c r="F326" t="n">
+        <v>365.05</v>
+      </c>
+      <c r="G326" t="n">
+        <v>394.83</v>
+      </c>
+      <c r="H326" t="n">
+        <v>393.4</v>
+      </c>
+      <c r="I326" t="n">
+        <v>309.08</v>
+      </c>
+      <c r="J326" t="n">
+        <v>316.35</v>
+      </c>
+      <c r="K326" t="n">
+        <v>316.77</v>
+      </c>
+      <c r="L326" t="n">
+        <v>312.56</v>
+      </c>
+      <c r="M326" t="n">
+        <v>275.31</v>
+      </c>
+      <c r="N326" t="n">
+        <v>318.66</v>
+      </c>
+      <c r="O326" t="n">
+        <v>305.64</v>
+      </c>
+      <c r="P326" t="n">
+        <v>301.75</v>
+      </c>
+      <c r="Q326" t="n">
+        <v>308.44</v>
+      </c>
+      <c r="R326" t="n">
+        <v>345.47</v>
+      </c>
+      <c r="S326" t="n">
+        <v>364.09</v>
+      </c>
+      <c r="T326" t="n">
+        <v>369.39</v>
+      </c>
+      <c r="U326" t="n">
+        <v>343.51</v>
+      </c>
+      <c r="V326" t="n">
+        <v>318.79</v>
+      </c>
+      <c r="W326" t="n">
+        <v>346.28</v>
+      </c>
+      <c r="X326" t="n">
+        <v>342.59</v>
+      </c>
+      <c r="Y326" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -26519,7 +26600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B351"/>
+  <dimension ref="A1:B352"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30032,6 +30113,16 @@
       </c>
       <c r="B351" t="n">
         <v>-0.71</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>2025-12-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B352" t="n">
+        <v>0.33</v>
       </c>
     </row>
   </sheetData>
@@ -30200,28 +30291,28 @@
         <v>0.0285</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7991799696545669</v>
+        <v>0.794689129864991</v>
       </c>
       <c r="J2" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K2" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1278952284562126</v>
+        <v>0.1271796242942634</v>
       </c>
       <c r="M2" t="n">
-        <v>12.17214735232015</v>
+        <v>12.15649887731507</v>
       </c>
       <c r="N2" t="n">
-        <v>233.2782140595929</v>
+        <v>232.7331359424739</v>
       </c>
       <c r="O2" t="n">
-        <v>15.27344800821324</v>
+        <v>15.25559359521857</v>
       </c>
       <c r="P2" t="n">
-        <v>335.6757213176773</v>
+        <v>335.7237897199134</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -30278,28 +30369,28 @@
         <v>0.0381</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.266808259779433</v>
+        <v>-0.232099436175725</v>
       </c>
       <c r="J3" t="n">
+        <v>325</v>
+      </c>
+      <c r="K3" t="n">
         <v>324</v>
       </c>
-      <c r="K3" t="n">
-        <v>323</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.01328453802828944</v>
+        <v>0.009794769433637329</v>
       </c>
       <c r="M3" t="n">
-        <v>11.96508894547524</v>
+        <v>12.06152651598942</v>
       </c>
       <c r="N3" t="n">
-        <v>285.6782809794555</v>
+        <v>295.0126907186246</v>
       </c>
       <c r="O3" t="n">
-        <v>16.9020200265961</v>
+        <v>17.17593347444687</v>
       </c>
       <c r="P3" t="n">
-        <v>339.3070042170338</v>
+        <v>338.9399663885358</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30356,28 +30447,28 @@
         <v>0.0304</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2092571972119531</v>
+        <v>-0.1663313171166042</v>
       </c>
       <c r="J4" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K4" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L4" t="n">
-        <v>0.007108458652190897</v>
+        <v>0.004339949058789538</v>
       </c>
       <c r="M4" t="n">
-        <v>13.28547165604878</v>
+        <v>13.4186445002534</v>
       </c>
       <c r="N4" t="n">
-        <v>328.5314281202902</v>
+        <v>341.8052661608592</v>
       </c>
       <c r="O4" t="n">
-        <v>18.12543594290328</v>
+        <v>18.48797625920315</v>
       </c>
       <c r="P4" t="n">
-        <v>336.5224389259412</v>
+        <v>336.0656839383302</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30434,28 +30525,28 @@
         <v>0.0232</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6850157233191434</v>
+        <v>0.8091305264995595</v>
       </c>
       <c r="J5" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K5" t="n">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04879114740179002</v>
+        <v>0.05798316693131733</v>
       </c>
       <c r="M5" t="n">
-        <v>17.93631870761978</v>
+        <v>18.50296507194084</v>
       </c>
       <c r="N5" t="n">
-        <v>493.0339808541352</v>
+        <v>574.7549504214327</v>
       </c>
       <c r="O5" t="n">
-        <v>22.20436850833942</v>
+        <v>23.97404743512102</v>
       </c>
       <c r="P5" t="n">
-        <v>325.7225161327557</v>
+        <v>324.4020033093049</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30512,28 +30603,28 @@
         <v>0.0304</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3054265166236513</v>
+        <v>0.3372930839931238</v>
       </c>
       <c r="J6" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K6" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L6" t="n">
-        <v>0.006804798924530786</v>
+        <v>0.008260755417537347</v>
       </c>
       <c r="M6" t="n">
-        <v>19.6865043338184</v>
+        <v>19.68774043276363</v>
       </c>
       <c r="N6" t="n">
-        <v>733.1530323039716</v>
+        <v>737.3349381317096</v>
       </c>
       <c r="O6" t="n">
-        <v>27.07679878242573</v>
+        <v>27.15391202261121</v>
       </c>
       <c r="P6" t="n">
-        <v>308.9902542536747</v>
+        <v>308.6516614281564</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30590,28 +30681,28 @@
         <v>0.0311</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0037376407000842</v>
+        <v>0.04897986064961043</v>
       </c>
       <c r="J7" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K7" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L7" t="n">
-        <v>1.635151921308697e-06</v>
+        <v>0.0002730367098733311</v>
       </c>
       <c r="M7" t="n">
-        <v>15.81763454050509</v>
+        <v>15.88176278303897</v>
       </c>
       <c r="N7" t="n">
-        <v>459.741913025713</v>
+        <v>473.9299886116554</v>
       </c>
       <c r="O7" t="n">
-        <v>21.44159306175063</v>
+        <v>21.7699331329165</v>
       </c>
       <c r="P7" t="n">
-        <v>323.7681679592029</v>
+        <v>323.2881531661629</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30668,28 +30759,28 @@
         <v>0.0451</v>
       </c>
       <c r="I8" t="n">
-        <v>0.08307821826514562</v>
+        <v>0.1217125994966019</v>
       </c>
       <c r="J8" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K8" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003119012015061928</v>
+        <v>0.00610693382364158</v>
       </c>
       <c r="M8" t="n">
-        <v>8.841261736674452</v>
+        <v>8.998664566783404</v>
       </c>
       <c r="N8" t="n">
-        <v>119.4347881449378</v>
+        <v>130.8693490640774</v>
       </c>
       <c r="O8" t="n">
-        <v>10.92862242668022</v>
+        <v>11.43981420583732</v>
       </c>
       <c r="P8" t="n">
-        <v>330.2054457138042</v>
+        <v>329.797122604247</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -30746,28 +30837,28 @@
         <v>0.0388</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1047615069577791</v>
+        <v>0.09002937806010934</v>
       </c>
       <c r="J9" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K9" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001991894471791933</v>
+        <v>0.001469921990702727</v>
       </c>
       <c r="M9" t="n">
-        <v>12.43672919072174</v>
+        <v>12.50354548964098</v>
       </c>
       <c r="N9" t="n">
-        <v>298.692546807407</v>
+        <v>299.84271444618</v>
       </c>
       <c r="O9" t="n">
-        <v>17.28272394061211</v>
+        <v>17.31596703756911</v>
       </c>
       <c r="P9" t="n">
-        <v>332.3160917523236</v>
+        <v>332.471758717476</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -30824,28 +30915,28 @@
         <v>0.079</v>
       </c>
       <c r="I10" t="n">
-        <v>0.01703541723656416</v>
+        <v>0.01441487515200593</v>
       </c>
       <c r="J10" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K10" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L10" t="n">
-        <v>6.879141016513657e-05</v>
+        <v>4.95219986741402e-05</v>
       </c>
       <c r="M10" t="n">
-        <v>12.79406914748053</v>
+        <v>12.77064366559788</v>
       </c>
       <c r="N10" t="n">
-        <v>226.7185681570158</v>
+        <v>226.0773070636438</v>
       </c>
       <c r="O10" t="n">
-        <v>15.05717663298853</v>
+        <v>15.03586735322056</v>
       </c>
       <c r="P10" t="n">
-        <v>320.4997236753714</v>
+        <v>320.52761705266</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -30902,28 +30993,28 @@
         <v>0.0864</v>
       </c>
       <c r="I11" t="n">
-        <v>0.01672758844322109</v>
+        <v>0.01744854139246632</v>
       </c>
       <c r="J11" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K11" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L11" t="n">
-        <v>5.454520201997326e-05</v>
+        <v>5.968443824622138e-05</v>
       </c>
       <c r="M11" t="n">
-        <v>13.75582578470833</v>
+        <v>13.71669161576219</v>
       </c>
       <c r="N11" t="n">
-        <v>276.981910434112</v>
+        <v>276.1239858452257</v>
       </c>
       <c r="O11" t="n">
-        <v>16.64277351988279</v>
+        <v>16.61697884229337</v>
       </c>
       <c r="P11" t="n">
-        <v>315.0730483633671</v>
+        <v>315.0653993128232</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -30980,28 +31071,28 @@
         <v>0.06569999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3386691941881099</v>
+        <v>0.329824027006641</v>
       </c>
       <c r="J12" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K12" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L12" t="n">
-        <v>0.02759035254025954</v>
+        <v>0.02627074822186926</v>
       </c>
       <c r="M12" t="n">
-        <v>12.21107983715318</v>
+        <v>12.23386376007142</v>
       </c>
       <c r="N12" t="n">
-        <v>219.4983227963959</v>
+        <v>219.5232609259494</v>
       </c>
       <c r="O12" t="n">
-        <v>14.81547578704092</v>
+        <v>14.81631738746</v>
       </c>
       <c r="P12" t="n">
-        <v>318.9066716806345</v>
+        <v>318.9998973695742</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -31058,28 +31149,28 @@
         <v>0.0371</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.5410333533959212</v>
+        <v>-0.5585738350509193</v>
       </c>
       <c r="J13" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K13" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L13" t="n">
-        <v>0.01490411812411008</v>
+        <v>0.01592165601124718</v>
       </c>
       <c r="M13" t="n">
-        <v>27.58093433095527</v>
+        <v>27.60380495442919</v>
       </c>
       <c r="N13" t="n">
-        <v>1077.269191268018</v>
+        <v>1076.535138105939</v>
       </c>
       <c r="O13" t="n">
-        <v>32.82177922154766</v>
+        <v>32.81059490630943</v>
       </c>
       <c r="P13" t="n">
-        <v>318.7981222257248</v>
+        <v>318.9811124521898</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -31136,28 +31227,28 @@
         <v>0.07920000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3902358878466707</v>
+        <v>-0.3775536093297785</v>
       </c>
       <c r="J14" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K14" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L14" t="n">
-        <v>0.01795118446518662</v>
+        <v>0.01686032801183601</v>
       </c>
       <c r="M14" t="n">
-        <v>18.2170651232895</v>
+        <v>18.23091622849227</v>
       </c>
       <c r="N14" t="n">
-        <v>452.7543556883634</v>
+        <v>452.8871798054183</v>
       </c>
       <c r="O14" t="n">
-        <v>21.27802518299956</v>
+        <v>21.28114611118063</v>
       </c>
       <c r="P14" t="n">
-        <v>306.4346516227121</v>
+        <v>306.3008534077886</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -31214,28 +31305,28 @@
         <v>0.1073</v>
       </c>
       <c r="I15" t="n">
-        <v>0.05340633417120386</v>
+        <v>0.05305111011251693</v>
       </c>
       <c r="J15" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K15" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0004341998364341126</v>
+        <v>0.0004308780855412087</v>
       </c>
       <c r="M15" t="n">
-        <v>16.19091457717578</v>
+        <v>16.14250480245463</v>
       </c>
       <c r="N15" t="n">
-        <v>357.4508660922752</v>
+        <v>356.3385236955721</v>
       </c>
       <c r="O15" t="n">
-        <v>18.90637104502806</v>
+        <v>18.87693099249908</v>
       </c>
       <c r="P15" t="n">
-        <v>304.8805170099162</v>
+        <v>304.8842640158704</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -31292,28 +31383,28 @@
         <v>0.0534</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2249873859383136</v>
+        <v>0.2140435315431904</v>
       </c>
       <c r="J16" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K16" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L16" t="n">
-        <v>0.004504916269361336</v>
+        <v>0.004094479441468679</v>
       </c>
       <c r="M16" t="n">
-        <v>20.10969957615787</v>
+        <v>20.11429180302202</v>
       </c>
       <c r="N16" t="n">
-        <v>600.243483970499</v>
+        <v>599.4935075158164</v>
       </c>
       <c r="O16" t="n">
-        <v>24.49986701944521</v>
+        <v>24.48455651049895</v>
       </c>
       <c r="P16" t="n">
-        <v>314.987037758574</v>
+        <v>315.1037970357702</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -31370,28 +31461,28 @@
         <v>0.0428</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.7953408788824397</v>
+        <v>-0.796560604153891</v>
       </c>
       <c r="J17" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K17" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L17" t="n">
-        <v>0.04840834113770243</v>
+        <v>0.04882817432552844</v>
       </c>
       <c r="M17" t="n">
-        <v>21.39962409449731</v>
+        <v>21.33393495565755</v>
       </c>
       <c r="N17" t="n">
-        <v>666.138897916864</v>
+        <v>663.9390210397441</v>
       </c>
       <c r="O17" t="n">
-        <v>25.809666753309</v>
+        <v>25.767014204982</v>
       </c>
       <c r="P17" t="n">
-        <v>331.1016875058328</v>
+        <v>331.1147092514877</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -31448,28 +31539,28 @@
         <v>0.0478</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1482629501286956</v>
+        <v>-0.135541078737362</v>
       </c>
       <c r="J18" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K18" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L18" t="n">
-        <v>0.01003469389693079</v>
+        <v>0.008339527427673743</v>
       </c>
       <c r="M18" t="n">
-        <v>8.542508530111348</v>
+        <v>8.563534942546855</v>
       </c>
       <c r="N18" t="n">
-        <v>116.1646826836454</v>
+        <v>117.3241964181035</v>
       </c>
       <c r="O18" t="n">
-        <v>10.77797210441952</v>
+        <v>10.83162944427585</v>
       </c>
       <c r="P18" t="n">
-        <v>327.0771668256455</v>
+        <v>326.9417640525048</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -31526,28 +31617,28 @@
         <v>0.0415</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1834563145677875</v>
+        <v>0.1909067757087079</v>
       </c>
       <c r="J19" t="n">
+        <v>325</v>
+      </c>
+      <c r="K19" t="n">
         <v>324</v>
       </c>
-      <c r="K19" t="n">
-        <v>323</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.02493829602526543</v>
+        <v>0.02690426449633765</v>
       </c>
       <c r="M19" t="n">
-        <v>6.364928669360019</v>
+        <v>6.378217515259606</v>
       </c>
       <c r="N19" t="n">
-        <v>71.09906007640842</v>
+        <v>71.40665016095379</v>
       </c>
       <c r="O19" t="n">
-        <v>8.432025858381152</v>
+        <v>8.450245568085805</v>
       </c>
       <c r="P19" t="n">
-        <v>346.1957101198004</v>
+        <v>346.1169099029017</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -31604,28 +31695,28 @@
         <v>0.0344</v>
       </c>
       <c r="I20" t="n">
-        <v>0.009503700722427148</v>
+        <v>0.02309068509585662</v>
       </c>
       <c r="J20" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K20" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L20" t="n">
-        <v>6.243819679285778e-05</v>
+        <v>0.0003624080148172393</v>
       </c>
       <c r="M20" t="n">
-        <v>6.8766968020851</v>
+        <v>6.937931946767398</v>
       </c>
       <c r="N20" t="n">
-        <v>78.31379389345193</v>
+        <v>79.83049869899943</v>
       </c>
       <c r="O20" t="n">
-        <v>8.849508115904065</v>
+        <v>8.934791474847046</v>
       </c>
       <c r="P20" t="n">
-        <v>345.2025235628249</v>
+        <v>345.0588900874662</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -31682,28 +31773,28 @@
         <v>0.0304</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2023317083492932</v>
+        <v>0.2113885226871713</v>
       </c>
       <c r="J21" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K21" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0101624420373071</v>
+        <v>0.01110494690746677</v>
       </c>
       <c r="M21" t="n">
-        <v>11.7672402788225</v>
+        <v>11.78160848720977</v>
       </c>
       <c r="N21" t="n">
-        <v>214.1494745867227</v>
+        <v>214.2567621494989</v>
       </c>
       <c r="O21" t="n">
-        <v>14.63384688271415</v>
+        <v>14.63751215710849</v>
       </c>
       <c r="P21" t="n">
-        <v>322.4178035667331</v>
+        <v>322.3213956387004</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -31760,28 +31851,28 @@
         <v>0.0447</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2390761940379033</v>
+        <v>0.2441427936120655</v>
       </c>
       <c r="J22" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K22" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L22" t="n">
-        <v>0.009075229730465706</v>
+        <v>0.009506843332645953</v>
       </c>
       <c r="M22" t="n">
-        <v>14.68402236350905</v>
+        <v>14.66625932874508</v>
       </c>
       <c r="N22" t="n">
-        <v>338.5184491477413</v>
+        <v>337.7153693505754</v>
       </c>
       <c r="O22" t="n">
-        <v>18.39887086610864</v>
+        <v>18.3770337473319</v>
       </c>
       <c r="P22" t="n">
-        <v>303.6438547926471</v>
+        <v>303.5903702903154</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -31838,28 +31929,28 @@
         <v>0.0592</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4733342547757536</v>
+        <v>0.4794075013146226</v>
       </c>
       <c r="J23" t="n">
+        <v>325</v>
+      </c>
+      <c r="K23" t="n">
         <v>324</v>
       </c>
-      <c r="K23" t="n">
-        <v>323</v>
-      </c>
       <c r="L23" t="n">
-        <v>0.1061494533438253</v>
+        <v>0.1088110832347408</v>
       </c>
       <c r="M23" t="n">
-        <v>7.918206137617352</v>
+        <v>7.917925775750429</v>
       </c>
       <c r="N23" t="n">
-        <v>101.9333328844236</v>
+        <v>101.9689206486059</v>
       </c>
       <c r="O23" t="n">
-        <v>10.09620388484819</v>
+        <v>10.09796616396618</v>
       </c>
       <c r="P23" t="n">
-        <v>323.2871868635048</v>
+        <v>323.222952833491</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -31916,28 +32007,28 @@
         <v>0.07870000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1617122412954854</v>
+        <v>0.1607665251321449</v>
       </c>
       <c r="J24" t="n">
+        <v>325</v>
+      </c>
+      <c r="K24" t="n">
         <v>324</v>
       </c>
-      <c r="K24" t="n">
-        <v>323</v>
-      </c>
       <c r="L24" t="n">
-        <v>0.04302610317568167</v>
+        <v>0.0427671061996292</v>
       </c>
       <c r="M24" t="n">
-        <v>3.986102761988098</v>
+        <v>3.979556203505374</v>
       </c>
       <c r="N24" t="n">
-        <v>31.34735706333036</v>
+        <v>31.25907065947388</v>
       </c>
       <c r="O24" t="n">
-        <v>5.598871052572149</v>
+        <v>5.59098118933286</v>
       </c>
       <c r="P24" t="n">
-        <v>340.0513530583418</v>
+        <v>340.0613722009339</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -31979,7 +32070,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y325"/>
+  <dimension ref="A1:Y326"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72555,32 +72646,32 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>-38.58408326991464,174.62964002288618</t>
+          <t>-38.5840807294396,174.62958778026828</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>-38.583382082660286,174.629688027228</t>
+          <t>-38.58337637770613,174.6295707116186</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>-38.58268310081056,174.6298425801515</t>
+          <t>-38.58266205655402,174.62921424725945</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>-38.581979255736705,174.6303336547542</t>
+          <t>-38.5819787015408,174.63024481518352</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>-38.581270518919695,174.63009443421743</t>
+          <t>-38.58127102261874,174.6300086942314</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>-38.58056946242013,174.62989803349768</t>
+          <t>-38.580569939672074,174.6298167706806</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
@@ -72664,6 +72755,133 @@
         </is>
       </c>
       <c r="Y325" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-16 22:06:48+00:00</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>-38.58478176501444,174.6295367969948</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>-38.584058984020984,174.62914062481994</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>-38.583354776922356,174.6291265392708</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>-38.58262307407193,174.62805058778108</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>-38.58197454363686,174.62957863315015</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>-38.581275531531574,174.62924070713512</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>-38.5805732027511,174.62926090079122</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>-38.57986528060986,174.630232479666</t>
+        </is>
+      </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>-38.57916352482317,174.63015280851573</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>-38.57846130020968,174.6301517596043</t>
+        </is>
+      </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>-38.577764441279605,174.6302037508922</t>
+        </is>
+      </c>
+      <c r="M326" t="inlineStr">
+        <is>
+          <t>-38.57707769978312,174.6306605693037</t>
+        </is>
+      </c>
+      <c r="N326" t="inlineStr">
+        <is>
+          <t>-38.57636747898552,174.63019832182783</t>
+        </is>
+      </c>
+      <c r="O326" t="inlineStr">
+        <is>
+          <t>-38.57566895526195,174.63038291461945</t>
+        </is>
+      </c>
+      <c r="P326" t="inlineStr">
+        <is>
+          <t>-38.574968164640914,174.6304627569802</t>
+        </is>
+      </c>
+      <c r="Q326" t="inlineStr">
+        <is>
+          <t>-38.57427225340035,174.63042073870955</t>
+        </is>
+      </c>
+      <c r="R326" t="inlineStr">
+        <is>
+          <t>-38.57355916288932,174.63006229668432</t>
+        </is>
+      </c>
+      <c r="S326" t="inlineStr">
+        <is>
+          <t>-38.57284775767673,174.6299236825651</t>
+        </is>
+      </c>
+      <c r="T326" t="inlineStr">
+        <is>
+          <t>-38.57214561524649,174.62993761043168</t>
+        </is>
+      </c>
+      <c r="U326" t="inlineStr">
+        <is>
+          <t>-38.57145639809487,174.6302913499238</t>
+        </is>
+      </c>
+      <c r="V326" t="inlineStr">
+        <is>
+          <t>-38.57075772428166,174.6306056780155</t>
+        </is>
+      </c>
+      <c r="W326" t="inlineStr">
+        <is>
+          <t>-38.570050601991994,174.63032075311907</t>
+        </is>
+      </c>
+      <c r="X326" t="inlineStr">
+        <is>
+          <t>-38.56935017087825,174.63040000991646</t>
+        </is>
+      </c>
+      <c r="Y326" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0264/nzd0264.xlsx
+++ b/data/nzd0264/nzd0264.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y326"/>
+  <dimension ref="A1:Y327"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26467,7 +26467,7 @@
         <v>312.56</v>
       </c>
       <c r="M325" t="n">
-        <v>275.31</v>
+        <v>254.78</v>
       </c>
       <c r="N325" t="n">
         <v>303.58</v>
@@ -26518,22 +26518,22 @@
         <v>348.62</v>
       </c>
       <c r="C326" t="n">
-        <v>388.97</v>
+        <v>349.94</v>
       </c>
       <c r="D326" t="n">
-        <v>395.97</v>
+        <v>357.2</v>
       </c>
       <c r="E326" t="n">
-        <v>495.53</v>
+        <v>394.06</v>
       </c>
       <c r="F326" t="n">
-        <v>365.05</v>
+        <v>307.01</v>
       </c>
       <c r="G326" t="n">
-        <v>394.83</v>
+        <v>344.52</v>
       </c>
       <c r="H326" t="n">
-        <v>393.4</v>
+        <v>344.97</v>
       </c>
       <c r="I326" t="n">
         <v>309.08</v>
@@ -26548,7 +26548,7 @@
         <v>312.56</v>
       </c>
       <c r="M326" t="n">
-        <v>275.31</v>
+        <v>254.78</v>
       </c>
       <c r="N326" t="n">
         <v>318.66</v>
@@ -26584,6 +26584,87 @@
         <v>342.59</v>
       </c>
       <c r="Y326" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:06:49+00:00</t>
+        </is>
+      </c>
+      <c r="B327" t="n">
+        <v>353.04</v>
+      </c>
+      <c r="C327" t="n">
+        <v>351.68</v>
+      </c>
+      <c r="D327" t="n">
+        <v>357.66</v>
+      </c>
+      <c r="E327" t="n">
+        <v>381.44</v>
+      </c>
+      <c r="F327" t="n">
+        <v>310.09</v>
+      </c>
+      <c r="G327" t="n">
+        <v>344.07</v>
+      </c>
+      <c r="H327" t="n">
+        <v>343.15</v>
+      </c>
+      <c r="I327" t="n">
+        <v>315.19</v>
+      </c>
+      <c r="J327" t="n">
+        <v>318.74</v>
+      </c>
+      <c r="K327" t="n">
+        <v>320.49</v>
+      </c>
+      <c r="L327" t="n">
+        <v>317.08</v>
+      </c>
+      <c r="M327" t="n">
+        <v>288.46</v>
+      </c>
+      <c r="N327" t="n">
+        <v>322.34</v>
+      </c>
+      <c r="O327" t="n">
+        <v>310.17</v>
+      </c>
+      <c r="P327" t="n">
+        <v>311.4</v>
+      </c>
+      <c r="Q327" t="n">
+        <v>314.88</v>
+      </c>
+      <c r="R327" t="n">
+        <v>344</v>
+      </c>
+      <c r="S327" t="n">
+        <v>363.62</v>
+      </c>
+      <c r="T327" t="n">
+        <v>369.67</v>
+      </c>
+      <c r="U327" t="n">
+        <v>346.45</v>
+      </c>
+      <c r="V327" t="n">
+        <v>321.87</v>
+      </c>
+      <c r="W327" t="n">
+        <v>344.74</v>
+      </c>
+      <c r="X327" t="n">
+        <v>343.18</v>
+      </c>
+      <c r="Y327" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -26600,7 +26681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B352"/>
+  <dimension ref="A1:B353"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30123,6 +30204,16 @@
       </c>
       <c r="B352" t="n">
         <v>0.33</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B353" t="n">
+        <v>0.93</v>
       </c>
     </row>
   </sheetData>
@@ -30291,28 +30382,28 @@
         <v>0.0285</v>
       </c>
       <c r="I2" t="n">
-        <v>0.794689129864991</v>
+        <v>0.7927666226008517</v>
       </c>
       <c r="J2" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K2" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1271796242942634</v>
+        <v>0.1272514027721039</v>
       </c>
       <c r="M2" t="n">
-        <v>12.15649887731507</v>
+        <v>12.12793455780054</v>
       </c>
       <c r="N2" t="n">
-        <v>232.7331359424739</v>
+        <v>232.0364344642136</v>
       </c>
       <c r="O2" t="n">
-        <v>15.25559359521857</v>
+        <v>15.2327421846565</v>
       </c>
       <c r="P2" t="n">
-        <v>335.7237897199134</v>
+        <v>335.7444145898132</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -30369,28 +30460,28 @@
         <v>0.0381</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.232099436175725</v>
+        <v>-0.2434505193212328</v>
       </c>
       <c r="J3" t="n">
+        <v>326</v>
+      </c>
+      <c r="K3" t="n">
         <v>325</v>
       </c>
-      <c r="K3" t="n">
-        <v>324</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.009794769433637329</v>
+        <v>0.01111424907295189</v>
       </c>
       <c r="M3" t="n">
-        <v>12.06152651598942</v>
+        <v>11.98012206419253</v>
       </c>
       <c r="N3" t="n">
-        <v>295.0126907186246</v>
+        <v>286.4005168871387</v>
       </c>
       <c r="O3" t="n">
-        <v>17.17593347444687</v>
+        <v>16.9233719124511</v>
       </c>
       <c r="P3" t="n">
-        <v>338.9399663885358</v>
+        <v>339.0597645702169</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30447,28 +30538,28 @@
         <v>0.0304</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1663313171166042</v>
+        <v>-0.173546854227121</v>
       </c>
       <c r="J4" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K4" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004339949058789538</v>
+        <v>0.004873604755958327</v>
       </c>
       <c r="M4" t="n">
-        <v>13.4186445002534</v>
+        <v>13.34721596078592</v>
       </c>
       <c r="N4" t="n">
-        <v>341.8052661608592</v>
+        <v>332.0296275265214</v>
       </c>
       <c r="O4" t="n">
-        <v>18.48797625920315</v>
+        <v>18.22168015103221</v>
       </c>
       <c r="P4" t="n">
-        <v>336.0656839383302</v>
+        <v>336.1421255201036</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30525,28 +30616,28 @@
         <v>0.0232</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8091305264995595</v>
+        <v>0.7702356107167757</v>
       </c>
       <c r="J5" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K5" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05798316693131733</v>
+        <v>0.05921630148904067</v>
       </c>
       <c r="M5" t="n">
-        <v>18.50296507194084</v>
+        <v>18.22118543756431</v>
       </c>
       <c r="N5" t="n">
-        <v>574.7549504214327</v>
+        <v>510.6551468536968</v>
       </c>
       <c r="O5" t="n">
-        <v>23.97404743512102</v>
+        <v>22.59768012105881</v>
       </c>
       <c r="P5" t="n">
-        <v>324.4020033093049</v>
+        <v>324.8155384757009</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30603,28 +30694,28 @@
         <v>0.0304</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3372930839931238</v>
+        <v>0.3002921644106585</v>
       </c>
       <c r="J6" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K6" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L6" t="n">
-        <v>0.008260755417537347</v>
+        <v>0.006655887284505613</v>
       </c>
       <c r="M6" t="n">
-        <v>19.68774043276363</v>
+        <v>19.60159745584375</v>
       </c>
       <c r="N6" t="n">
-        <v>737.3349381317096</v>
+        <v>728.3850413293807</v>
       </c>
       <c r="O6" t="n">
-        <v>27.15391202261121</v>
+        <v>26.98860947380173</v>
       </c>
       <c r="P6" t="n">
-        <v>308.6516614281564</v>
+        <v>309.0450260743281</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30681,28 +30772,28 @@
         <v>0.0311</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04897986064961043</v>
+        <v>0.0314088101391589</v>
       </c>
       <c r="J7" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K7" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0002730367098733311</v>
+        <v>0.0001161425775834113</v>
       </c>
       <c r="M7" t="n">
-        <v>15.88176278303897</v>
+        <v>15.7786609146967</v>
       </c>
       <c r="N7" t="n">
-        <v>473.9299886116554</v>
+        <v>459.4274312714744</v>
       </c>
       <c r="O7" t="n">
-        <v>21.7699331329165</v>
+        <v>21.43425835599344</v>
       </c>
       <c r="P7" t="n">
-        <v>323.2881531661629</v>
+        <v>323.4743467163638</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30759,28 +30850,28 @@
         <v>0.0451</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1217125994966019</v>
+        <v>0.1002259640420497</v>
       </c>
       <c r="J8" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K8" t="n">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="L8" t="n">
-        <v>0.00610693382364158</v>
+        <v>0.004538029180940262</v>
       </c>
       <c r="M8" t="n">
-        <v>8.998664566783404</v>
+        <v>8.867199497936074</v>
       </c>
       <c r="N8" t="n">
-        <v>130.8693490640774</v>
+        <v>119.9181901756491</v>
       </c>
       <c r="O8" t="n">
-        <v>11.43981420583732</v>
+        <v>10.95071642294006</v>
       </c>
       <c r="P8" t="n">
-        <v>329.797122604247</v>
+        <v>330.0241230755354</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -30837,28 +30928,28 @@
         <v>0.0388</v>
       </c>
       <c r="I9" t="n">
-        <v>0.09002937806010934</v>
+        <v>0.07893712299892343</v>
       </c>
       <c r="J9" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K9" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001469921990702727</v>
+        <v>0.001132315959378793</v>
       </c>
       <c r="M9" t="n">
-        <v>12.50354548964098</v>
+        <v>12.54448063981563</v>
       </c>
       <c r="N9" t="n">
-        <v>299.84271444618</v>
+        <v>300.097714083994</v>
       </c>
       <c r="O9" t="n">
-        <v>17.31596703756911</v>
+        <v>17.32332860867085</v>
       </c>
       <c r="P9" t="n">
-        <v>332.471758717476</v>
+        <v>332.5892326205015</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -30915,28 +31006,28 @@
         <v>0.079</v>
       </c>
       <c r="I10" t="n">
-        <v>0.01441487515200593</v>
+        <v>0.01318275990756703</v>
       </c>
       <c r="J10" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K10" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L10" t="n">
-        <v>4.95219986741402e-05</v>
+        <v>4.165061751171262e-05</v>
       </c>
       <c r="M10" t="n">
-        <v>12.77064366559788</v>
+        <v>12.73865176859488</v>
       </c>
       <c r="N10" t="n">
-        <v>226.0773070636438</v>
+        <v>225.389659637636</v>
       </c>
       <c r="O10" t="n">
-        <v>15.03586735322056</v>
+        <v>15.01298303594712</v>
       </c>
       <c r="P10" t="n">
-        <v>320.52761705266</v>
+        <v>320.5407615190522</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -30993,28 +31084,28 @@
         <v>0.0864</v>
       </c>
       <c r="I11" t="n">
-        <v>0.01744854139246632</v>
+        <v>0.02026579257214188</v>
       </c>
       <c r="J11" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K11" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L11" t="n">
-        <v>5.968443824622138e-05</v>
+        <v>8.094619069132225e-05</v>
       </c>
       <c r="M11" t="n">
-        <v>13.71669161576219</v>
+        <v>13.68851695279617</v>
       </c>
       <c r="N11" t="n">
-        <v>276.1239858452257</v>
+        <v>275.3424297725112</v>
       </c>
       <c r="O11" t="n">
-        <v>16.61697884229337</v>
+        <v>16.59344538582965</v>
       </c>
       <c r="P11" t="n">
-        <v>315.0653993128232</v>
+        <v>315.0354413992252</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -31071,28 +31162,28 @@
         <v>0.06569999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.329824027006641</v>
+        <v>0.3237209114031382</v>
       </c>
       <c r="J12" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K12" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L12" t="n">
-        <v>0.02627074822186926</v>
+        <v>0.02543736021280663</v>
       </c>
       <c r="M12" t="n">
-        <v>12.23386376007142</v>
+        <v>12.23733916782892</v>
       </c>
       <c r="N12" t="n">
-        <v>219.5232609259494</v>
+        <v>219.1731665571428</v>
       </c>
       <c r="O12" t="n">
-        <v>14.81631738746</v>
+        <v>14.80449818660338</v>
       </c>
       <c r="P12" t="n">
-        <v>318.9998973695742</v>
+        <v>319.0643679644213</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -31149,28 +31240,28 @@
         <v>0.0371</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.5585738350509193</v>
+        <v>-0.5922396776149372</v>
       </c>
       <c r="J13" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K13" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L13" t="n">
-        <v>0.01592165601124718</v>
+        <v>0.0177790160886625</v>
       </c>
       <c r="M13" t="n">
-        <v>27.60380495442919</v>
+        <v>27.73251989400917</v>
       </c>
       <c r="N13" t="n">
-        <v>1076.535138105939</v>
+        <v>1084.523002661937</v>
       </c>
       <c r="O13" t="n">
-        <v>32.81059490630943</v>
+        <v>32.93209684581195</v>
       </c>
       <c r="P13" t="n">
-        <v>318.9811124521898</v>
+        <v>319.3322544943168</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -31227,28 +31318,28 @@
         <v>0.07920000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3775536093297785</v>
+        <v>-0.3629453431647887</v>
       </c>
       <c r="J14" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K14" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L14" t="n">
-        <v>0.01686032801183601</v>
+        <v>0.01561807246977021</v>
       </c>
       <c r="M14" t="n">
-        <v>18.23091622849227</v>
+        <v>18.25561162581837</v>
       </c>
       <c r="N14" t="n">
-        <v>452.8871798054183</v>
+        <v>453.5384443767148</v>
       </c>
       <c r="O14" t="n">
-        <v>21.28114611118063</v>
+        <v>21.29644205910261</v>
       </c>
       <c r="P14" t="n">
-        <v>306.3008534077886</v>
+        <v>306.146385476617</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -31305,28 +31396,28 @@
         <v>0.1073</v>
       </c>
       <c r="I15" t="n">
-        <v>0.05305111011251693</v>
+        <v>0.05525468528843499</v>
       </c>
       <c r="J15" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K15" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0004308780855412087</v>
+        <v>0.0004699840654576182</v>
       </c>
       <c r="M15" t="n">
-        <v>16.14250480245463</v>
+        <v>16.10390615654488</v>
       </c>
       <c r="N15" t="n">
-        <v>356.3385236955721</v>
+        <v>355.2787740267333</v>
       </c>
       <c r="O15" t="n">
-        <v>18.87693099249908</v>
+        <v>18.84884012417563</v>
       </c>
       <c r="P15" t="n">
-        <v>304.8842640158704</v>
+        <v>304.860966926978</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -31383,28 +31474,28 @@
         <v>0.0534</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2140435315431904</v>
+        <v>0.2087464627239251</v>
       </c>
       <c r="J16" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K16" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L16" t="n">
-        <v>0.004094479441468679</v>
+        <v>0.003915392087794456</v>
       </c>
       <c r="M16" t="n">
-        <v>20.11429180302202</v>
+        <v>20.08392098764043</v>
       </c>
       <c r="N16" t="n">
-        <v>599.4935075158164</v>
+        <v>597.8867012837179</v>
       </c>
       <c r="O16" t="n">
-        <v>24.48455651049895</v>
+        <v>24.45172184701351</v>
       </c>
       <c r="P16" t="n">
-        <v>315.1037970357702</v>
+        <v>315.1604394407167</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -31461,28 +31552,28 @@
         <v>0.0428</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.796560604153891</v>
+        <v>-0.7938408736733602</v>
       </c>
       <c r="J17" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K17" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L17" t="n">
-        <v>0.04882817432552844</v>
+        <v>0.04878493770542169</v>
       </c>
       <c r="M17" t="n">
-        <v>21.33393495565755</v>
+        <v>21.28079436213417</v>
       </c>
       <c r="N17" t="n">
-        <v>663.9390210397441</v>
+        <v>661.806650406424</v>
       </c>
       <c r="O17" t="n">
-        <v>25.767014204982</v>
+        <v>25.72560301346548</v>
       </c>
       <c r="P17" t="n">
-        <v>331.1147092514877</v>
+        <v>331.0856077542364</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -31539,28 +31630,28 @@
         <v>0.0478</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.135541078737362</v>
+        <v>-0.1238237195322749</v>
       </c>
       <c r="J18" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K18" t="n">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="L18" t="n">
-        <v>0.008339527427673743</v>
+        <v>0.006932775290568793</v>
       </c>
       <c r="M18" t="n">
-        <v>8.563534942546855</v>
+        <v>8.580761438787608</v>
       </c>
       <c r="N18" t="n">
-        <v>117.3241964181035</v>
+        <v>118.2581508069769</v>
       </c>
       <c r="O18" t="n">
-        <v>10.83162944427585</v>
+        <v>10.87465635351191</v>
       </c>
       <c r="P18" t="n">
-        <v>326.9417640525048</v>
+        <v>326.8167736488051</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -31617,28 +31708,28 @@
         <v>0.0415</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1909067757087079</v>
+        <v>0.1979929415804501</v>
       </c>
       <c r="J19" t="n">
+        <v>326</v>
+      </c>
+      <c r="K19" t="n">
         <v>325</v>
       </c>
-      <c r="K19" t="n">
-        <v>324</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.02690426449633765</v>
+        <v>0.02885068959950388</v>
       </c>
       <c r="M19" t="n">
-        <v>6.378217515259606</v>
+        <v>6.390740775899896</v>
       </c>
       <c r="N19" t="n">
-        <v>71.40665016095379</v>
+        <v>71.66640454846848</v>
       </c>
       <c r="O19" t="n">
-        <v>8.450245568085805</v>
+        <v>8.465601251445078</v>
       </c>
       <c r="P19" t="n">
-        <v>346.1169099029017</v>
+        <v>346.0417940148879</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -31695,28 +31786,28 @@
         <v>0.0344</v>
       </c>
       <c r="I20" t="n">
-        <v>0.02309068509585662</v>
+        <v>0.03665640318376406</v>
       </c>
       <c r="J20" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K20" t="n">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0003624080148172393</v>
+        <v>0.0008981136464564221</v>
       </c>
       <c r="M20" t="n">
-        <v>6.937931946767398</v>
+        <v>7.000684211408045</v>
       </c>
       <c r="N20" t="n">
-        <v>79.83049869899943</v>
+        <v>81.3477176365563</v>
       </c>
       <c r="O20" t="n">
-        <v>8.934791474847046</v>
+        <v>9.019296959106974</v>
       </c>
       <c r="P20" t="n">
-        <v>345.0588900874662</v>
+        <v>344.915157023447</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -31773,28 +31864,28 @@
         <v>0.0304</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2113885226871713</v>
+        <v>0.2219985412989718</v>
       </c>
       <c r="J21" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K21" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L21" t="n">
-        <v>0.01110494690746677</v>
+        <v>0.01224189780558282</v>
       </c>
       <c r="M21" t="n">
-        <v>11.78160848720977</v>
+        <v>11.80456434640099</v>
       </c>
       <c r="N21" t="n">
-        <v>214.2567621494989</v>
+        <v>214.6601875060032</v>
       </c>
       <c r="O21" t="n">
-        <v>14.63751215710849</v>
+        <v>14.65128620654184</v>
       </c>
       <c r="P21" t="n">
-        <v>322.3213956387004</v>
+        <v>322.2081991745361</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -31851,28 +31942,28 @@
         <v>0.0447</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2441427936120655</v>
+        <v>0.2508791221444997</v>
       </c>
       <c r="J22" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K22" t="n">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="L22" t="n">
-        <v>0.009506843332645953</v>
+        <v>0.01007688781059235</v>
       </c>
       <c r="M22" t="n">
-        <v>14.66625932874508</v>
+        <v>14.65758336944243</v>
       </c>
       <c r="N22" t="n">
-        <v>337.7153693505754</v>
+        <v>337.1085304956322</v>
       </c>
       <c r="O22" t="n">
-        <v>18.3770337473319</v>
+        <v>18.36051552913567</v>
       </c>
       <c r="P22" t="n">
-        <v>303.5903702903154</v>
+        <v>303.5190986213745</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -31929,28 +32020,28 @@
         <v>0.0592</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4794075013146226</v>
+        <v>0.4845198483264899</v>
       </c>
       <c r="J23" t="n">
+        <v>326</v>
+      </c>
+      <c r="K23" t="n">
         <v>325</v>
       </c>
-      <c r="K23" t="n">
-        <v>324</v>
-      </c>
       <c r="L23" t="n">
-        <v>0.1088110832347408</v>
+        <v>0.111203288267203</v>
       </c>
       <c r="M23" t="n">
-        <v>7.917925775750429</v>
+        <v>7.913757680347071</v>
       </c>
       <c r="N23" t="n">
-        <v>101.9689206486059</v>
+        <v>101.904731220369</v>
       </c>
       <c r="O23" t="n">
-        <v>10.09796616396618</v>
+        <v>10.09478732913027</v>
       </c>
       <c r="P23" t="n">
-        <v>323.222952833491</v>
+        <v>323.1687601300486</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -32007,28 +32098,28 @@
         <v>0.07870000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1607665251321449</v>
+        <v>0.1601632441923008</v>
       </c>
       <c r="J24" t="n">
+        <v>326</v>
+      </c>
+      <c r="K24" t="n">
         <v>325</v>
       </c>
-      <c r="K24" t="n">
-        <v>324</v>
-      </c>
       <c r="L24" t="n">
-        <v>0.0427671061996292</v>
+        <v>0.04268715650548383</v>
       </c>
       <c r="M24" t="n">
-        <v>3.979556203505374</v>
+        <v>3.970957850285626</v>
       </c>
       <c r="N24" t="n">
-        <v>31.25907065947388</v>
+        <v>31.16635303879702</v>
       </c>
       <c r="O24" t="n">
-        <v>5.59098118933286</v>
+        <v>5.582683318870687</v>
       </c>
       <c r="P24" t="n">
-        <v>340.0613722009339</v>
+        <v>340.0677778522093</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -32070,7 +32161,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y326"/>
+  <dimension ref="A1:Y327"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72696,7 +72787,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>-38.57707769978312,174.6306605693037</t>
+          <t>-38.577082210966914,174.6308961335507</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
@@ -72773,32 +72864,32 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>-38.584058984020984,174.62914062481994</t>
+          <t>-38.5840807294396,174.62958778026828</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>-38.583354776922356,174.6291265392708</t>
+          <t>-38.58337637770613,174.6295707116186</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>-38.58262307407193,174.62805058778108</t>
+          <t>-38.58266205655402,174.62921424725945</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>-38.58197454363686,174.62957863315015</t>
+          <t>-38.5819787015408,174.63024481518352</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>-38.581275531531574,174.62924070713512</t>
+          <t>-38.58127214172505,174.62981816091684</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>-38.5805732027511,174.62926090079122</t>
+          <t>-38.580569939672074,174.6298167706806</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
@@ -72823,7 +72914,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>-38.57707769978312,174.6306605693037</t>
+          <t>-38.577082210966914,174.6308961335507</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -72882,6 +72973,133 @@
         </is>
       </c>
       <c r="Y326" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:06:49+00:00</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>-38.584779302510626,174.62948615782662</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>-38.58407976004162,174.62956784558588</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>-38.58337612142613,174.62956544158178</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>-38.582666904061725,174.6293589736675</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>-38.58197848098929,174.63020946300264</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>-38.581272111391925,174.6298233259768</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>-38.58056981699406,174.62983766027514</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>-38.5798656926666,174.63016235100818</t>
+        </is>
+      </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>-38.57916368598548,174.63012537711407</t>
+        </is>
+      </c>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>-38.57846155104554,174.63010906344496</t>
+        </is>
+      </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>-38.57776415966012,174.6301518730531</t>
+        </is>
+      </c>
+      <c r="M327" t="inlineStr">
+        <is>
+          <t>-38.5770748100028,174.63050968427146</t>
+        </is>
+      </c>
+      <c r="N327" t="inlineStr">
+        <is>
+          <t>-38.57636656801875,174.63015610075686</t>
+        </is>
+      </c>
+      <c r="O327" t="inlineStr">
+        <is>
+          <t>-38.57566783394727,174.63033094190314</t>
+        </is>
+      </c>
+      <c r="P327" t="inlineStr">
+        <is>
+          <t>-38.574965775985646,174.63035204355236</t>
+        </is>
+      </c>
+      <c r="Q327" t="inlineStr">
+        <is>
+          <t>-38.57426965067606,174.63034690048346</t>
+        </is>
+      </c>
+      <c r="R327" t="inlineStr">
+        <is>
+          <t>-38.57356004721491,174.63007913022966</t>
+        </is>
+      </c>
+      <c r="S327" t="inlineStr">
+        <is>
+          <t>-38.57284805963326,174.62992906297248</t>
+        </is>
+      </c>
+      <c r="T327" t="inlineStr">
+        <is>
+          <t>-38.57214546016539,174.62993440301122</t>
+        </is>
+      </c>
+      <c r="U327" t="inlineStr">
+        <is>
+          <t>-38.571455419484195,174.63025763155463</t>
+        </is>
+      </c>
+      <c r="V327" t="inlineStr">
+        <is>
+          <t>-38.570757106706644,174.6305703389787</t>
+        </is>
+      </c>
+      <c r="W327" t="inlineStr">
+        <is>
+          <t>-38.570050960528604,174.6303384209414</t>
+        </is>
+      </c>
+      <c r="X327" t="inlineStr">
+        <is>
+          <t>-38.56935001447708,174.63039324181173</t>
+        </is>
+      </c>
+      <c r="Y327" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0264/nzd0264.xlsx
+++ b/data/nzd0264/nzd0264.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y327"/>
+  <dimension ref="A1:Y328"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26670,6 +26670,87 @@
         </is>
       </c>
     </row>
+    <row r="328">
+      <c r="A328" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:26+00:00</t>
+        </is>
+      </c>
+      <c r="B328" t="n">
+        <v>358.38</v>
+      </c>
+      <c r="C328" t="n">
+        <v>357.54</v>
+      </c>
+      <c r="D328" t="n">
+        <v>350.51</v>
+      </c>
+      <c r="E328" t="n">
+        <v>381.44</v>
+      </c>
+      <c r="F328" t="n">
+        <v>314.48</v>
+      </c>
+      <c r="G328" t="n">
+        <v>338.34</v>
+      </c>
+      <c r="H328" t="n">
+        <v>341.91</v>
+      </c>
+      <c r="I328" t="n">
+        <v>327.81</v>
+      </c>
+      <c r="J328" t="n">
+        <v>330.84</v>
+      </c>
+      <c r="K328" t="n">
+        <v>331.37</v>
+      </c>
+      <c r="L328" t="n">
+        <v>329.08</v>
+      </c>
+      <c r="M328" t="n">
+        <v>315.02</v>
+      </c>
+      <c r="N328" t="n">
+        <v>336.94</v>
+      </c>
+      <c r="O328" t="n">
+        <v>329.66</v>
+      </c>
+      <c r="P328" t="n">
+        <v>331.29</v>
+      </c>
+      <c r="Q328" t="n">
+        <v>322.38</v>
+      </c>
+      <c r="R328" t="n">
+        <v>336.58</v>
+      </c>
+      <c r="S328" t="n">
+        <v>360.04</v>
+      </c>
+      <c r="T328" t="n">
+        <v>358.15</v>
+      </c>
+      <c r="U328" t="n">
+        <v>349.91</v>
+      </c>
+      <c r="V328" t="n">
+        <v>332.58</v>
+      </c>
+      <c r="W328" t="n">
+        <v>336.66</v>
+      </c>
+      <c r="X328" t="n">
+        <v>341.48</v>
+      </c>
+      <c r="Y328" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -26681,7 +26762,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B353"/>
+  <dimension ref="A1:B354"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30214,6 +30295,16 @@
       </c>
       <c r="B353" t="n">
         <v>0.93</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B354" t="n">
+        <v>-0.51</v>
       </c>
     </row>
   </sheetData>
@@ -30382,28 +30473,28 @@
         <v>0.0285</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7927666226008517</v>
+        <v>0.7938661522834649</v>
       </c>
       <c r="J2" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K2" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1272514027721039</v>
+        <v>0.1281898058902103</v>
       </c>
       <c r="M2" t="n">
-        <v>12.12793455780054</v>
+        <v>12.09637986496973</v>
       </c>
       <c r="N2" t="n">
-        <v>232.0364344642136</v>
+        <v>231.3204608658736</v>
       </c>
       <c r="O2" t="n">
-        <v>15.2327421846565</v>
+        <v>15.20922288829622</v>
       </c>
       <c r="P2" t="n">
-        <v>335.7444145898132</v>
+        <v>335.7325519472859</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -30460,28 +30551,28 @@
         <v>0.0381</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2434505193212328</v>
+        <v>-0.2293818318899418</v>
       </c>
       <c r="J3" t="n">
+        <v>327</v>
+      </c>
+      <c r="K3" t="n">
         <v>326</v>
       </c>
-      <c r="K3" t="n">
-        <v>325</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.01111424907295189</v>
+        <v>0.009871110444862219</v>
       </c>
       <c r="M3" t="n">
-        <v>11.98012206419253</v>
+        <v>11.9967771789612</v>
       </c>
       <c r="N3" t="n">
-        <v>286.4005168871387</v>
+        <v>287.3980607773748</v>
       </c>
       <c r="O3" t="n">
-        <v>16.9233719124511</v>
+        <v>16.952818667625</v>
       </c>
       <c r="P3" t="n">
-        <v>339.0597645702169</v>
+        <v>338.9097997932139</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30538,28 +30629,28 @@
         <v>0.0304</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.173546854227121</v>
+        <v>-0.1627601300441846</v>
       </c>
       <c r="J4" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K4" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004873604755958327</v>
+        <v>0.004299458381208487</v>
       </c>
       <c r="M4" t="n">
-        <v>13.34721596078592</v>
+        <v>13.34898960530841</v>
       </c>
       <c r="N4" t="n">
-        <v>332.0296275265214</v>
+        <v>332.0984069614114</v>
       </c>
       <c r="O4" t="n">
-        <v>18.22168015103221</v>
+        <v>18.22356735003911</v>
       </c>
       <c r="P4" t="n">
-        <v>336.1421255201036</v>
+        <v>336.0264101962934</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30616,28 +30707,28 @@
         <v>0.0232</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7702356107167757</v>
+        <v>0.7920982494903198</v>
       </c>
       <c r="J5" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K5" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05921630148904067</v>
+        <v>0.06226792715034635</v>
       </c>
       <c r="M5" t="n">
-        <v>18.22118543756431</v>
+        <v>18.28268010725417</v>
       </c>
       <c r="N5" t="n">
-        <v>510.6551468536968</v>
+        <v>513.3069831047062</v>
       </c>
       <c r="O5" t="n">
-        <v>22.59768012105881</v>
+        <v>22.65627910987826</v>
       </c>
       <c r="P5" t="n">
-        <v>324.8155384757009</v>
+        <v>324.5809355963872</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30694,28 +30785,28 @@
         <v>0.0304</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3002921644106585</v>
+        <v>0.2989174962298451</v>
       </c>
       <c r="J6" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K6" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L6" t="n">
-        <v>0.006655887284505613</v>
+        <v>0.00663289043604498</v>
       </c>
       <c r="M6" t="n">
-        <v>19.60159745584375</v>
+        <v>19.5508135877428</v>
       </c>
       <c r="N6" t="n">
-        <v>728.3850413293807</v>
+        <v>726.1478649590109</v>
       </c>
       <c r="O6" t="n">
-        <v>26.98860947380173</v>
+        <v>26.94713092258638</v>
       </c>
       <c r="P6" t="n">
-        <v>309.0450260743281</v>
+        <v>309.0597522816579</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30772,28 +30863,28 @@
         <v>0.0311</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0314088101391589</v>
+        <v>0.03949148493679896</v>
       </c>
       <c r="J7" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K7" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001161425775834113</v>
+        <v>0.0001844209315561285</v>
       </c>
       <c r="M7" t="n">
-        <v>15.7786609146967</v>
+        <v>15.75310770032294</v>
       </c>
       <c r="N7" t="n">
-        <v>459.4274312714744</v>
+        <v>458.604817340822</v>
       </c>
       <c r="O7" t="n">
-        <v>21.43425835599344</v>
+        <v>21.41506052620029</v>
       </c>
       <c r="P7" t="n">
-        <v>323.4743467163638</v>
+        <v>323.3879003907215</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30850,28 +30941,28 @@
         <v>0.0451</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1002259640420497</v>
+        <v>0.1054732095756166</v>
       </c>
       <c r="J8" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K8" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L8" t="n">
-        <v>0.004538029180940262</v>
+        <v>0.005040866721479076</v>
       </c>
       <c r="M8" t="n">
-        <v>8.867199497936074</v>
+        <v>8.864374942495493</v>
       </c>
       <c r="N8" t="n">
-        <v>119.9181901756491</v>
+        <v>119.8111316990274</v>
       </c>
       <c r="O8" t="n">
-        <v>10.95071642294006</v>
+        <v>10.94582713635783</v>
       </c>
       <c r="P8" t="n">
-        <v>330.0241230755354</v>
+        <v>329.9682152086139</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -30928,28 +31019,28 @@
         <v>0.0388</v>
       </c>
       <c r="I9" t="n">
-        <v>0.07893712299892343</v>
+        <v>0.0750625354877007</v>
       </c>
       <c r="J9" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K9" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001132315959378793</v>
+        <v>0.001029354556194684</v>
       </c>
       <c r="M9" t="n">
-        <v>12.54448063981563</v>
+        <v>12.53315948409934</v>
       </c>
       <c r="N9" t="n">
-        <v>300.097714083994</v>
+        <v>299.3122745448739</v>
       </c>
       <c r="O9" t="n">
-        <v>17.32332860867085</v>
+        <v>17.30064376099554</v>
       </c>
       <c r="P9" t="n">
-        <v>332.5892326205015</v>
+        <v>332.6304991057406</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31006,28 +31097,28 @@
         <v>0.079</v>
       </c>
       <c r="I10" t="n">
-        <v>0.01318275990756703</v>
+        <v>0.01885533985334655</v>
       </c>
       <c r="J10" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K10" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L10" t="n">
-        <v>4.165061751171262e-05</v>
+        <v>8.557616474536012e-05</v>
       </c>
       <c r="M10" t="n">
-        <v>12.73865176859488</v>
+        <v>12.72549395424962</v>
       </c>
       <c r="N10" t="n">
-        <v>225.389659637636</v>
+        <v>224.9959695206583</v>
       </c>
       <c r="O10" t="n">
-        <v>15.01298303594712</v>
+        <v>14.99986565008695</v>
       </c>
       <c r="P10" t="n">
-        <v>320.5407615190522</v>
+        <v>320.4799059184159</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -31084,28 +31175,28 @@
         <v>0.0864</v>
       </c>
       <c r="I11" t="n">
-        <v>0.02026579257214188</v>
+        <v>0.02924568872434567</v>
       </c>
       <c r="J11" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K11" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L11" t="n">
-        <v>8.094619069132225e-05</v>
+        <v>0.0001690536634900708</v>
       </c>
       <c r="M11" t="n">
-        <v>13.68851695279617</v>
+        <v>13.69147137846594</v>
       </c>
       <c r="N11" t="n">
-        <v>275.3424297725112</v>
+        <v>275.2560762167038</v>
       </c>
       <c r="O11" t="n">
-        <v>16.59344538582965</v>
+        <v>16.5908431436351</v>
       </c>
       <c r="P11" t="n">
-        <v>315.0354413992252</v>
+        <v>314.9394140719605</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -31162,28 +31253,28 @@
         <v>0.06569999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3237209114031382</v>
+        <v>0.3246275122503649</v>
       </c>
       <c r="J12" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K12" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L12" t="n">
-        <v>0.02543736021280663</v>
+        <v>0.02572302465509224</v>
       </c>
       <c r="M12" t="n">
-        <v>12.23733916782892</v>
+        <v>12.20217373673447</v>
       </c>
       <c r="N12" t="n">
-        <v>219.1731665571428</v>
+        <v>218.4871809209904</v>
       </c>
       <c r="O12" t="n">
-        <v>14.80449818660338</v>
+        <v>14.78131188091877</v>
       </c>
       <c r="P12" t="n">
-        <v>319.0643679644213</v>
+        <v>319.0547373786134</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -31240,28 +31331,28 @@
         <v>0.0371</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.5922396776149372</v>
+        <v>-0.5856113208203121</v>
       </c>
       <c r="J13" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K13" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0177790160886625</v>
+        <v>0.01748604652719388</v>
       </c>
       <c r="M13" t="n">
-        <v>27.73251989400917</v>
+        <v>27.6709883755523</v>
       </c>
       <c r="N13" t="n">
-        <v>1084.523002661937</v>
+        <v>1081.319203712007</v>
       </c>
       <c r="O13" t="n">
-        <v>32.93209684581195</v>
+        <v>32.8834183702365</v>
       </c>
       <c r="P13" t="n">
-        <v>319.3322544943168</v>
+        <v>319.2625321546589</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -31318,28 +31409,28 @@
         <v>0.07920000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3629453431647887</v>
+        <v>-0.3401502383521556</v>
       </c>
       <c r="J14" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K14" t="n">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="L14" t="n">
-        <v>0.01561807246977021</v>
+        <v>0.01367368190494445</v>
       </c>
       <c r="M14" t="n">
-        <v>18.25561162581837</v>
+        <v>18.32409393053389</v>
       </c>
       <c r="N14" t="n">
-        <v>453.5384443767148</v>
+        <v>457.10172305035</v>
       </c>
       <c r="O14" t="n">
-        <v>21.29644205910261</v>
+        <v>21.3799373958473</v>
       </c>
       <c r="P14" t="n">
-        <v>306.146385476617</v>
+        <v>305.9039913861193</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -31396,28 +31487,28 @@
         <v>0.1073</v>
       </c>
       <c r="I15" t="n">
-        <v>0.05525468528843499</v>
+        <v>0.06846844374700856</v>
       </c>
       <c r="J15" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K15" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0004699840654576182</v>
+        <v>0.0007221830401575868</v>
       </c>
       <c r="M15" t="n">
-        <v>16.10390615654488</v>
+        <v>16.12296887408135</v>
       </c>
       <c r="N15" t="n">
-        <v>355.2787740267333</v>
+        <v>355.8524954252642</v>
       </c>
       <c r="O15" t="n">
-        <v>18.84884012417563</v>
+        <v>18.86405299571818</v>
       </c>
       <c r="P15" t="n">
-        <v>304.860966926978</v>
+        <v>304.7204742940602</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -31474,28 +31565,28 @@
         <v>0.0534</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2087464627239251</v>
+        <v>0.2148565054806402</v>
       </c>
       <c r="J16" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K16" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L16" t="n">
-        <v>0.003915392087794456</v>
+        <v>0.004168219644010374</v>
       </c>
       <c r="M16" t="n">
-        <v>20.08392098764043</v>
+        <v>20.05035899211038</v>
       </c>
       <c r="N16" t="n">
-        <v>597.8867012837179</v>
+        <v>596.3761693334725</v>
       </c>
       <c r="O16" t="n">
-        <v>24.45172184701351</v>
+        <v>24.42081426434165</v>
       </c>
       <c r="P16" t="n">
-        <v>315.1604394407167</v>
+        <v>315.0947362148835</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -31552,28 +31643,28 @@
         <v>0.0428</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.7938408736733602</v>
+        <v>-0.7865341205621761</v>
       </c>
       <c r="J17" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K17" t="n">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="L17" t="n">
-        <v>0.04878493770542169</v>
+        <v>0.04817849776606431</v>
       </c>
       <c r="M17" t="n">
-        <v>21.28079436213417</v>
+        <v>21.2571147935812</v>
       </c>
       <c r="N17" t="n">
-        <v>661.806650406424</v>
+        <v>660.0963885108964</v>
       </c>
       <c r="O17" t="n">
-        <v>25.72560301346548</v>
+        <v>25.69234104769156</v>
       </c>
       <c r="P17" t="n">
-        <v>331.0856077542364</v>
+        <v>331.0069856021888</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -31630,28 +31721,28 @@
         <v>0.0478</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1238237195322749</v>
+        <v>-0.1164058505437965</v>
       </c>
       <c r="J18" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K18" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L18" t="n">
-        <v>0.006932775290568793</v>
+        <v>0.00614038205585099</v>
       </c>
       <c r="M18" t="n">
-        <v>8.580761438787608</v>
+        <v>8.581574631069861</v>
       </c>
       <c r="N18" t="n">
-        <v>118.2581508069769</v>
+        <v>118.4098746719034</v>
       </c>
       <c r="O18" t="n">
-        <v>10.87465635351191</v>
+        <v>10.88163014772618</v>
       </c>
       <c r="P18" t="n">
-        <v>326.8167736488051</v>
+        <v>326.7372077951153</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -31708,28 +31799,28 @@
         <v>0.0415</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1979929415804501</v>
+        <v>0.2029934795747081</v>
       </c>
       <c r="J19" t="n">
+        <v>327</v>
+      </c>
+      <c r="K19" t="n">
         <v>326</v>
       </c>
-      <c r="K19" t="n">
-        <v>325</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.02885068959950388</v>
+        <v>0.03035276820243293</v>
       </c>
       <c r="M19" t="n">
-        <v>6.390740775899896</v>
+        <v>6.39388436385371</v>
       </c>
       <c r="N19" t="n">
-        <v>71.66640454846848</v>
+        <v>71.6835840725268</v>
       </c>
       <c r="O19" t="n">
-        <v>8.465601251445078</v>
+        <v>8.466615857148994</v>
       </c>
       <c r="P19" t="n">
-        <v>346.0417940148879</v>
+        <v>345.9884909211298</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -31786,28 +31877,28 @@
         <v>0.0344</v>
       </c>
       <c r="I20" t="n">
-        <v>0.03665640318376406</v>
+        <v>0.04360802802773028</v>
       </c>
       <c r="J20" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K20" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0008981136464564221</v>
+        <v>0.001270666637519846</v>
       </c>
       <c r="M20" t="n">
-        <v>7.000684211408045</v>
+        <v>7.022456413532455</v>
       </c>
       <c r="N20" t="n">
-        <v>81.3477176365563</v>
+        <v>81.55712224223582</v>
       </c>
       <c r="O20" t="n">
-        <v>9.019296959106974</v>
+        <v>9.030898196870332</v>
       </c>
       <c r="P20" t="n">
-        <v>344.915157023447</v>
+        <v>344.8410894933156</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -31864,28 +31955,28 @@
         <v>0.0304</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2219985412989718</v>
+        <v>0.2344989120212837</v>
       </c>
       <c r="J21" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K21" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L21" t="n">
-        <v>0.01224189780558282</v>
+        <v>0.01362481971588347</v>
       </c>
       <c r="M21" t="n">
-        <v>11.80456434640099</v>
+        <v>11.83821461279968</v>
       </c>
       <c r="N21" t="n">
-        <v>214.6601875060032</v>
+        <v>215.4681214366449</v>
       </c>
       <c r="O21" t="n">
-        <v>14.65128620654184</v>
+        <v>14.67883242756878</v>
       </c>
       <c r="P21" t="n">
-        <v>322.2081991745361</v>
+        <v>322.0740887749316</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -31942,28 +32033,28 @@
         <v>0.0447</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2508791221444997</v>
+        <v>0.2636155615656641</v>
       </c>
       <c r="J22" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K22" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L22" t="n">
-        <v>0.01007688781059235</v>
+        <v>0.01112682065697324</v>
       </c>
       <c r="M22" t="n">
-        <v>14.65758336944243</v>
+        <v>14.68222142782557</v>
       </c>
       <c r="N22" t="n">
-        <v>337.1085304956322</v>
+        <v>337.6166449732079</v>
       </c>
       <c r="O22" t="n">
-        <v>18.36051552913567</v>
+        <v>18.37434747067791</v>
       </c>
       <c r="P22" t="n">
-        <v>303.5190986213745</v>
+        <v>303.3835884708138</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -32020,28 +32111,28 @@
         <v>0.0592</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4845198483264899</v>
+        <v>0.4849875166497327</v>
       </c>
       <c r="J23" t="n">
+        <v>327</v>
+      </c>
+      <c r="K23" t="n">
         <v>326</v>
       </c>
-      <c r="K23" t="n">
-        <v>325</v>
-      </c>
       <c r="L23" t="n">
-        <v>0.111203288267203</v>
+        <v>0.11196042730662</v>
       </c>
       <c r="M23" t="n">
-        <v>7.913757680347071</v>
+        <v>7.891312812497173</v>
       </c>
       <c r="N23" t="n">
-        <v>101.904731220369</v>
+        <v>101.5942131119454</v>
       </c>
       <c r="O23" t="n">
-        <v>10.09478732913027</v>
+        <v>10.07939547353637</v>
       </c>
       <c r="P23" t="n">
-        <v>323.1687601300486</v>
+        <v>323.163775032743</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -32098,28 +32189,28 @@
         <v>0.07870000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1601632441923008</v>
+        <v>0.1585886282937093</v>
       </c>
       <c r="J24" t="n">
+        <v>327</v>
+      </c>
+      <c r="K24" t="n">
         <v>326</v>
       </c>
-      <c r="K24" t="n">
-        <v>325</v>
-      </c>
       <c r="L24" t="n">
-        <v>0.04268715650548383</v>
+        <v>0.04208719989273391</v>
       </c>
       <c r="M24" t="n">
-        <v>3.970957850285626</v>
+        <v>3.968187150031667</v>
       </c>
       <c r="N24" t="n">
-        <v>31.16635303879702</v>
+        <v>31.09417715959248</v>
       </c>
       <c r="O24" t="n">
-        <v>5.582683318870687</v>
+        <v>5.576215307858233</v>
       </c>
       <c r="P24" t="n">
-        <v>340.0677778522093</v>
+        <v>340.0845901797721</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -32161,7 +32252,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y327"/>
+  <dimension ref="A1:Y328"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73105,6 +73196,133 @@
         </is>
       </c>
     </row>
+    <row r="328">
+      <c r="A328" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:26+00:00</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>-38.584776327420094,174.62942497838262</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>-38.584076495262465,174.62950070924478</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>-38.58338010488195,174.62964735628756</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>-38.582666904061725,174.6293589736675</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>-38.58197816661332,174.63015907466664</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>-38.58127172513016,174.62988909440583</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>-38.58056973340908,174.629851892746</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>-38.579866543622956,174.63001750261108</t>
+        </is>
+      </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>-38.57916450181313,174.62998649846415</t>
+        </is>
+      </c>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>-38.578462284583594,174.6299841886515</t>
+        </is>
+      </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>-38.57776341188612,174.6300141442748</t>
+        </is>
+      </c>
+      <c r="M328" t="inlineStr">
+        <is>
+          <t>-38.57706897271154,174.63020493094453</t>
+        </is>
+      </c>
+      <c r="N328" t="inlineStr">
+        <is>
+          <t>-38.57636295370669,174.62998859325222</t>
+        </is>
+      </c>
+      <c r="O328" t="inlineStr">
+        <is>
+          <t>-38.57566300930754,174.63010733302897</t>
+        </is>
+      </c>
+      <c r="P328" t="inlineStr">
+        <is>
+          <t>-38.574960852301956,174.63012384770056</t>
+        </is>
+      </c>
+      <c r="Q328" t="inlineStr">
+        <is>
+          <t>-38.57426661949415,174.63026090876517</t>
+        </is>
+      </c>
+      <c r="R328" t="inlineStr">
+        <is>
+          <t>-38.57356451091656,174.63016409955875</t>
+        </is>
+      </c>
+      <c r="S328" t="inlineStr">
+        <is>
+          <t>-38.57285035963434,174.62997004565113</t>
+        </is>
+      </c>
+      <c r="T328" t="inlineStr">
+        <is>
+          <t>-38.57215184057277,174.63006636546257</t>
+        </is>
+      </c>
+      <c r="U328" t="inlineStr">
+        <is>
+          <t>-38.57145426777344,174.63021794939297</t>
+        </is>
+      </c>
+      <c r="V328" t="inlineStr">
+        <is>
+          <t>-38.57075495914668,174.63044745551164</t>
+        </is>
+      </c>
+      <c r="W328" t="inlineStr">
+        <is>
+          <t>-38.570052841637974,174.6304311196468</t>
+        </is>
+      </c>
+      <c r="X328" t="inlineStr">
+        <is>
+          <t>-38.569350465123456,174.6304127431305</t>
+        </is>
+      </c>
+      <c r="Y328" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0264/nzd0264.xlsx
+++ b/data/nzd0264/nzd0264.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y328"/>
+  <dimension ref="A1:Y330"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26629,7 +26629,7 @@
         <v>317.08</v>
       </c>
       <c r="M327" t="n">
-        <v>288.46</v>
+        <v>254.78</v>
       </c>
       <c r="N327" t="n">
         <v>322.34</v>
@@ -26686,7 +26686,7 @@
         <v>350.51</v>
       </c>
       <c r="E328" t="n">
-        <v>381.44</v>
+        <v>362.63</v>
       </c>
       <c r="F328" t="n">
         <v>314.48</v>
@@ -26710,13 +26710,13 @@
         <v>329.08</v>
       </c>
       <c r="M328" t="n">
-        <v>315.02</v>
+        <v>251.07</v>
       </c>
       <c r="N328" t="n">
-        <v>336.94</v>
+        <v>328.88</v>
       </c>
       <c r="O328" t="n">
-        <v>329.66</v>
+        <v>323.75</v>
       </c>
       <c r="P328" t="n">
         <v>331.29</v>
@@ -26748,6 +26748,166 @@
       <c r="Y328" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:06:25+00:00</t>
+        </is>
+      </c>
+      <c r="B329" t="n">
+        <v>355.47</v>
+      </c>
+      <c r="C329" t="n">
+        <v>360.17</v>
+      </c>
+      <c r="D329" t="n">
+        <v>352.41</v>
+      </c>
+      <c r="E329" t="n">
+        <v>362.63</v>
+      </c>
+      <c r="F329" t="n">
+        <v>321.67</v>
+      </c>
+      <c r="G329" t="n">
+        <v>333.29</v>
+      </c>
+      <c r="H329" t="n">
+        <v>343.63</v>
+      </c>
+      <c r="I329" t="n">
+        <v>332.29</v>
+      </c>
+      <c r="J329" t="n">
+        <v>337.45</v>
+      </c>
+      <c r="K329" t="n">
+        <v>337.62</v>
+      </c>
+      <c r="L329" t="n">
+        <v>336</v>
+      </c>
+      <c r="M329" t="inlineStr"/>
+      <c r="N329" t="n">
+        <v>328.88</v>
+      </c>
+      <c r="O329" t="n">
+        <v>329.86</v>
+      </c>
+      <c r="P329" t="n">
+        <v>341.29</v>
+      </c>
+      <c r="Q329" t="n">
+        <v>330.69</v>
+      </c>
+      <c r="R329" t="n">
+        <v>330.71</v>
+      </c>
+      <c r="S329" t="n">
+        <v>356.18</v>
+      </c>
+      <c r="T329" t="n">
+        <v>352.76</v>
+      </c>
+      <c r="U329" t="n">
+        <v>346.81</v>
+      </c>
+      <c r="V329" t="n">
+        <v>340.88</v>
+      </c>
+      <c r="W329" t="n">
+        <v>336.37</v>
+      </c>
+      <c r="X329" t="n">
+        <v>342.98</v>
+      </c>
+      <c r="Y329" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:06:21+00:00</t>
+        </is>
+      </c>
+      <c r="B330" t="n">
+        <v>351.54</v>
+      </c>
+      <c r="C330" t="n">
+        <v>362.84</v>
+      </c>
+      <c r="D330" t="n">
+        <v>354.87</v>
+      </c>
+      <c r="E330" t="n">
+        <v>362.63</v>
+      </c>
+      <c r="F330" t="n">
+        <v>327.94</v>
+      </c>
+      <c r="G330" t="n">
+        <v>331.54</v>
+      </c>
+      <c r="H330" t="n">
+        <v>345.49</v>
+      </c>
+      <c r="I330" t="n">
+        <v>340.81</v>
+      </c>
+      <c r="J330" t="n">
+        <v>341.57</v>
+      </c>
+      <c r="K330" t="n">
+        <v>342.11</v>
+      </c>
+      <c r="L330" t="n">
+        <v>342.27</v>
+      </c>
+      <c r="M330" t="n">
+        <v>296.44</v>
+      </c>
+      <c r="N330" t="n">
+        <v>328.91</v>
+      </c>
+      <c r="O330" t="n">
+        <v>328.81</v>
+      </c>
+      <c r="P330" t="n">
+        <v>341.35</v>
+      </c>
+      <c r="Q330" t="n">
+        <v>334.26</v>
+      </c>
+      <c r="R330" t="n">
+        <v>330.6</v>
+      </c>
+      <c r="S330" t="n">
+        <v>356.44</v>
+      </c>
+      <c r="T330" t="n">
+        <v>353.27</v>
+      </c>
+      <c r="U330" t="n">
+        <v>346.27</v>
+      </c>
+      <c r="V330" t="n">
+        <v>345.14</v>
+      </c>
+      <c r="W330" t="n">
+        <v>336.37</v>
+      </c>
+      <c r="X330" t="n">
+        <v>343.44</v>
+      </c>
+      <c r="Y330" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -26762,7 +26922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B354"/>
+  <dimension ref="A1:B356"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30305,6 +30465,26 @@
       </c>
       <c r="B354" t="n">
         <v>-0.51</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B355" t="n">
+        <v>-0.38</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B356" t="n">
+        <v>0.59</v>
       </c>
     </row>
   </sheetData>
@@ -30473,28 +30653,28 @@
         <v>0.0285</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7938661522834649</v>
+        <v>0.7904123504587963</v>
       </c>
       <c r="J2" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K2" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1281898058902103</v>
+        <v>0.1284471300315616</v>
       </c>
       <c r="M2" t="n">
-        <v>12.09637986496973</v>
+        <v>12.03816779468545</v>
       </c>
       <c r="N2" t="n">
-        <v>231.3204608658736</v>
+        <v>229.960208014923</v>
       </c>
       <c r="O2" t="n">
-        <v>15.20922288829622</v>
+        <v>15.16443892845769</v>
       </c>
       <c r="P2" t="n">
-        <v>335.7325519472859</v>
+        <v>335.770000961288</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -30551,28 +30731,28 @@
         <v>0.0381</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2293818318899418</v>
+        <v>-0.1972923688251657</v>
       </c>
       <c r="J3" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K3" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="L3" t="n">
-        <v>0.009871110444862219</v>
+        <v>0.00728045300742397</v>
       </c>
       <c r="M3" t="n">
-        <v>11.9967771789612</v>
+        <v>12.04516506190174</v>
       </c>
       <c r="N3" t="n">
-        <v>287.3980607773748</v>
+        <v>290.5598889671264</v>
       </c>
       <c r="O3" t="n">
-        <v>16.952818667625</v>
+        <v>17.04581734523535</v>
       </c>
       <c r="P3" t="n">
-        <v>338.9097997932139</v>
+        <v>338.5664014217335</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30629,28 +30809,28 @@
         <v>0.0304</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1627601300441846</v>
+        <v>-0.1380320567541286</v>
       </c>
       <c r="J4" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K4" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004299458381208487</v>
+        <v>0.003104238146790284</v>
       </c>
       <c r="M4" t="n">
-        <v>13.34898960530841</v>
+        <v>13.36412734337432</v>
       </c>
       <c r="N4" t="n">
-        <v>332.0984069614114</v>
+        <v>332.9591317710947</v>
       </c>
       <c r="O4" t="n">
-        <v>18.22356735003911</v>
+        <v>18.24716777396138</v>
       </c>
       <c r="P4" t="n">
-        <v>336.0264101962934</v>
+        <v>335.7600900305516</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30707,28 +30887,28 @@
         <v>0.0232</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7920982494903198</v>
+        <v>0.8015344156999429</v>
       </c>
       <c r="J5" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K5" t="n">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06226792715034635</v>
+        <v>0.06453845725402974</v>
       </c>
       <c r="M5" t="n">
-        <v>18.28268010725417</v>
+        <v>18.21479615818003</v>
       </c>
       <c r="N5" t="n">
-        <v>513.3069831047062</v>
+        <v>508.6255746975105</v>
       </c>
       <c r="O5" t="n">
-        <v>22.65627910987826</v>
+        <v>22.55272876388821</v>
       </c>
       <c r="P5" t="n">
-        <v>324.5809355963872</v>
+        <v>324.478810597234</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30785,28 +30965,28 @@
         <v>0.0304</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2989174962298451</v>
+        <v>0.3078528930755969</v>
       </c>
       <c r="J6" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K6" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L6" t="n">
-        <v>0.00663289043604498</v>
+        <v>0.007108334000166083</v>
       </c>
       <c r="M6" t="n">
-        <v>19.5508135877428</v>
+        <v>19.46274237349777</v>
       </c>
       <c r="N6" t="n">
-        <v>726.1478649590109</v>
+        <v>722.1181689157377</v>
       </c>
       <c r="O6" t="n">
-        <v>26.94713092258638</v>
+        <v>26.8722564909562</v>
       </c>
       <c r="P6" t="n">
-        <v>309.0597522816579</v>
+        <v>308.9635977768219</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30863,28 +31043,28 @@
         <v>0.0311</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03949148493679896</v>
+        <v>0.04859904192945898</v>
       </c>
       <c r="J7" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K7" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001844209315561285</v>
+        <v>0.0002822733293822433</v>
       </c>
       <c r="M7" t="n">
-        <v>15.75310770032294</v>
+        <v>15.68226247899865</v>
       </c>
       <c r="N7" t="n">
-        <v>458.604817340822</v>
+        <v>456.1585956874996</v>
       </c>
       <c r="O7" t="n">
-        <v>21.41506052620029</v>
+        <v>21.35786964300278</v>
       </c>
       <c r="P7" t="n">
-        <v>323.3879003907215</v>
+        <v>323.2901363469001</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30941,28 +31121,28 @@
         <v>0.0451</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1054732095756166</v>
+        <v>0.1187357190217746</v>
       </c>
       <c r="J8" t="n">
+        <v>329</v>
+      </c>
+      <c r="K8" t="n">
         <v>327</v>
       </c>
-      <c r="K8" t="n">
-        <v>325</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.005040866721479076</v>
+        <v>0.006407210070478619</v>
       </c>
       <c r="M8" t="n">
-        <v>8.864374942495493</v>
+        <v>8.871761264719325</v>
       </c>
       <c r="N8" t="n">
-        <v>119.8111316990274</v>
+        <v>119.9239439333175</v>
       </c>
       <c r="O8" t="n">
-        <v>10.94582713635783</v>
+        <v>10.95097913126116</v>
       </c>
       <c r="P8" t="n">
-        <v>329.9682152086139</v>
+        <v>329.8263425538996</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31019,28 +31199,28 @@
         <v>0.0388</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0750625354877007</v>
+        <v>0.07727040124439609</v>
       </c>
       <c r="J9" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K9" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001029354556194684</v>
+        <v>0.001102702659388055</v>
       </c>
       <c r="M9" t="n">
-        <v>12.53315948409934</v>
+        <v>12.47865091614227</v>
       </c>
       <c r="N9" t="n">
-        <v>299.3122745448739</v>
+        <v>297.6048739866424</v>
       </c>
       <c r="O9" t="n">
-        <v>17.30064376099554</v>
+        <v>17.25122818777383</v>
       </c>
       <c r="P9" t="n">
-        <v>332.6304991057406</v>
+        <v>332.6068066156169</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31097,28 +31277,28 @@
         <v>0.079</v>
       </c>
       <c r="I10" t="n">
-        <v>0.01885533985334655</v>
+        <v>0.0397794873460104</v>
       </c>
       <c r="J10" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K10" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L10" t="n">
-        <v>8.557616474536012e-05</v>
+        <v>0.0003815563682993961</v>
       </c>
       <c r="M10" t="n">
-        <v>12.72549395424962</v>
+        <v>12.7430380853873</v>
       </c>
       <c r="N10" t="n">
-        <v>224.9959695206583</v>
+        <v>225.7149271785667</v>
       </c>
       <c r="O10" t="n">
-        <v>14.99986565008695</v>
+        <v>15.02381200556525</v>
       </c>
       <c r="P10" t="n">
-        <v>320.4799059184159</v>
+        <v>320.2545218740213</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -31175,28 +31355,28 @@
         <v>0.0864</v>
       </c>
       <c r="I11" t="n">
-        <v>0.02924568872434567</v>
+        <v>0.05644559357088214</v>
       </c>
       <c r="J11" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K11" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0001690536634900708</v>
+        <v>0.0006284827800191461</v>
       </c>
       <c r="M11" t="n">
-        <v>13.69147137846594</v>
+        <v>13.74305166754922</v>
       </c>
       <c r="N11" t="n">
-        <v>275.2560762167038</v>
+        <v>277.1227711961828</v>
       </c>
       <c r="O11" t="n">
-        <v>16.5908431436351</v>
+        <v>16.6470048716333</v>
       </c>
       <c r="P11" t="n">
-        <v>314.9394140719605</v>
+        <v>314.6473756272438</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -31253,28 +31433,28 @@
         <v>0.06569999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3246275122503649</v>
+        <v>0.3379751688902792</v>
       </c>
       <c r="J12" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K12" t="n">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="L12" t="n">
-        <v>0.02572302465509224</v>
+        <v>0.02803035175884339</v>
       </c>
       <c r="M12" t="n">
-        <v>12.20217373673447</v>
+        <v>12.17707101994591</v>
       </c>
       <c r="N12" t="n">
-        <v>218.4871809209904</v>
+        <v>218.0013010138071</v>
       </c>
       <c r="O12" t="n">
-        <v>14.78131188091877</v>
+        <v>14.7648671180545</v>
       </c>
       <c r="P12" t="n">
-        <v>319.0547373786134</v>
+        <v>318.9123369035725</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -31331,28 +31511,28 @@
         <v>0.0371</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.5856113208203121</v>
+        <v>-0.6472776770182813</v>
       </c>
       <c r="J13" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K13" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L13" t="n">
-        <v>0.01748604652719388</v>
+        <v>0.02109972845757613</v>
       </c>
       <c r="M13" t="n">
-        <v>27.6709883755523</v>
+        <v>27.91236248359282</v>
       </c>
       <c r="N13" t="n">
-        <v>1081.319203712007</v>
+        <v>1093.716928039381</v>
       </c>
       <c r="O13" t="n">
-        <v>32.8834183702365</v>
+        <v>33.07139138348099</v>
       </c>
       <c r="P13" t="n">
-        <v>319.2625321546589</v>
+        <v>319.9101949400133</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -31409,28 +31589,28 @@
         <v>0.07920000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3401502383521556</v>
+        <v>-0.3088728179507879</v>
       </c>
       <c r="J14" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K14" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="L14" t="n">
-        <v>0.01367368190494445</v>
+        <v>0.01132182037095553</v>
       </c>
       <c r="M14" t="n">
-        <v>18.32409393053389</v>
+        <v>18.380393445332</v>
       </c>
       <c r="N14" t="n">
-        <v>457.10172305035</v>
+        <v>458.6856445760816</v>
       </c>
       <c r="O14" t="n">
-        <v>21.3799373958473</v>
+        <v>21.41694760174945</v>
       </c>
       <c r="P14" t="n">
-        <v>305.9039913861193</v>
+        <v>305.5699187812032</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -31487,28 +31667,28 @@
         <v>0.1073</v>
       </c>
       <c r="I15" t="n">
-        <v>0.06846844374700856</v>
+        <v>0.09075272591731832</v>
       </c>
       <c r="J15" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K15" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0007221830401575868</v>
+        <v>0.00127384333249192</v>
       </c>
       <c r="M15" t="n">
-        <v>16.12296887408135</v>
+        <v>16.13899183525991</v>
       </c>
       <c r="N15" t="n">
-        <v>355.8524954252642</v>
+        <v>356.0928158073468</v>
       </c>
       <c r="O15" t="n">
-        <v>18.86405299571818</v>
+        <v>18.87042171779282</v>
       </c>
       <c r="P15" t="n">
-        <v>304.7204742940602</v>
+        <v>304.4824877580093</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -31565,28 +31745,28 @@
         <v>0.0534</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2148565054806402</v>
+        <v>0.2381907397212718</v>
       </c>
       <c r="J16" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K16" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="L16" t="n">
-        <v>0.004168219644010374</v>
+        <v>0.005153960147187719</v>
       </c>
       <c r="M16" t="n">
-        <v>20.05035899211038</v>
+        <v>20.03657145775754</v>
       </c>
       <c r="N16" t="n">
-        <v>596.3761693334725</v>
+        <v>595.2631833325689</v>
       </c>
       <c r="O16" t="n">
-        <v>24.42081426434165</v>
+        <v>24.39801597123358</v>
       </c>
       <c r="P16" t="n">
-        <v>315.0947362148835</v>
+        <v>314.8428424814537</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -31643,28 +31823,28 @@
         <v>0.0428</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.7865341205621761</v>
+        <v>-0.7600153171284127</v>
       </c>
       <c r="J17" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K17" t="n">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="L17" t="n">
-        <v>0.04817849776606431</v>
+        <v>0.04544342994891271</v>
       </c>
       <c r="M17" t="n">
-        <v>21.2571147935812</v>
+        <v>21.28507346980935</v>
       </c>
       <c r="N17" t="n">
-        <v>660.0963885108964</v>
+        <v>658.9280474921851</v>
       </c>
       <c r="O17" t="n">
-        <v>25.69234104769156</v>
+        <v>25.66959383185065</v>
       </c>
       <c r="P17" t="n">
-        <v>331.0069856021888</v>
+        <v>330.7204940291329</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -31721,28 +31901,28 @@
         <v>0.0478</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1164058505437965</v>
+        <v>-0.1085309366708465</v>
       </c>
       <c r="J18" t="n">
+        <v>329</v>
+      </c>
+      <c r="K18" t="n">
         <v>327</v>
       </c>
-      <c r="K18" t="n">
-        <v>325</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.00614038205585099</v>
+        <v>0.005389914090988102</v>
       </c>
       <c r="M18" t="n">
-        <v>8.581574631069861</v>
+        <v>8.557520296520773</v>
       </c>
       <c r="N18" t="n">
-        <v>118.4098746719034</v>
+        <v>117.9776972582628</v>
       </c>
       <c r="O18" t="n">
-        <v>10.88163014772618</v>
+        <v>10.86175387579109</v>
       </c>
       <c r="P18" t="n">
-        <v>326.7372077951153</v>
+        <v>326.6524178791977</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -31799,28 +31979,28 @@
         <v>0.0415</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2029934795747081</v>
+        <v>0.2086003970985649</v>
       </c>
       <c r="J19" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K19" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="L19" t="n">
-        <v>0.03035276820243293</v>
+        <v>0.03228846378228911</v>
       </c>
       <c r="M19" t="n">
-        <v>6.39388436385371</v>
+        <v>6.380022063309164</v>
       </c>
       <c r="N19" t="n">
-        <v>71.6835840725268</v>
+        <v>71.39630124462941</v>
       </c>
       <c r="O19" t="n">
-        <v>8.466615857148994</v>
+        <v>8.449633201780383</v>
       </c>
       <c r="P19" t="n">
-        <v>345.9884909211298</v>
+        <v>345.9284919181556</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -31877,28 +32057,28 @@
         <v>0.0344</v>
       </c>
       <c r="I20" t="n">
-        <v>0.04360802802773028</v>
+        <v>0.05149185025473817</v>
       </c>
       <c r="J20" t="n">
+        <v>329</v>
+      </c>
+      <c r="K20" t="n">
         <v>327</v>
       </c>
-      <c r="K20" t="n">
-        <v>325</v>
-      </c>
       <c r="L20" t="n">
-        <v>0.001270666637519846</v>
+        <v>0.001784500884545737</v>
       </c>
       <c r="M20" t="n">
-        <v>7.022456413532455</v>
+        <v>7.02898830660885</v>
       </c>
       <c r="N20" t="n">
-        <v>81.55712224223582</v>
+        <v>81.3557396734432</v>
       </c>
       <c r="O20" t="n">
-        <v>9.030898196870332</v>
+        <v>9.01974166334287</v>
       </c>
       <c r="P20" t="n">
-        <v>344.8410894933156</v>
+        <v>344.7567600070831</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -31955,28 +32135,28 @@
         <v>0.0304</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2344989120212837</v>
+        <v>0.255202813869299</v>
       </c>
       <c r="J21" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K21" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L21" t="n">
-        <v>0.01362481971588347</v>
+        <v>0.01612798085823597</v>
       </c>
       <c r="M21" t="n">
-        <v>11.83821461279968</v>
+        <v>11.88160398093726</v>
       </c>
       <c r="N21" t="n">
-        <v>215.4681214366449</v>
+        <v>216.1725520226526</v>
       </c>
       <c r="O21" t="n">
-        <v>14.67883242756878</v>
+        <v>14.70280762380616</v>
       </c>
       <c r="P21" t="n">
-        <v>322.0740887749316</v>
+        <v>321.8511157213996</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -32033,28 +32213,28 @@
         <v>0.0447</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2636155615656641</v>
+        <v>0.300282379862838</v>
       </c>
       <c r="J22" t="n">
+        <v>329</v>
+      </c>
+      <c r="K22" t="n">
         <v>327</v>
       </c>
-      <c r="K22" t="n">
-        <v>325</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.01112682065697324</v>
+        <v>0.01428154301168372</v>
       </c>
       <c r="M22" t="n">
-        <v>14.68222142782557</v>
+        <v>14.79242661690647</v>
       </c>
       <c r="N22" t="n">
-        <v>337.6166449732079</v>
+        <v>342.01281472252</v>
       </c>
       <c r="O22" t="n">
-        <v>18.37434747067791</v>
+        <v>18.49358847607786</v>
       </c>
       <c r="P22" t="n">
-        <v>303.3835884708138</v>
+        <v>302.9919181248493</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -32111,28 +32291,28 @@
         <v>0.0592</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4849875166497327</v>
+        <v>0.485547820183362</v>
       </c>
       <c r="J23" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K23" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="L23" t="n">
-        <v>0.11196042730662</v>
+        <v>0.1133320575416684</v>
       </c>
       <c r="M23" t="n">
-        <v>7.891312812497173</v>
+        <v>7.845376886554292</v>
       </c>
       <c r="N23" t="n">
-        <v>101.5942131119454</v>
+        <v>100.9762334310566</v>
       </c>
       <c r="O23" t="n">
-        <v>10.07939547353637</v>
+        <v>10.04869312055337</v>
       </c>
       <c r="P23" t="n">
-        <v>323.163775032743</v>
+        <v>323.1577798489255</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -32189,28 +32369,28 @@
         <v>0.07870000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1585886282937093</v>
+        <v>0.1574321786908237</v>
       </c>
       <c r="J24" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K24" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="L24" t="n">
-        <v>0.04208719989273391</v>
+        <v>0.04194965288522678</v>
       </c>
       <c r="M24" t="n">
-        <v>3.968187150031667</v>
+        <v>3.951009860261259</v>
       </c>
       <c r="N24" t="n">
-        <v>31.09417715959248</v>
+        <v>30.91123519509402</v>
       </c>
       <c r="O24" t="n">
-        <v>5.576215307858233</v>
+        <v>5.559787333621136</v>
       </c>
       <c r="P24" t="n">
-        <v>340.0845901797721</v>
+        <v>340.0969806623947</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -32252,7 +32432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y328"/>
+  <dimension ref="A1:Y330"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73132,7 +73312,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>-38.5770748100028,174.63050968427146</t>
+          <t>-38.577082210966914,174.6308961335507</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
@@ -73219,7 +73399,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>-38.582666904061725,174.6293589736675</t>
+          <t>-38.582674128896585,174.6295746871416</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
@@ -73259,17 +73439,17 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>-38.57706897271154,174.63020493094453</t>
+          <t>-38.57708302613748,174.630938702639</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
         <is>
-          <t>-38.57636295370669,174.62998859325222</t>
+          <t>-38.57636494903468,174.63008106657225</t>
         </is>
       </c>
       <c r="O328" t="inlineStr">
         <is>
-          <t>-38.57566300930754,174.63010733302897</t>
+          <t>-38.57566447233997,174.63017513848902</t>
         </is>
       </c>
       <c r="P328" t="inlineStr">
@@ -73320,6 +73500,256 @@
       <c r="Y328" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:06:25+00:00</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>-38.58477794868127,174.62945831774206</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>-38.584075029999184,174.6294705780898</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>-38.58337904634685,174.6296255887427</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>-38.582674128896585,174.6295746871416</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>-38.58197765167726,174.6300765479835</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>-38.58127138467683,174.6299470578538</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>-38.580569849349054,174.62983215093155</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>-38.5798668456626,174.62996608257555</t>
+        </is>
+      </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>-38.57916494741467,174.62991063169375</t>
+        </is>
+      </c>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>-38.57846270590319,174.62991245450672</t>
+        </is>
+      </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>-38.57776298059605,174.62993472067797</t>
+        </is>
+      </c>
+      <c r="M329" t="inlineStr"/>
+      <c r="N329" t="inlineStr">
+        <is>
+          <t>-38.57636494903468,174.63008106657225</t>
+        </is>
+      </c>
+      <c r="O329" t="inlineStr">
+        <is>
+          <t>-38.575662959796446,174.63010503842798</t>
+        </is>
+      </c>
+      <c r="P329" t="inlineStr">
+        <is>
+          <t>-38.57495837667669,174.63000911877128</t>
+        </is>
+      </c>
+      <c r="Q329" t="inlineStr">
+        <is>
+          <t>-38.5742632608706,174.63016562994713</t>
+        </is>
+      </c>
+      <c r="R329" t="inlineStr">
+        <is>
+          <t>-38.573568042129914,174.63023131923606</t>
+        </is>
+      </c>
+      <c r="S329" t="inlineStr">
+        <is>
+          <t>-38.57285283950762,174.63001423368135</t>
+        </is>
+      </c>
+      <c r="T329" t="inlineStr">
+        <is>
+          <t>-38.57215482579889,174.6301281083171</t>
+        </is>
+      </c>
+      <c r="U329" t="inlineStr">
+        <is>
+          <t>-38.57145529965364,174.63025350277476</t>
+        </is>
+      </c>
+      <c r="V329" t="inlineStr">
+        <is>
+          <t>-38.570753294748975,174.63035222369496</t>
+        </is>
+      </c>
+      <c r="W329" t="inlineStr">
+        <is>
+          <t>-38.570052909151656,174.63043444670433</t>
+        </is>
+      </c>
+      <c r="X329" t="inlineStr">
+        <is>
+          <t>-38.56935006749448,174.6303955360845</t>
+        </is>
+      </c>
+      <c r="Y329" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:06:21+00:00</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>-38.58478013820443,174.62950334306439</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>-38.58407354244258,174.6294399886673</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>-38.58337767581644,174.62959740550113</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>-38.582674128896585,174.6295746871416</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>-38.58197720258257,174.6300045810421</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>-38.58127126669127,174.62996714419677</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>-38.58056997472226,174.629810802225</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>-38.57986742001495,174.62986829268308</t>
+        </is>
+      </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>-38.57916522513235,174.62986334408356</t>
+        </is>
+      </c>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>-38.57846300855207,174.62986092069562</t>
+        </is>
+      </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>-38.57776258977076,174.62986275738925</t>
+        </is>
+      </c>
+      <c r="M330" t="inlineStr">
+        <is>
+          <t>-38.577073056261625,174.63041812058142</t>
+        </is>
+      </c>
+      <c r="N330" t="inlineStr">
+        <is>
+          <t>-38.57636494160804,174.63008072237875</t>
+        </is>
+      </c>
+      <c r="O330" t="inlineStr">
+        <is>
+          <t>-38.57566321972918,174.6301170850832</t>
+        </is>
+      </c>
+      <c r="P330" t="inlineStr">
+        <is>
+          <t>-38.57495836182261,174.63000843039774</t>
+        </is>
+      </c>
+      <c r="Q330" t="inlineStr">
+        <is>
+          <t>-38.57426181797235,174.63012469789356</t>
+        </is>
+      </c>
+      <c r="R330" t="inlineStr">
+        <is>
+          <t>-38.5735681083022,174.63023257888935</t>
+        </is>
+      </c>
+      <c r="S330" t="inlineStr">
+        <is>
+          <t>-38.57285267247005,174.63001125728545</t>
+        </is>
+      </c>
+      <c r="T330" t="inlineStr">
+        <is>
+          <t>-38.5721545433392,174.63012226622865</t>
+        </is>
+      </c>
+      <c r="U330" t="inlineStr">
+        <is>
+          <t>-38.57145547939941,174.63025969594455</t>
+        </is>
+      </c>
+      <c r="V330" t="inlineStr">
+        <is>
+          <t>-38.57075244046169,174.63030334567884</t>
+        </is>
+      </c>
+      <c r="W330" t="inlineStr">
+        <is>
+          <t>-38.570052909151656,174.63043444670433</t>
+        </is>
+      </c>
+      <c r="X330" t="inlineStr">
+        <is>
+          <t>-38.56934994555443,174.6303902592571</t>
+        </is>
+      </c>
+      <c r="Y330" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>

--- a/data/nzd0264/nzd0264.xlsx
+++ b/data/nzd0264/nzd0264.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y330"/>
+  <dimension ref="A1:Y331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26686,7 +26686,7 @@
         <v>350.51</v>
       </c>
       <c r="E328" t="n">
-        <v>362.63</v>
+        <v>381.44</v>
       </c>
       <c r="F328" t="n">
         <v>314.48</v>
@@ -26767,7 +26767,7 @@
         <v>352.41</v>
       </c>
       <c r="E329" t="n">
-        <v>362.63</v>
+        <v>381.44</v>
       </c>
       <c r="F329" t="n">
         <v>321.67</v>
@@ -26846,7 +26846,7 @@
         <v>354.87</v>
       </c>
       <c r="E330" t="n">
-        <v>362.63</v>
+        <v>381.44</v>
       </c>
       <c r="F330" t="n">
         <v>327.94</v>
@@ -26869,9 +26869,7 @@
       <c r="L330" t="n">
         <v>342.27</v>
       </c>
-      <c r="M330" t="n">
-        <v>296.44</v>
-      </c>
+      <c r="M330" t="inlineStr"/>
       <c r="N330" t="n">
         <v>328.91</v>
       </c>
@@ -26906,6 +26904,87 @@
         <v>343.44</v>
       </c>
       <c r="Y330" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:11+00:00</t>
+        </is>
+      </c>
+      <c r="B331" t="n">
+        <v>346.01</v>
+      </c>
+      <c r="C331" t="n">
+        <v>353.55</v>
+      </c>
+      <c r="D331" t="n">
+        <v>345.1</v>
+      </c>
+      <c r="E331" t="n">
+        <v>360.37</v>
+      </c>
+      <c r="F331" t="n">
+        <v>331.51</v>
+      </c>
+      <c r="G331" t="n">
+        <v>331.56</v>
+      </c>
+      <c r="H331" t="n">
+        <v>339.43</v>
+      </c>
+      <c r="I331" t="n">
+        <v>338.45</v>
+      </c>
+      <c r="J331" t="n">
+        <v>341.57</v>
+      </c>
+      <c r="K331" t="n">
+        <v>342.11</v>
+      </c>
+      <c r="L331" t="n">
+        <v>342.27</v>
+      </c>
+      <c r="M331" t="n">
+        <v>193.58</v>
+      </c>
+      <c r="N331" t="n">
+        <v>328.91</v>
+      </c>
+      <c r="O331" t="n">
+        <v>328.81</v>
+      </c>
+      <c r="P331" t="n">
+        <v>341.35</v>
+      </c>
+      <c r="Q331" t="n">
+        <v>334.26</v>
+      </c>
+      <c r="R331" t="n">
+        <v>323.72</v>
+      </c>
+      <c r="S331" t="n">
+        <v>355.22</v>
+      </c>
+      <c r="T331" t="n">
+        <v>352.58</v>
+      </c>
+      <c r="U331" t="n">
+        <v>343.23</v>
+      </c>
+      <c r="V331" t="n">
+        <v>344.38</v>
+      </c>
+      <c r="W331" t="n">
+        <v>337.55</v>
+      </c>
+      <c r="X331" t="n">
+        <v>342.48</v>
+      </c>
+      <c r="Y331" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -26922,7 +27001,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B356"/>
+  <dimension ref="A1:B358"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30485,6 +30564,26 @@
       </c>
       <c r="B356" t="n">
         <v>0.59</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>-0.02</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B358" t="n">
+        <v>-0.8</v>
       </c>
     </row>
   </sheetData>
@@ -30653,28 +30752,28 @@
         <v>0.0285</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7904123504587963</v>
+        <v>0.7843887259359231</v>
       </c>
       <c r="J2" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K2" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1284471300315616</v>
+        <v>0.1272122188015343</v>
       </c>
       <c r="M2" t="n">
-        <v>12.03816779468545</v>
+        <v>12.03049750768487</v>
       </c>
       <c r="N2" t="n">
-        <v>229.960208014923</v>
+        <v>229.5899223599634</v>
       </c>
       <c r="O2" t="n">
-        <v>15.16443892845769</v>
+        <v>15.15222499700831</v>
       </c>
       <c r="P2" t="n">
-        <v>335.770000961288</v>
+        <v>335.8356397947072</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -30731,28 +30830,28 @@
         <v>0.0381</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1972923688251657</v>
+        <v>-0.1859406702703228</v>
       </c>
       <c r="J3" t="n">
+        <v>330</v>
+      </c>
+      <c r="K3" t="n">
         <v>329</v>
       </c>
-      <c r="K3" t="n">
-        <v>328</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.00728045300742397</v>
+        <v>0.006481816808566521</v>
       </c>
       <c r="M3" t="n">
-        <v>12.04516506190174</v>
+        <v>12.05295315414089</v>
       </c>
       <c r="N3" t="n">
-        <v>290.5598889671264</v>
+        <v>290.9037111884492</v>
       </c>
       <c r="O3" t="n">
-        <v>17.04581734523535</v>
+        <v>17.05589960067921</v>
       </c>
       <c r="P3" t="n">
-        <v>338.5664014217335</v>
+        <v>338.4442035165723</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30809,28 +30908,28 @@
         <v>0.0304</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1380320567541286</v>
+        <v>-0.1306764991197747</v>
       </c>
       <c r="J4" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K4" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003104238146790284</v>
+        <v>0.002794803153959413</v>
       </c>
       <c r="M4" t="n">
-        <v>13.36412734337432</v>
+        <v>13.35157905671521</v>
       </c>
       <c r="N4" t="n">
-        <v>332.9591317710947</v>
+        <v>332.4499713680667</v>
       </c>
       <c r="O4" t="n">
-        <v>18.24716777396138</v>
+        <v>18.23321067086284</v>
       </c>
       <c r="P4" t="n">
-        <v>335.7600900305516</v>
+        <v>335.6804011773315</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30887,28 +30986,28 @@
         <v>0.0232</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8015344156999429</v>
+        <v>0.8433629985661067</v>
       </c>
       <c r="J5" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K5" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06453845725402974</v>
+        <v>0.07003551484977344</v>
       </c>
       <c r="M5" t="n">
-        <v>18.21479615818003</v>
+        <v>18.39376667094616</v>
       </c>
       <c r="N5" t="n">
-        <v>508.6255746975105</v>
+        <v>517.2676275517301</v>
       </c>
       <c r="O5" t="n">
-        <v>22.55272876388821</v>
+        <v>22.74351836351909</v>
       </c>
       <c r="P5" t="n">
-        <v>324.478810597234</v>
+        <v>324.0281179009735</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30965,28 +31064,28 @@
         <v>0.0304</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3078528930755969</v>
+        <v>0.3160226272160206</v>
       </c>
       <c r="J6" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K6" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L6" t="n">
-        <v>0.007108334000166083</v>
+        <v>0.007523936882808946</v>
       </c>
       <c r="M6" t="n">
-        <v>19.46274237349777</v>
+        <v>19.43204008148205</v>
       </c>
       <c r="N6" t="n">
-        <v>722.1181689157377</v>
+        <v>720.5375096529531</v>
       </c>
       <c r="O6" t="n">
-        <v>26.8722564909562</v>
+        <v>26.84282976239564</v>
       </c>
       <c r="P6" t="n">
-        <v>308.9635977768219</v>
+        <v>308.8752094953468</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31043,28 +31142,28 @@
         <v>0.0311</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04859904192945898</v>
+        <v>0.05259322997715953</v>
       </c>
       <c r="J7" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K7" t="n">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0002822733293822433</v>
+        <v>0.0003323828951382612</v>
       </c>
       <c r="M7" t="n">
-        <v>15.68226247899865</v>
+        <v>15.64544171433435</v>
       </c>
       <c r="N7" t="n">
-        <v>456.1585956874996</v>
+        <v>454.9000729403571</v>
       </c>
       <c r="O7" t="n">
-        <v>21.35786964300278</v>
+        <v>21.32838655267569</v>
       </c>
       <c r="P7" t="n">
-        <v>323.2901363469001</v>
+        <v>323.2469960722974</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31121,28 +31220,28 @@
         <v>0.0451</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1187357190217746</v>
+        <v>0.1223786390808533</v>
       </c>
       <c r="J8" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K8" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L8" t="n">
-        <v>0.006407210070478619</v>
+        <v>0.006835377397539921</v>
       </c>
       <c r="M8" t="n">
-        <v>8.871761264719325</v>
+        <v>8.861885390809041</v>
       </c>
       <c r="N8" t="n">
-        <v>119.9239439333175</v>
+        <v>119.6851301424734</v>
       </c>
       <c r="O8" t="n">
-        <v>10.95097913126116</v>
+        <v>10.94006993316192</v>
       </c>
       <c r="P8" t="n">
-        <v>329.8263425538996</v>
+        <v>329.7871430964293</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31199,28 +31298,28 @@
         <v>0.0388</v>
       </c>
       <c r="I9" t="n">
-        <v>0.07727040124439609</v>
+        <v>0.07941057194025056</v>
       </c>
       <c r="J9" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K9" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001102702659388055</v>
+        <v>0.001171063789798477</v>
       </c>
       <c r="M9" t="n">
-        <v>12.47865091614227</v>
+        <v>12.44850246957778</v>
       </c>
       <c r="N9" t="n">
-        <v>297.6048739866424</v>
+        <v>296.7359950499658</v>
       </c>
       <c r="O9" t="n">
-        <v>17.25122818777383</v>
+        <v>17.22602667622356</v>
       </c>
       <c r="P9" t="n">
-        <v>332.6068066156169</v>
+        <v>332.5837843028216</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31277,28 +31376,28 @@
         <v>0.079</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0397794873460104</v>
+        <v>0.05125045722078002</v>
       </c>
       <c r="J10" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K10" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0003815563682993961</v>
+        <v>0.0006333062693846259</v>
       </c>
       <c r="M10" t="n">
-        <v>12.7430380853873</v>
+        <v>12.75648646760966</v>
       </c>
       <c r="N10" t="n">
-        <v>225.7149271785667</v>
+        <v>226.2713755679221</v>
       </c>
       <c r="O10" t="n">
-        <v>15.02381200556525</v>
+        <v>15.04231948762963</v>
       </c>
       <c r="P10" t="n">
-        <v>320.2545218740213</v>
+        <v>320.1302395706743</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -31355,28 +31454,28 @@
         <v>0.0864</v>
       </c>
       <c r="I11" t="n">
-        <v>0.05644559357088214</v>
+        <v>0.0711121703046038</v>
       </c>
       <c r="J11" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K11" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0006284827800191461</v>
+        <v>0.0009954892248996705</v>
       </c>
       <c r="M11" t="n">
-        <v>13.74305166754922</v>
+        <v>13.77319799597622</v>
       </c>
       <c r="N11" t="n">
-        <v>277.1227711961828</v>
+        <v>278.325074280167</v>
       </c>
       <c r="O11" t="n">
-        <v>16.6470048716333</v>
+        <v>16.68307748229226</v>
       </c>
       <c r="P11" t="n">
-        <v>314.6473756272438</v>
+        <v>314.4889746236269</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -31433,28 +31532,28 @@
         <v>0.06569999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3379751688902792</v>
+        <v>0.3463291238009689</v>
       </c>
       <c r="J12" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K12" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L12" t="n">
-        <v>0.02803035175884339</v>
+        <v>0.02947572553990674</v>
       </c>
       <c r="M12" t="n">
-        <v>12.17707101994591</v>
+        <v>12.17083224534157</v>
       </c>
       <c r="N12" t="n">
-        <v>218.0013010138071</v>
+        <v>217.9670788269424</v>
       </c>
       <c r="O12" t="n">
-        <v>14.7648671180545</v>
+        <v>14.76370816654618</v>
       </c>
       <c r="P12" t="n">
-        <v>318.9123369035725</v>
+        <v>318.8227140956364</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -31511,28 +31610,28 @@
         <v>0.0371</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.6472776770182813</v>
+        <v>-0.7089891997958259</v>
       </c>
       <c r="J13" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K13" t="n">
         <v>301</v>
       </c>
       <c r="L13" t="n">
-        <v>0.02109972845757613</v>
+        <v>0.0243598308236781</v>
       </c>
       <c r="M13" t="n">
-        <v>27.91236248359282</v>
+        <v>28.32494005364564</v>
       </c>
       <c r="N13" t="n">
-        <v>1093.716928039381</v>
+        <v>1132.927707513448</v>
       </c>
       <c r="O13" t="n">
-        <v>33.07139138348099</v>
+        <v>33.65899148093193</v>
       </c>
       <c r="P13" t="n">
-        <v>319.9101949400133</v>
+        <v>320.566207297366</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -31589,28 +31688,28 @@
         <v>0.07920000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3088728179507879</v>
+        <v>-0.2911839502528341</v>
       </c>
       <c r="J14" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K14" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L14" t="n">
-        <v>0.01132182037095553</v>
+        <v>0.01006682603098008</v>
       </c>
       <c r="M14" t="n">
-        <v>18.380393445332</v>
+        <v>18.41825491332279</v>
       </c>
       <c r="N14" t="n">
-        <v>458.6856445760816</v>
+        <v>460.2849947595017</v>
       </c>
       <c r="O14" t="n">
-        <v>21.41694760174945</v>
+        <v>21.45425353535988</v>
       </c>
       <c r="P14" t="n">
-        <v>305.5699187812032</v>
+        <v>305.3799455234942</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -31667,28 +31766,28 @@
         <v>0.1073</v>
       </c>
       <c r="I15" t="n">
-        <v>0.09075272591731832</v>
+        <v>0.1030838291722908</v>
       </c>
       <c r="J15" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K15" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L15" t="n">
-        <v>0.00127384333249192</v>
+        <v>0.001645568206214532</v>
       </c>
       <c r="M15" t="n">
-        <v>16.13899183525991</v>
+        <v>16.15258539099318</v>
       </c>
       <c r="N15" t="n">
-        <v>356.0928158073468</v>
+        <v>356.4644469543722</v>
       </c>
       <c r="O15" t="n">
-        <v>18.87042171779282</v>
+        <v>18.88026607212865</v>
       </c>
       <c r="P15" t="n">
-        <v>304.4824877580093</v>
+        <v>304.3500648802242</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -31745,28 +31844,28 @@
         <v>0.0534</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2381907397212718</v>
+        <v>0.2496902119662423</v>
       </c>
       <c r="J16" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K16" t="n">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="L16" t="n">
-        <v>0.005153960147187719</v>
+        <v>0.005681213414942654</v>
       </c>
       <c r="M16" t="n">
-        <v>20.03657145775754</v>
+        <v>20.02957951224212</v>
       </c>
       <c r="N16" t="n">
-        <v>595.2631833325689</v>
+        <v>594.6781299963186</v>
       </c>
       <c r="O16" t="n">
-        <v>24.39801597123358</v>
+        <v>24.38602325095912</v>
       </c>
       <c r="P16" t="n">
-        <v>314.8428424814537</v>
+        <v>314.7179536880367</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -31823,28 +31922,28 @@
         <v>0.0428</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.7600153171284127</v>
+        <v>-0.745838622137864</v>
       </c>
       <c r="J17" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K17" t="n">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L17" t="n">
-        <v>0.04544342994891271</v>
+        <v>0.04397793850281939</v>
       </c>
       <c r="M17" t="n">
-        <v>21.28507346980935</v>
+        <v>21.30629244098428</v>
       </c>
       <c r="N17" t="n">
-        <v>658.9280474921851</v>
+        <v>658.5707923572706</v>
       </c>
       <c r="O17" t="n">
-        <v>25.66959383185065</v>
+        <v>25.66263416637642</v>
       </c>
       <c r="P17" t="n">
-        <v>330.7204940291329</v>
+        <v>330.5664324859937</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -31901,28 +32000,28 @@
         <v>0.0478</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1085309366708465</v>
+        <v>-0.1085744373902329</v>
       </c>
       <c r="J18" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K18" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L18" t="n">
-        <v>0.005389914090988102</v>
+        <v>0.005425232737982233</v>
       </c>
       <c r="M18" t="n">
-        <v>8.557520296520773</v>
+        <v>8.531740186100722</v>
       </c>
       <c r="N18" t="n">
-        <v>117.9776972582628</v>
+        <v>117.6180269683191</v>
       </c>
       <c r="O18" t="n">
-        <v>10.86175387579109</v>
+        <v>10.8451845059602</v>
       </c>
       <c r="P18" t="n">
-        <v>326.6524178791977</v>
+        <v>326.6528890576244</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -31979,28 +32078,28 @@
         <v>0.0415</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2086003970985649</v>
+        <v>0.2107377579235267</v>
       </c>
       <c r="J19" t="n">
+        <v>330</v>
+      </c>
+      <c r="K19" t="n">
         <v>329</v>
       </c>
-      <c r="K19" t="n">
-        <v>328</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.03228846378228911</v>
+        <v>0.03309563086311818</v>
       </c>
       <c r="M19" t="n">
-        <v>6.380022063309164</v>
+        <v>6.370046501635168</v>
       </c>
       <c r="N19" t="n">
-        <v>71.39630124462941</v>
+        <v>71.22278953488913</v>
       </c>
       <c r="O19" t="n">
-        <v>8.449633201780383</v>
+        <v>8.439359545302542</v>
       </c>
       <c r="P19" t="n">
-        <v>345.9284919181556</v>
+        <v>345.9054838181675</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -32057,28 +32156,28 @@
         <v>0.0344</v>
       </c>
       <c r="I20" t="n">
-        <v>0.05149185025473817</v>
+        <v>0.05512699457732225</v>
       </c>
       <c r="J20" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K20" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L20" t="n">
-        <v>0.001784500884545737</v>
+        <v>0.002053375973767091</v>
       </c>
       <c r="M20" t="n">
-        <v>7.02898830660885</v>
+        <v>7.030058282888604</v>
       </c>
       <c r="N20" t="n">
-        <v>81.3557396734432</v>
+        <v>81.2339711109436</v>
       </c>
       <c r="O20" t="n">
-        <v>9.01974166334287</v>
+        <v>9.012989022013929</v>
       </c>
       <c r="P20" t="n">
-        <v>344.7567600070831</v>
+        <v>344.717644220033</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -32135,28 +32234,28 @@
         <v>0.0304</v>
       </c>
       <c r="I21" t="n">
-        <v>0.255202813869299</v>
+        <v>0.263509356322192</v>
       </c>
       <c r="J21" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K21" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L21" t="n">
-        <v>0.01612798085823597</v>
+        <v>0.0172226470408432</v>
       </c>
       <c r="M21" t="n">
-        <v>11.88160398093726</v>
+        <v>11.89208682012445</v>
       </c>
       <c r="N21" t="n">
-        <v>216.1725520226526</v>
+        <v>216.1624720184477</v>
       </c>
       <c r="O21" t="n">
-        <v>14.70280762380616</v>
+        <v>14.7024648279956</v>
       </c>
       <c r="P21" t="n">
-        <v>321.8511157213996</v>
+        <v>321.7611162957457</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -32213,28 +32312,28 @@
         <v>0.0447</v>
       </c>
       <c r="I22" t="n">
-        <v>0.300282379862838</v>
+        <v>0.319095971736239</v>
       </c>
       <c r="J22" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K22" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L22" t="n">
-        <v>0.01428154301168372</v>
+        <v>0.01603196051432809</v>
       </c>
       <c r="M22" t="n">
-        <v>14.79242661690647</v>
+        <v>14.85036247384608</v>
       </c>
       <c r="N22" t="n">
-        <v>342.01281472252</v>
+        <v>344.3573246230708</v>
       </c>
       <c r="O22" t="n">
-        <v>18.49358847607786</v>
+        <v>18.55686731706272</v>
       </c>
       <c r="P22" t="n">
-        <v>302.9919181248493</v>
+        <v>302.7897610655216</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -32291,28 +32390,28 @@
         <v>0.0592</v>
       </c>
       <c r="I23" t="n">
-        <v>0.485547820183362</v>
+        <v>0.4864513668145602</v>
       </c>
       <c r="J23" t="n">
+        <v>330</v>
+      </c>
+      <c r="K23" t="n">
         <v>329</v>
       </c>
-      <c r="K23" t="n">
-        <v>328</v>
-      </c>
       <c r="L23" t="n">
-        <v>0.1133320575416684</v>
+        <v>0.1142790302328355</v>
       </c>
       <c r="M23" t="n">
-        <v>7.845376886554292</v>
+        <v>7.825007583569148</v>
       </c>
       <c r="N23" t="n">
-        <v>100.9762334310566</v>
+        <v>100.6770883130589</v>
       </c>
       <c r="O23" t="n">
-        <v>10.04869312055337</v>
+        <v>10.03379730276922</v>
       </c>
       <c r="P23" t="n">
-        <v>323.1577798489255</v>
+        <v>323.1480534185579</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -32369,28 +32468,28 @@
         <v>0.07870000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1574321786908237</v>
+        <v>0.1564379864328629</v>
       </c>
       <c r="J24" t="n">
+        <v>330</v>
+      </c>
+      <c r="K24" t="n">
         <v>329</v>
       </c>
-      <c r="K24" t="n">
-        <v>328</v>
-      </c>
       <c r="L24" t="n">
-        <v>0.04194965288522678</v>
+        <v>0.0416603655306591</v>
       </c>
       <c r="M24" t="n">
-        <v>3.951009860261259</v>
+        <v>3.944959802993712</v>
       </c>
       <c r="N24" t="n">
-        <v>30.91123519509402</v>
+        <v>30.82666146751688</v>
       </c>
       <c r="O24" t="n">
-        <v>5.559787333621136</v>
+        <v>5.552176282100279</v>
       </c>
       <c r="P24" t="n">
-        <v>340.0969806623947</v>
+        <v>340.1077003170607</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -32432,7 +32531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y330"/>
+  <dimension ref="A1:Y331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73399,7 +73498,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>-38.582674128896585,174.6295746871416</t>
+          <t>-38.582666904061725,174.6293589736675</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
@@ -73526,7 +73625,7 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>-38.582674128896585,174.6295746871416</t>
+          <t>-38.582666904061725,174.6293589736675</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
@@ -73649,7 +73748,7 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>-38.582674128896585,174.6295746871416</t>
+          <t>-38.582666904061725,174.6293589736675</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
@@ -73687,11 +73786,7 @@
           <t>-38.57776258977076,174.62986275738925</t>
         </is>
       </c>
-      <c r="M330" t="inlineStr">
-        <is>
-          <t>-38.577073056261625,174.63041812058142</t>
-        </is>
-      </c>
+      <c r="M330" t="inlineStr"/>
       <c r="N330" t="inlineStr">
         <is>
           <t>-38.57636494160804,174.63008072237875</t>
@@ -73748,6 +73843,133 @@
         </is>
       </c>
       <c r="Y330" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:11+00:00</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>-38.58478321910705,174.62956669931035</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>-38.58407871821357,174.6295464215311</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>-38.583383118899064,174.6297093365102</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>-38.5826749969254,174.6296006048709</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>-38.58197694685816,174.62996360464933</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>-38.581271268039686,174.6299669146386</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>-38.58056956623396,174.62988035768745</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>-38.57986726093023,174.62989538002466</t>
+        </is>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>-38.57916522513235,174.62986334408356</t>
+        </is>
+      </c>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>-38.57846300855207,174.62986092069562</t>
+        </is>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>-38.57776258977076,174.62986275738925</t>
+        </is>
+      </c>
+      <c r="M331" t="inlineStr">
+        <is>
+          <t>-38.57709565600294,174.63159835144864</t>
+        </is>
+      </c>
+      <c r="N331" t="inlineStr">
+        <is>
+          <t>-38.57636494160804,174.63008072237875</t>
+        </is>
+      </c>
+      <c r="O331" t="inlineStr">
+        <is>
+          <t>-38.57566321972918,174.6301170850832</t>
+        </is>
+      </c>
+      <c r="P331" t="inlineStr">
+        <is>
+          <t>-38.57495836182261,174.63000843039774</t>
+        </is>
+      </c>
+      <c r="Q331" t="inlineStr">
+        <is>
+          <t>-38.57426181797235,174.63012469789356</t>
+        </is>
+      </c>
+      <c r="R331" t="inlineStr">
+        <is>
+          <t>-38.5735722470506,174.6303113644804</t>
+        </is>
+      </c>
+      <c r="S331" t="inlineStr">
+        <is>
+          <t>-38.572853456261065,174.6300252234509</t>
+        </is>
+      </c>
+      <c r="T331" t="inlineStr">
+        <is>
+          <t>-38.572154925490494,174.6301301702307</t>
+        </is>
+      </c>
+      <c r="U331" t="inlineStr">
+        <is>
+          <t>-38.571456491295386,174.63029456119708</t>
+        </is>
+      </c>
+      <c r="V331" t="inlineStr">
+        <is>
+          <t>-38.57075259287124,174.63031206570045</t>
+        </is>
+      </c>
+      <c r="W331" t="inlineStr">
+        <is>
+          <t>-38.57005263444017,174.63042090902195</t>
+        </is>
+      </c>
+      <c r="X331" t="inlineStr">
+        <is>
+          <t>-38.569350200037746,174.6304012717665</t>
+        </is>
+      </c>
+      <c r="Y331" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0264/nzd0264.xlsx
+++ b/data/nzd0264/nzd0264.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y331"/>
+  <dimension ref="A1:Y333"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26943,7 +26943,7 @@
         <v>341.57</v>
       </c>
       <c r="K331" t="n">
-        <v>342.11</v>
+        <v>329.05</v>
       </c>
       <c r="L331" t="n">
         <v>342.27</v>
@@ -26987,6 +26987,168 @@
       <c r="Y331" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:53+00:00</t>
+        </is>
+      </c>
+      <c r="B332" t="n">
+        <v>346.01</v>
+      </c>
+      <c r="C332" t="n">
+        <v>353.55</v>
+      </c>
+      <c r="D332" t="n">
+        <v>345.1</v>
+      </c>
+      <c r="E332" t="n">
+        <v>360.37</v>
+      </c>
+      <c r="F332" t="n">
+        <v>331.51</v>
+      </c>
+      <c r="G332" t="n">
+        <v>331.56</v>
+      </c>
+      <c r="H332" t="n">
+        <v>339.43</v>
+      </c>
+      <c r="I332" t="n">
+        <v>338.45</v>
+      </c>
+      <c r="J332" t="n">
+        <v>341.57</v>
+      </c>
+      <c r="K332" t="n">
+        <v>329.05</v>
+      </c>
+      <c r="L332" t="n">
+        <v>342.27</v>
+      </c>
+      <c r="M332" t="n">
+        <v>193.58</v>
+      </c>
+      <c r="N332" t="n">
+        <v>333.06</v>
+      </c>
+      <c r="O332" t="n">
+        <v>333.52</v>
+      </c>
+      <c r="P332" t="n">
+        <v>346.86</v>
+      </c>
+      <c r="Q332" t="n">
+        <v>337.99</v>
+      </c>
+      <c r="R332" t="n">
+        <v>330.28</v>
+      </c>
+      <c r="S332" t="n">
+        <v>358.2</v>
+      </c>
+      <c r="T332" t="n">
+        <v>355.82</v>
+      </c>
+      <c r="U332" t="n">
+        <v>347.28</v>
+      </c>
+      <c r="V332" t="n">
+        <v>345.28</v>
+      </c>
+      <c r="W332" t="n">
+        <v>339.47</v>
+      </c>
+      <c r="X332" t="n">
+        <v>344.64</v>
+      </c>
+      <c r="Y332" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:32+00:00</t>
+        </is>
+      </c>
+      <c r="B333" t="n">
+        <v>348.68</v>
+      </c>
+      <c r="C333" t="n">
+        <v>341.96</v>
+      </c>
+      <c r="D333" t="n">
+        <v>333.86</v>
+      </c>
+      <c r="E333" t="n">
+        <v>343.52</v>
+      </c>
+      <c r="F333" t="n">
+        <v>329.5</v>
+      </c>
+      <c r="G333" t="n">
+        <v>335.64</v>
+      </c>
+      <c r="H333" t="n">
+        <v>334.88</v>
+      </c>
+      <c r="I333" t="n">
+        <v>333.4</v>
+      </c>
+      <c r="J333" t="n">
+        <v>331.26</v>
+      </c>
+      <c r="K333" t="n">
+        <v>322.59</v>
+      </c>
+      <c r="L333" t="n">
+        <v>341.3</v>
+      </c>
+      <c r="M333" t="n">
+        <v>193.58</v>
+      </c>
+      <c r="N333" t="n">
+        <v>327.78</v>
+      </c>
+      <c r="O333" t="n">
+        <v>329.82</v>
+      </c>
+      <c r="P333" t="n">
+        <v>346.86</v>
+      </c>
+      <c r="Q333" t="n">
+        <v>337.99</v>
+      </c>
+      <c r="R333" t="n">
+        <v>327.79</v>
+      </c>
+      <c r="S333" t="n">
+        <v>356.62</v>
+      </c>
+      <c r="T333" t="n">
+        <v>356.45</v>
+      </c>
+      <c r="U333" t="n">
+        <v>347.68</v>
+      </c>
+      <c r="V333" t="n">
+        <v>342.48</v>
+      </c>
+      <c r="W333" t="n">
+        <v>340.34</v>
+      </c>
+      <c r="X333" t="n">
+        <v>345.69</v>
+      </c>
+      <c r="Y333" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -27001,7 +27163,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B358"/>
+  <dimension ref="A1:B360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30584,6 +30746,26 @@
       </c>
       <c r="B358" t="n">
         <v>-0.8</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B359" t="n">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B360" t="n">
+        <v>1.65</v>
       </c>
     </row>
   </sheetData>
@@ -30752,28 +30934,28 @@
         <v>0.0285</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7843887259359231</v>
+        <v>0.7740698646335652</v>
       </c>
       <c r="J2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="K2" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1272122188015343</v>
+        <v>0.1252899316090117</v>
       </c>
       <c r="M2" t="n">
-        <v>12.03049750768487</v>
+        <v>12.00801509141708</v>
       </c>
       <c r="N2" t="n">
-        <v>229.5899223599634</v>
+        <v>228.6941084839017</v>
       </c>
       <c r="O2" t="n">
-        <v>15.15222499700831</v>
+        <v>15.12263563284858</v>
       </c>
       <c r="P2" t="n">
-        <v>335.8356397947072</v>
+        <v>335.948311213075</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -30830,28 +31012,28 @@
         <v>0.0381</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1859406702703228</v>
+        <v>-0.1701687988758201</v>
       </c>
       <c r="J3" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="K3" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006481816808566521</v>
+        <v>0.005470108851110211</v>
       </c>
       <c r="M3" t="n">
-        <v>12.05295315414089</v>
+        <v>12.04186756695161</v>
       </c>
       <c r="N3" t="n">
-        <v>290.9037111884492</v>
+        <v>290.548789107948</v>
       </c>
       <c r="O3" t="n">
-        <v>17.05589960067921</v>
+        <v>17.04549175318647</v>
       </c>
       <c r="P3" t="n">
-        <v>338.4442035165723</v>
+        <v>338.2741333406353</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30908,28 +31090,28 @@
         <v>0.0304</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1306764991197747</v>
+        <v>-0.1225802744840191</v>
       </c>
       <c r="J4" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="K4" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002794803153959413</v>
+        <v>0.00248435122659918</v>
       </c>
       <c r="M4" t="n">
-        <v>13.35157905671521</v>
+        <v>13.30171485589694</v>
       </c>
       <c r="N4" t="n">
-        <v>332.4499713680667</v>
+        <v>330.9302247810836</v>
       </c>
       <c r="O4" t="n">
-        <v>18.23321067086284</v>
+        <v>18.19148770114978</v>
       </c>
       <c r="P4" t="n">
-        <v>335.6804011773315</v>
+        <v>335.5925730274101</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30986,28 +31168,28 @@
         <v>0.0232</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8433629985661067</v>
+        <v>0.8499932137429141</v>
       </c>
       <c r="J5" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="K5" t="n">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07003551484977344</v>
+        <v>0.07176423857920233</v>
       </c>
       <c r="M5" t="n">
-        <v>18.39376667094616</v>
+        <v>18.33163865075476</v>
       </c>
       <c r="N5" t="n">
-        <v>517.2676275517301</v>
+        <v>514.5941956101832</v>
       </c>
       <c r="O5" t="n">
-        <v>22.74351836351909</v>
+        <v>22.68466873485666</v>
       </c>
       <c r="P5" t="n">
-        <v>324.0281179009735</v>
+        <v>323.9562177803341</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31064,28 +31246,28 @@
         <v>0.0304</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3160226272160206</v>
+        <v>0.3308667970660835</v>
       </c>
       <c r="J6" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="K6" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="L6" t="n">
-        <v>0.007523936882808946</v>
+        <v>0.008322584444227066</v>
       </c>
       <c r="M6" t="n">
-        <v>19.43204008148205</v>
+        <v>19.36564823252137</v>
       </c>
       <c r="N6" t="n">
-        <v>720.5375096529531</v>
+        <v>717.2099621532218</v>
       </c>
       <c r="O6" t="n">
-        <v>26.84282976239564</v>
+        <v>26.78077598116272</v>
       </c>
       <c r="P6" t="n">
-        <v>308.8752094953468</v>
+        <v>308.7142757850499</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31142,28 +31324,28 @@
         <v>0.0311</v>
       </c>
       <c r="I7" t="n">
-        <v>0.05259322997715953</v>
+        <v>0.06271040060050351</v>
       </c>
       <c r="J7" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="K7" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0003323828951382612</v>
+        <v>0.0004774376417944204</v>
       </c>
       <c r="M7" t="n">
-        <v>15.64544171433435</v>
+        <v>15.57840322064501</v>
       </c>
       <c r="N7" t="n">
-        <v>454.9000729403571</v>
+        <v>452.619211651743</v>
       </c>
       <c r="O7" t="n">
-        <v>21.32838655267569</v>
+        <v>21.27484927447767</v>
       </c>
       <c r="P7" t="n">
-        <v>323.2469960722974</v>
+        <v>323.1374605038351</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31220,28 +31402,28 @@
         <v>0.0451</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1223786390808533</v>
+        <v>0.1269717702109469</v>
       </c>
       <c r="J8" t="n">
+        <v>332</v>
+      </c>
+      <c r="K8" t="n">
         <v>330</v>
       </c>
-      <c r="K8" t="n">
-        <v>328</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.006835377397539921</v>
+        <v>0.007429482175766444</v>
       </c>
       <c r="M8" t="n">
-        <v>8.861885390809041</v>
+        <v>8.829622224018978</v>
       </c>
       <c r="N8" t="n">
-        <v>119.6851301424734</v>
+        <v>119.093362550951</v>
       </c>
       <c r="O8" t="n">
-        <v>10.94006993316192</v>
+        <v>10.91299054113725</v>
       </c>
       <c r="P8" t="n">
-        <v>329.7871430964293</v>
+        <v>329.7376417191541</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31298,28 +31480,28 @@
         <v>0.0388</v>
       </c>
       <c r="I9" t="n">
-        <v>0.07941057194025056</v>
+        <v>0.08078780142399983</v>
       </c>
       <c r="J9" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="K9" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001171063789798477</v>
+        <v>0.001225597534299294</v>
       </c>
       <c r="M9" t="n">
-        <v>12.44850246957778</v>
+        <v>12.38572140367664</v>
       </c>
       <c r="N9" t="n">
-        <v>296.7359950499658</v>
+        <v>294.9747736624833</v>
       </c>
       <c r="O9" t="n">
-        <v>17.22602667622356</v>
+        <v>17.17482965454049</v>
       </c>
       <c r="P9" t="n">
-        <v>332.5837843028216</v>
+        <v>332.5689701234286</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31376,28 +31558,28 @@
         <v>0.079</v>
       </c>
       <c r="I10" t="n">
-        <v>0.05125045722078002</v>
+        <v>0.06791867032276451</v>
       </c>
       <c r="J10" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="K10" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0006333062693846259</v>
+        <v>0.001116967047869011</v>
       </c>
       <c r="M10" t="n">
-        <v>12.75648646760966</v>
+        <v>12.75454878823</v>
       </c>
       <c r="N10" t="n">
-        <v>226.2713755679221</v>
+        <v>226.3895265643494</v>
       </c>
       <c r="O10" t="n">
-        <v>15.04231948762963</v>
+        <v>15.04624626158795</v>
       </c>
       <c r="P10" t="n">
-        <v>320.1302395706743</v>
+        <v>319.9493250710732</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -31454,28 +31636,28 @@
         <v>0.0864</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0711121703046038</v>
+        <v>0.07439202869399429</v>
       </c>
       <c r="J11" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="K11" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0009954892248996705</v>
+        <v>0.001105450310231904</v>
       </c>
       <c r="M11" t="n">
-        <v>13.77319799597622</v>
+        <v>13.70509508403004</v>
       </c>
       <c r="N11" t="n">
-        <v>278.325074280167</v>
+        <v>275.7046932704367</v>
       </c>
       <c r="O11" t="n">
-        <v>16.68307748229226</v>
+        <v>16.60435765907362</v>
       </c>
       <c r="P11" t="n">
-        <v>314.4889746236269</v>
+        <v>314.4533443843117</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -31532,28 +31714,28 @@
         <v>0.06569999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3463291238009689</v>
+        <v>0.3620938384355314</v>
       </c>
       <c r="J12" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="K12" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L12" t="n">
-        <v>0.02947572553990674</v>
+        <v>0.03232929450054611</v>
       </c>
       <c r="M12" t="n">
-        <v>12.17083224534157</v>
+        <v>12.15494641913493</v>
       </c>
       <c r="N12" t="n">
-        <v>217.9670788269424</v>
+        <v>217.7807530229597</v>
       </c>
       <c r="O12" t="n">
-        <v>14.76370816654618</v>
+        <v>14.7573965530157</v>
       </c>
       <c r="P12" t="n">
-        <v>318.8227140956364</v>
+        <v>318.653227235775</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -31610,28 +31792,28 @@
         <v>0.0371</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.7089891997958259</v>
+        <v>-0.837061987867683</v>
       </c>
       <c r="J13" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="K13" t="n">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0243598308236781</v>
+        <v>0.03194680439834252</v>
       </c>
       <c r="M13" t="n">
-        <v>28.32494005364564</v>
+        <v>28.98535558135828</v>
       </c>
       <c r="N13" t="n">
-        <v>1132.927707513448</v>
+        <v>1201.413931802533</v>
       </c>
       <c r="O13" t="n">
-        <v>33.65899148093193</v>
+        <v>34.66141849091772</v>
       </c>
       <c r="P13" t="n">
-        <v>320.566207297366</v>
+        <v>321.9303183161761</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -31688,28 +31870,28 @@
         <v>0.07920000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2911839502528341</v>
+        <v>-0.2548863393770484</v>
       </c>
       <c r="J14" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="K14" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="L14" t="n">
-        <v>0.01006682603098008</v>
+        <v>0.007711729297097514</v>
       </c>
       <c r="M14" t="n">
-        <v>18.41825491332279</v>
+        <v>18.50151191652712</v>
       </c>
       <c r="N14" t="n">
-        <v>460.2849947595017</v>
+        <v>463.925214069102</v>
       </c>
       <c r="O14" t="n">
-        <v>21.45425353535988</v>
+        <v>21.53892323374365</v>
       </c>
       <c r="P14" t="n">
-        <v>305.3799455234942</v>
+        <v>304.98930556439</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -31766,28 +31948,28 @@
         <v>0.1073</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1030838291722908</v>
+        <v>0.1303714606471828</v>
       </c>
       <c r="J15" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="K15" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="L15" t="n">
-        <v>0.001645568206214532</v>
+        <v>0.002632391742170337</v>
       </c>
       <c r="M15" t="n">
-        <v>16.15258539099318</v>
+        <v>16.19446525149914</v>
       </c>
       <c r="N15" t="n">
-        <v>356.4644469543722</v>
+        <v>357.9389180616731</v>
       </c>
       <c r="O15" t="n">
-        <v>18.88026607212865</v>
+        <v>18.91927371919105</v>
       </c>
       <c r="P15" t="n">
-        <v>304.3500648802242</v>
+        <v>304.0564079851599</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -31844,28 +32026,28 @@
         <v>0.0534</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2496902119662423</v>
+        <v>0.2783615203830776</v>
       </c>
       <c r="J16" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="K16" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="L16" t="n">
-        <v>0.005681213414942654</v>
+        <v>0.007084342390225817</v>
       </c>
       <c r="M16" t="n">
-        <v>20.02957951224212</v>
+        <v>20.04245642255013</v>
       </c>
       <c r="N16" t="n">
-        <v>594.6781299963186</v>
+        <v>594.9668204739701</v>
       </c>
       <c r="O16" t="n">
-        <v>24.38602325095912</v>
+        <v>24.39194171184349</v>
       </c>
       <c r="P16" t="n">
-        <v>314.7179536880367</v>
+        <v>314.4058955411878</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -31922,28 +32104,28 @@
         <v>0.0428</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.745838622137864</v>
+        <v>-0.7136802155232106</v>
       </c>
       <c r="J17" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="K17" t="n">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="L17" t="n">
-        <v>0.04397793850281939</v>
+        <v>0.04060778852922386</v>
       </c>
       <c r="M17" t="n">
-        <v>21.30629244098428</v>
+        <v>21.37175920347937</v>
       </c>
       <c r="N17" t="n">
-        <v>658.5707923572706</v>
+        <v>658.9742805571678</v>
       </c>
       <c r="O17" t="n">
-        <v>25.66263416637642</v>
+        <v>25.67049435747523</v>
       </c>
       <c r="P17" t="n">
-        <v>330.5664324859937</v>
+        <v>330.2161999213981</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -32000,28 +32182,28 @@
         <v>0.0478</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1085744373902329</v>
+        <v>-0.1027110503257379</v>
       </c>
       <c r="J18" t="n">
+        <v>332</v>
+      </c>
+      <c r="K18" t="n">
         <v>330</v>
       </c>
-      <c r="K18" t="n">
-        <v>328</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.005425232737982233</v>
+        <v>0.004906184596256025</v>
       </c>
       <c r="M18" t="n">
-        <v>8.531740186100722</v>
+        <v>8.501175607326386</v>
       </c>
       <c r="N18" t="n">
-        <v>117.6180269683191</v>
+        <v>117.078362062418</v>
       </c>
       <c r="O18" t="n">
-        <v>10.8451845059602</v>
+        <v>10.82027550769471</v>
       </c>
       <c r="P18" t="n">
-        <v>326.6528890576244</v>
+        <v>326.5892599897065</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -32078,28 +32260,28 @@
         <v>0.0415</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2107377579235267</v>
+        <v>0.2173416313165848</v>
       </c>
       <c r="J19" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="K19" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="L19" t="n">
-        <v>0.03309563086311818</v>
+        <v>0.03541332152750998</v>
       </c>
       <c r="M19" t="n">
-        <v>6.370046501635168</v>
+        <v>6.360338582075322</v>
       </c>
       <c r="N19" t="n">
-        <v>71.22278953488913</v>
+        <v>71.00644551756113</v>
       </c>
       <c r="O19" t="n">
-        <v>8.439359545302542</v>
+        <v>8.426532235597342</v>
       </c>
       <c r="P19" t="n">
-        <v>345.9054838181675</v>
+        <v>345.8342521357661</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -32156,28 +32338,28 @@
         <v>0.0344</v>
       </c>
       <c r="I20" t="n">
-        <v>0.05512699457732225</v>
+        <v>0.06619113548712668</v>
       </c>
       <c r="J20" t="n">
+        <v>332</v>
+      </c>
+      <c r="K20" t="n">
         <v>330</v>
       </c>
-      <c r="K20" t="n">
-        <v>328</v>
-      </c>
       <c r="L20" t="n">
-        <v>0.002053375973767091</v>
+        <v>0.002969663919139998</v>
       </c>
       <c r="M20" t="n">
-        <v>7.030058282888604</v>
+        <v>7.055665582687349</v>
       </c>
       <c r="N20" t="n">
-        <v>81.2339711109436</v>
+        <v>81.33380970229253</v>
       </c>
       <c r="O20" t="n">
-        <v>9.012989022013929</v>
+        <v>9.018525916262176</v>
       </c>
       <c r="P20" t="n">
-        <v>344.717644220033</v>
+        <v>344.5983271336278</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -32234,28 +32416,28 @@
         <v>0.0304</v>
       </c>
       <c r="I21" t="n">
-        <v>0.263509356322192</v>
+        <v>0.2845071477093423</v>
       </c>
       <c r="J21" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="K21" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0172226470408432</v>
+        <v>0.02005134846516343</v>
       </c>
       <c r="M21" t="n">
-        <v>11.89208682012445</v>
+        <v>11.93820430682746</v>
       </c>
       <c r="N21" t="n">
-        <v>216.1624720184477</v>
+        <v>216.9552061003389</v>
       </c>
       <c r="O21" t="n">
-        <v>14.7024648279956</v>
+        <v>14.72939938016275</v>
       </c>
       <c r="P21" t="n">
-        <v>321.7611162957457</v>
+        <v>321.5331159030276</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -32312,28 +32494,28 @@
         <v>0.0447</v>
       </c>
       <c r="I22" t="n">
-        <v>0.319095971736239</v>
+        <v>0.3553336985831205</v>
       </c>
       <c r="J22" t="n">
+        <v>332</v>
+      </c>
+      <c r="K22" t="n">
         <v>330</v>
       </c>
-      <c r="K22" t="n">
-        <v>328</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.01603196051432809</v>
+        <v>0.01966723183893793</v>
       </c>
       <c r="M22" t="n">
-        <v>14.85036247384608</v>
+        <v>14.96049106026969</v>
       </c>
       <c r="N22" t="n">
-        <v>344.3573246230708</v>
+        <v>348.6399773415525</v>
       </c>
       <c r="O22" t="n">
-        <v>18.55686731706272</v>
+        <v>18.67190342042162</v>
       </c>
       <c r="P22" t="n">
-        <v>302.7897610655216</v>
+        <v>302.3995511587278</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -32390,28 +32572,28 @@
         <v>0.0592</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4864513668145602</v>
+        <v>0.4908145990210932</v>
       </c>
       <c r="J23" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="K23" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1142790302328355</v>
+        <v>0.1171776430399549</v>
       </c>
       <c r="M23" t="n">
-        <v>7.825007583569148</v>
+        <v>7.794393176719508</v>
       </c>
       <c r="N23" t="n">
-        <v>100.6770883130589</v>
+        <v>100.1615046070183</v>
       </c>
       <c r="O23" t="n">
-        <v>10.03379730276922</v>
+        <v>10.0080719725139</v>
       </c>
       <c r="P23" t="n">
-        <v>323.1480534185579</v>
+        <v>323.1009776653952</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -32468,28 +32650,28 @@
         <v>0.07870000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1564379864328629</v>
+        <v>0.1574776732998431</v>
       </c>
       <c r="J24" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="K24" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0416603655306591</v>
+        <v>0.04264658183234304</v>
       </c>
       <c r="M24" t="n">
-        <v>3.944959802993712</v>
+        <v>3.926047870726676</v>
       </c>
       <c r="N24" t="n">
-        <v>30.82666146751688</v>
+        <v>30.64723012482555</v>
       </c>
       <c r="O24" t="n">
-        <v>5.552176282100279</v>
+        <v>5.535994050288128</v>
       </c>
       <c r="P24" t="n">
-        <v>340.1077003170607</v>
+        <v>340.0964591874609</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -32531,7 +32713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y331"/>
+  <dimension ref="A1:Y333"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73901,7 +74083,7 @@
       </c>
       <c r="K331" t="inlineStr">
         <is>
-          <t>-38.57846300855207,174.62986092069562</t>
+          <t>-38.578462128178565,174.63001081636543</t>
         </is>
       </c>
       <c r="L331" t="inlineStr">
@@ -73972,6 +74154,260 @@
       <c r="Y331" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:53+00:00</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>-38.58478321910705,174.62956669931035</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>-38.58407871821357,174.6295464215311</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>-38.583383118899064,174.6297093365102</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>-38.5826749969254,174.6296006048709</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>-38.58197694685816,174.62996360464933</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>-38.581271268039686,174.6299669146386</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>-38.58056956623396,174.62988035768745</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>-38.57986726093023,174.62989538002466</t>
+        </is>
+      </c>
+      <c r="J332" t="inlineStr">
+        <is>
+          <t>-38.57916522513235,174.62986334408356</t>
+        </is>
+      </c>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>-38.578462128178565,174.63001081636543</t>
+        </is>
+      </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>-38.57776258977076,174.62986275738925</t>
+        </is>
+      </c>
+      <c r="M332" t="inlineStr">
+        <is>
+          <t>-38.57709565600294,174.63159835144864</t>
+        </is>
+      </c>
+      <c r="N332" t="inlineStr">
+        <is>
+          <t>-38.576363914245924,174.63003310894445</t>
+        </is>
+      </c>
+      <c r="O332" t="inlineStr">
+        <is>
+          <t>-38.57566205373549,174.6300630472301</t>
+        </is>
+      </c>
+      <c r="P332" t="inlineStr">
+        <is>
+          <t>-38.57495699770456,174.62994521475937</t>
+        </is>
+      </c>
+      <c r="Q332" t="inlineStr">
+        <is>
+          <t>-38.57426031039104,174.63008193135147</t>
+        </is>
+      </c>
+      <c r="R332" t="inlineStr">
+        <is>
+          <t>-38.573568300803295,174.63023624333528</t>
+        </is>
+      </c>
+      <c r="S332" t="inlineStr">
+        <is>
+          <t>-38.57285154175217,174.62999110937508</t>
+        </is>
+      </c>
+      <c r="T332" t="inlineStr">
+        <is>
+          <t>-38.572153131036316,174.63009305578697</t>
+        </is>
+      </c>
+      <c r="U332" t="inlineStr">
+        <is>
+          <t>-38.571455143207984,174.6302481124233</t>
+        </is>
+      </c>
+      <c r="V332" t="inlineStr">
+        <is>
+          <t>-38.57075241238617,174.63030173935906</t>
+        </is>
+      </c>
+      <c r="W332" t="inlineStr">
+        <is>
+          <t>-38.57005218744862,174.63039888160668</t>
+        </is>
+      </c>
+      <c r="X332" t="inlineStr">
+        <is>
+          <t>-38.56934962744877,174.63037649362042</t>
+        </is>
+      </c>
+      <c r="Y332" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:32+00:00</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>-38.584781731586936,174.6295361095853</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>-38.584085175255574,174.6296792048515</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>-38.5833893808182,174.6298381087415</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>-38.58268146855177,174.62979384105176</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>-38.58197709083923,174.6299866753915</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>-38.58127154310918,174.62992008476434</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>-38.580569259503555,174.6299325816718</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>-38.57986692049482,174.62995334234333</t>
+        </is>
+      </c>
+      <c r="J333" t="inlineStr">
+        <is>
+          <t>-38.579164530128146,174.62998167788274</t>
+        </is>
+      </c>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>-38.57846169263954,174.63008496077398</t>
+        </is>
+      </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>-38.57776265023625,174.62987389046586</t>
+        </is>
+      </c>
+      <c r="M333" t="inlineStr">
+        <is>
+          <t>-38.57709565600294,174.63159835144864</t>
+        </is>
+      </c>
+      <c r="N333" t="inlineStr">
+        <is>
+          <t>-38.57636522134425,174.63009368700074</t>
+        </is>
+      </c>
+      <c r="O333" t="inlineStr">
+        <is>
+          <t>-38.57566296969869,174.63010549734818</t>
+        </is>
+      </c>
+      <c r="P333" t="inlineStr">
+        <is>
+          <t>-38.57495699770456,174.62994521475937</t>
+        </is>
+      </c>
+      <c r="Q333" t="inlineStr">
+        <is>
+          <t>-38.57426031039104,174.63008193135147</t>
+        </is>
+      </c>
+      <c r="R333" t="inlineStr">
+        <is>
+          <t>-38.57356979869861,174.63026475730578</t>
+        </is>
+      </c>
+      <c r="S333" t="inlineStr">
+        <is>
+          <t>-38.57285255682861,174.63000919670367</t>
+        </is>
+      </c>
+      <c r="T333" t="inlineStr">
+        <is>
+          <t>-38.57215278211329,174.63008583908973</t>
+        </is>
+      </c>
+      <c r="U333" t="inlineStr">
+        <is>
+          <t>-38.57145501006255,174.63024352489012</t>
+        </is>
+      </c>
+      <c r="V333" t="inlineStr">
+        <is>
+          <t>-38.5707529738923,174.63033386575458</t>
+        </is>
+      </c>
+      <c r="W333" t="inlineStr">
+        <is>
+          <t>-38.57005198490421,174.63038890043416</t>
+        </is>
+      </c>
+      <c r="X333" t="inlineStr">
+        <is>
+          <t>-38.56934934910502,174.63036444868837</t>
+        </is>
+      </c>
+      <c r="Y333" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>

--- a/data/nzd0264/nzd0264.xlsx
+++ b/data/nzd0264/nzd0264.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y333"/>
+  <dimension ref="A1:Y335"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26948,9 +26948,7 @@
       <c r="L331" t="n">
         <v>342.27</v>
       </c>
-      <c r="M331" t="n">
-        <v>193.58</v>
-      </c>
+      <c r="M331" t="inlineStr"/>
       <c r="N331" t="n">
         <v>328.91</v>
       </c>
@@ -27029,9 +27027,7 @@
       <c r="L332" t="n">
         <v>342.27</v>
       </c>
-      <c r="M332" t="n">
-        <v>193.58</v>
-      </c>
+      <c r="M332" t="inlineStr"/>
       <c r="N332" t="n">
         <v>333.06</v>
       </c>
@@ -27054,7 +27050,7 @@
         <v>355.82</v>
       </c>
       <c r="U332" t="n">
-        <v>347.28</v>
+        <v>343.23</v>
       </c>
       <c r="V332" t="n">
         <v>345.28</v>
@@ -27087,7 +27083,7 @@
         <v>333.86</v>
       </c>
       <c r="E333" t="n">
-        <v>343.52</v>
+        <v>312.32</v>
       </c>
       <c r="F333" t="n">
         <v>329.5</v>
@@ -27102,17 +27098,15 @@
         <v>333.4</v>
       </c>
       <c r="J333" t="n">
-        <v>331.26</v>
+        <v>338.15</v>
       </c>
       <c r="K333" t="n">
         <v>322.59</v>
       </c>
       <c r="L333" t="n">
-        <v>341.3</v>
-      </c>
-      <c r="M333" t="n">
-        <v>193.58</v>
-      </c>
+        <v>332.5</v>
+      </c>
+      <c r="M333" t="inlineStr"/>
       <c r="N333" t="n">
         <v>327.78</v>
       </c>
@@ -27135,7 +27129,7 @@
         <v>356.45</v>
       </c>
       <c r="U333" t="n">
-        <v>347.68</v>
+        <v>338.59</v>
       </c>
       <c r="V333" t="n">
         <v>342.48</v>
@@ -27149,6 +27143,166 @@
       <c r="Y333" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:42+00:00</t>
+        </is>
+      </c>
+      <c r="B334" t="n">
+        <v>348.76</v>
+      </c>
+      <c r="C334" t="n">
+        <v>341.96</v>
+      </c>
+      <c r="D334" t="n">
+        <v>333.86</v>
+      </c>
+      <c r="E334" t="n">
+        <v>312.32</v>
+      </c>
+      <c r="F334" t="n">
+        <v>329.5</v>
+      </c>
+      <c r="G334" t="n">
+        <v>335.64</v>
+      </c>
+      <c r="H334" t="n">
+        <v>334.88</v>
+      </c>
+      <c r="I334" t="n">
+        <v>337.71</v>
+      </c>
+      <c r="J334" t="n">
+        <v>343.01</v>
+      </c>
+      <c r="K334" t="n">
+        <v>320.48</v>
+      </c>
+      <c r="L334" t="n">
+        <v>334.22</v>
+      </c>
+      <c r="M334" t="inlineStr"/>
+      <c r="N334" t="n">
+        <v>328.18</v>
+      </c>
+      <c r="O334" t="n">
+        <v>328.41</v>
+      </c>
+      <c r="P334" t="n">
+        <v>348.41</v>
+      </c>
+      <c r="Q334" t="n">
+        <v>337.76</v>
+      </c>
+      <c r="R334" t="n">
+        <v>322.21</v>
+      </c>
+      <c r="S334" t="n">
+        <v>357.04</v>
+      </c>
+      <c r="T334" t="n">
+        <v>357.84</v>
+      </c>
+      <c r="U334" t="n">
+        <v>341.33</v>
+      </c>
+      <c r="V334" t="n">
+        <v>345.22</v>
+      </c>
+      <c r="W334" t="n">
+        <v>339.47</v>
+      </c>
+      <c r="X334" t="n">
+        <v>344.22</v>
+      </c>
+      <c r="Y334" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:54+00:00</t>
+        </is>
+      </c>
+      <c r="B335" t="n">
+        <v>350.58</v>
+      </c>
+      <c r="C335" t="n">
+        <v>342.19</v>
+      </c>
+      <c r="D335" t="n">
+        <v>327.4</v>
+      </c>
+      <c r="E335" t="n">
+        <v>301.44</v>
+      </c>
+      <c r="F335" t="n">
+        <v>321.01</v>
+      </c>
+      <c r="G335" t="n">
+        <v>330.53</v>
+      </c>
+      <c r="H335" t="n">
+        <v>327.89</v>
+      </c>
+      <c r="I335" t="n">
+        <v>328.59</v>
+      </c>
+      <c r="J335" t="n">
+        <v>329.49</v>
+      </c>
+      <c r="K335" t="n">
+        <v>314.4</v>
+      </c>
+      <c r="L335" t="n">
+        <v>334.22</v>
+      </c>
+      <c r="M335" t="n">
+        <v>251.91</v>
+      </c>
+      <c r="N335" t="n">
+        <v>322.1</v>
+      </c>
+      <c r="O335" t="n">
+        <v>321.97</v>
+      </c>
+      <c r="P335" t="n">
+        <v>339.19</v>
+      </c>
+      <c r="Q335" t="n">
+        <v>331.01</v>
+      </c>
+      <c r="R335" t="n">
+        <v>322.16</v>
+      </c>
+      <c r="S335" t="n">
+        <v>356.22</v>
+      </c>
+      <c r="T335" t="n">
+        <v>359.48</v>
+      </c>
+      <c r="U335" t="n">
+        <v>339.35</v>
+      </c>
+      <c r="V335" t="n">
+        <v>339.3</v>
+      </c>
+      <c r="W335" t="n">
+        <v>340.52</v>
+      </c>
+      <c r="X335" t="n">
+        <v>345.88</v>
+      </c>
+      <c r="Y335" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -27163,7 +27317,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B360"/>
+  <dimension ref="A1:B362"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30766,6 +30920,26 @@
       </c>
       <c r="B360" t="n">
         <v>1.65</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B361" t="n">
+        <v>-0.78</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B362" t="n">
+        <v>0.22</v>
       </c>
     </row>
   </sheetData>
@@ -30934,28 +31108,28 @@
         <v>0.0285</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7740698646335652</v>
+        <v>0.7664993013752189</v>
       </c>
       <c r="J2" t="n">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="K2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1252899316090117</v>
+        <v>0.1242444263499005</v>
       </c>
       <c r="M2" t="n">
-        <v>12.00801509141708</v>
+        <v>11.97175527707283</v>
       </c>
       <c r="N2" t="n">
-        <v>228.6941084839017</v>
+        <v>227.5727457209224</v>
       </c>
       <c r="O2" t="n">
-        <v>15.12263563284858</v>
+        <v>15.08551443341997</v>
       </c>
       <c r="P2" t="n">
-        <v>335.948311213075</v>
+        <v>336.0314268476574</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -31012,28 +31186,28 @@
         <v>0.0381</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1701687988758201</v>
+        <v>-0.1610029177361296</v>
       </c>
       <c r="J3" t="n">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="K3" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="L3" t="n">
-        <v>0.005470108851110211</v>
+        <v>0.004948310938911238</v>
       </c>
       <c r="M3" t="n">
-        <v>12.04186756695161</v>
+        <v>12.00466474403561</v>
       </c>
       <c r="N3" t="n">
-        <v>290.548789107948</v>
+        <v>289.2114281960726</v>
       </c>
       <c r="O3" t="n">
-        <v>17.04549175318647</v>
+        <v>17.0062173394342</v>
       </c>
       <c r="P3" t="n">
-        <v>338.2741333406353</v>
+        <v>338.1747180977107</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31090,28 +31264,28 @@
         <v>0.0304</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1225802744840191</v>
+        <v>-0.1244923584464986</v>
       </c>
       <c r="J4" t="n">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="K4" t="n">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00248435122659918</v>
+        <v>0.002590846231105837</v>
       </c>
       <c r="M4" t="n">
-        <v>13.30171485589694</v>
+        <v>13.24332977459044</v>
       </c>
       <c r="N4" t="n">
-        <v>330.9302247810836</v>
+        <v>329.0052164844544</v>
       </c>
       <c r="O4" t="n">
-        <v>18.19148770114978</v>
+        <v>18.13850094369583</v>
       </c>
       <c r="P4" t="n">
-        <v>335.5925730274101</v>
+        <v>335.6134875802475</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31168,28 +31342,28 @@
         <v>0.0232</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8499932137429141</v>
+        <v>0.7859261596124595</v>
       </c>
       <c r="J5" t="n">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="K5" t="n">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07176423857920233</v>
+        <v>0.06116861698430265</v>
       </c>
       <c r="M5" t="n">
-        <v>18.33163865075476</v>
+        <v>18.55357239790424</v>
       </c>
       <c r="N5" t="n">
-        <v>514.5941956101832</v>
+        <v>524.8732744587362</v>
       </c>
       <c r="O5" t="n">
-        <v>22.68466873485666</v>
+        <v>22.91011292985559</v>
       </c>
       <c r="P5" t="n">
-        <v>323.9562177803341</v>
+        <v>324.6551555365443</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31246,28 +31420,28 @@
         <v>0.0304</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3308667970660835</v>
+        <v>0.3394853299834406</v>
       </c>
       <c r="J6" t="n">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="K6" t="n">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="L6" t="n">
-        <v>0.008322584444227066</v>
+        <v>0.008851259737415074</v>
       </c>
       <c r="M6" t="n">
-        <v>19.36564823252137</v>
+        <v>19.2779720196944</v>
       </c>
       <c r="N6" t="n">
-        <v>717.2099621532218</v>
+        <v>713.3334378477365</v>
       </c>
       <c r="O6" t="n">
-        <v>26.78077598116272</v>
+        <v>26.70830278860371</v>
       </c>
       <c r="P6" t="n">
-        <v>308.7142757850499</v>
+        <v>308.6203790179794</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31324,28 +31498,28 @@
         <v>0.0311</v>
       </c>
       <c r="I7" t="n">
-        <v>0.06271040060050351</v>
+        <v>0.07198699339573485</v>
       </c>
       <c r="J7" t="n">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="K7" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0004774376417944204</v>
+        <v>0.0006356840411497755</v>
       </c>
       <c r="M7" t="n">
-        <v>15.57840322064501</v>
+        <v>15.50940969904041</v>
       </c>
       <c r="N7" t="n">
-        <v>452.619211651743</v>
+        <v>450.3105584258403</v>
       </c>
       <c r="O7" t="n">
-        <v>21.27484927447767</v>
+        <v>21.22052210540166</v>
       </c>
       <c r="P7" t="n">
-        <v>323.1374605038351</v>
+        <v>323.0365433418775</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31402,28 +31576,28 @@
         <v>0.0451</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1269717702109469</v>
+        <v>0.1250755080121428</v>
       </c>
       <c r="J8" t="n">
+        <v>334</v>
+      </c>
+      <c r="K8" t="n">
         <v>332</v>
       </c>
-      <c r="K8" t="n">
-        <v>330</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.007429482175766444</v>
+        <v>0.007286978804569078</v>
       </c>
       <c r="M8" t="n">
-        <v>8.829622224018978</v>
+        <v>8.799006942794763</v>
       </c>
       <c r="N8" t="n">
-        <v>119.093362550951</v>
+        <v>118.4670352242372</v>
       </c>
       <c r="O8" t="n">
-        <v>10.91299054113725</v>
+        <v>10.88425630092554</v>
       </c>
       <c r="P8" t="n">
-        <v>329.7376417191541</v>
+        <v>329.7582466716907</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31480,28 +31654,28 @@
         <v>0.0388</v>
       </c>
       <c r="I9" t="n">
-        <v>0.08078780142399983</v>
+        <v>0.07905805882345103</v>
       </c>
       <c r="J9" t="n">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="K9" t="n">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001225597534299294</v>
+        <v>0.001186519578320833</v>
       </c>
       <c r="M9" t="n">
-        <v>12.38572140367664</v>
+        <v>12.34109530195484</v>
       </c>
       <c r="N9" t="n">
-        <v>294.9747736624833</v>
+        <v>293.327529595827</v>
       </c>
       <c r="O9" t="n">
-        <v>17.17482965454049</v>
+        <v>17.12680733808339</v>
       </c>
       <c r="P9" t="n">
-        <v>332.5689701234286</v>
+        <v>332.587779612029</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31558,28 +31732,28 @@
         <v>0.079</v>
       </c>
       <c r="I10" t="n">
-        <v>0.06791867032276451</v>
+        <v>0.08779385452310033</v>
       </c>
       <c r="J10" t="n">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="K10" t="n">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="L10" t="n">
-        <v>0.001116967047869011</v>
+        <v>0.001869101754550351</v>
       </c>
       <c r="M10" t="n">
-        <v>12.75454878823</v>
+        <v>12.76629527782052</v>
       </c>
       <c r="N10" t="n">
-        <v>226.3895265643494</v>
+        <v>227.0774417802258</v>
       </c>
       <c r="O10" t="n">
-        <v>15.04624626158795</v>
+        <v>15.06908894990755</v>
       </c>
       <c r="P10" t="n">
-        <v>319.9493250710732</v>
+        <v>319.7326222661636</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -31636,28 +31810,28 @@
         <v>0.0864</v>
       </c>
       <c r="I11" t="n">
-        <v>0.07439202869399429</v>
+        <v>0.07550946557715268</v>
       </c>
       <c r="J11" t="n">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="K11" t="n">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="L11" t="n">
-        <v>0.001105450310231904</v>
+        <v>0.001151581103416066</v>
       </c>
       <c r="M11" t="n">
-        <v>13.70509508403004</v>
+        <v>13.63994172520059</v>
       </c>
       <c r="N11" t="n">
-        <v>275.7046932704367</v>
+        <v>274.0960734520812</v>
       </c>
       <c r="O11" t="n">
-        <v>16.60435765907362</v>
+        <v>16.55584710765599</v>
       </c>
       <c r="P11" t="n">
-        <v>314.4533443843117</v>
+        <v>314.441223847346</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -31714,28 +31888,28 @@
         <v>0.06569999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3620938384355314</v>
+        <v>0.3639212322432525</v>
       </c>
       <c r="J12" t="n">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="K12" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="L12" t="n">
-        <v>0.03232929450054611</v>
+        <v>0.03305417089654838</v>
       </c>
       <c r="M12" t="n">
-        <v>12.15494641913493</v>
+        <v>12.08635490826886</v>
       </c>
       <c r="N12" t="n">
-        <v>217.7807530229597</v>
+        <v>216.1794923479462</v>
       </c>
       <c r="O12" t="n">
-        <v>14.7573965530157</v>
+        <v>14.70304364231931</v>
       </c>
       <c r="P12" t="n">
-        <v>318.653227235775</v>
+        <v>318.6332397105612</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -31792,28 +31966,28 @@
         <v>0.0371</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.837061987867683</v>
+        <v>-0.6744441190551381</v>
       </c>
       <c r="J13" t="n">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="K13" t="n">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="L13" t="n">
-        <v>0.03194680439834252</v>
+        <v>0.02270365116643325</v>
       </c>
       <c r="M13" t="n">
-        <v>28.98535558135828</v>
+        <v>28.09034782566955</v>
       </c>
       <c r="N13" t="n">
-        <v>1201.413931802533</v>
+        <v>1102.102927524257</v>
       </c>
       <c r="O13" t="n">
-        <v>34.66141849091772</v>
+        <v>33.19793559130232</v>
       </c>
       <c r="P13" t="n">
-        <v>321.9303183161761</v>
+        <v>320.2019745879601</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -31870,28 +32044,28 @@
         <v>0.07920000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2548863393770484</v>
+        <v>-0.2252461939484767</v>
       </c>
       <c r="J14" t="n">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="K14" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="L14" t="n">
-        <v>0.007711729297097514</v>
+        <v>0.00604436951903875</v>
       </c>
       <c r="M14" t="n">
-        <v>18.50151191652712</v>
+        <v>18.54794121548596</v>
       </c>
       <c r="N14" t="n">
-        <v>463.925214069102</v>
+        <v>465.4745768114342</v>
       </c>
       <c r="O14" t="n">
-        <v>21.53892323374365</v>
+        <v>21.57485983294988</v>
       </c>
       <c r="P14" t="n">
-        <v>304.98930556439</v>
+        <v>304.6685882155176</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -31948,28 +32122,28 @@
         <v>0.1073</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1303714606471828</v>
+        <v>0.1498475463265431</v>
       </c>
       <c r="J15" t="n">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="K15" t="n">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="L15" t="n">
-        <v>0.002632391742170337</v>
+        <v>0.003495300995398298</v>
       </c>
       <c r="M15" t="n">
-        <v>16.19446525149914</v>
+        <v>16.19642563162193</v>
       </c>
       <c r="N15" t="n">
-        <v>357.9389180616731</v>
+        <v>357.6945795905516</v>
       </c>
       <c r="O15" t="n">
-        <v>18.91927371919105</v>
+        <v>18.91281522118142</v>
       </c>
       <c r="P15" t="n">
-        <v>304.0564079851599</v>
+        <v>303.8456929515546</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -32026,28 +32200,28 @@
         <v>0.0534</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2783615203830776</v>
+        <v>0.3028965055093912</v>
       </c>
       <c r="J16" t="n">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="K16" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="L16" t="n">
-        <v>0.007084342390225817</v>
+        <v>0.008429213391055734</v>
       </c>
       <c r="M16" t="n">
-        <v>20.04245642255013</v>
+        <v>20.0345157880061</v>
       </c>
       <c r="N16" t="n">
-        <v>594.9668204739701</v>
+        <v>594.375486438125</v>
       </c>
       <c r="O16" t="n">
-        <v>24.39194171184349</v>
+        <v>24.37981719451819</v>
       </c>
       <c r="P16" t="n">
-        <v>314.4058955411878</v>
+        <v>314.1374676560518</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -32104,28 +32278,28 @@
         <v>0.0428</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.7136802155232106</v>
+        <v>-0.6865144077071917</v>
       </c>
       <c r="J17" t="n">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="K17" t="n">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="L17" t="n">
-        <v>0.04060778852922386</v>
+        <v>0.03793483042840573</v>
       </c>
       <c r="M17" t="n">
-        <v>21.37175920347937</v>
+        <v>21.40338114081258</v>
       </c>
       <c r="N17" t="n">
-        <v>658.9742805571678</v>
+        <v>658.1668943415395</v>
       </c>
       <c r="O17" t="n">
-        <v>25.67049435747523</v>
+        <v>25.65476357991902</v>
       </c>
       <c r="P17" t="n">
-        <v>330.2161999213981</v>
+        <v>329.9187797757445</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -32182,28 +32356,28 @@
         <v>0.0478</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1027110503257379</v>
+        <v>-0.1045781030785901</v>
       </c>
       <c r="J18" t="n">
+        <v>334</v>
+      </c>
+      <c r="K18" t="n">
         <v>332</v>
       </c>
-      <c r="K18" t="n">
-        <v>330</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.004906184596256025</v>
+        <v>0.005142548158134419</v>
       </c>
       <c r="M18" t="n">
-        <v>8.501175607326386</v>
+        <v>8.463250235909902</v>
       </c>
       <c r="N18" t="n">
-        <v>117.078362062418</v>
+        <v>116.3897922698456</v>
       </c>
       <c r="O18" t="n">
-        <v>10.82027550769471</v>
+        <v>10.7884100899922</v>
       </c>
       <c r="P18" t="n">
-        <v>326.5892599897065</v>
+        <v>326.6096351712214</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -32260,28 +32434,28 @@
         <v>0.0415</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2173416313165848</v>
+        <v>0.2229007802455811</v>
       </c>
       <c r="J19" t="n">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="K19" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="L19" t="n">
-        <v>0.03541332152750998</v>
+        <v>0.03751181272043824</v>
       </c>
       <c r="M19" t="n">
-        <v>6.360338582075322</v>
+        <v>6.345909482910637</v>
       </c>
       <c r="N19" t="n">
-        <v>71.00644551756113</v>
+        <v>70.73100543495329</v>
       </c>
       <c r="O19" t="n">
-        <v>8.426532235597342</v>
+        <v>8.410172735143631</v>
       </c>
       <c r="P19" t="n">
-        <v>345.8342521357661</v>
+        <v>345.7739626083797</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -32338,28 +32512,28 @@
         <v>0.0344</v>
       </c>
       <c r="I20" t="n">
-        <v>0.06619113548712668</v>
+        <v>0.07976296569659594</v>
       </c>
       <c r="J20" t="n">
+        <v>334</v>
+      </c>
+      <c r="K20" t="n">
         <v>332</v>
       </c>
-      <c r="K20" t="n">
-        <v>330</v>
-      </c>
       <c r="L20" t="n">
-        <v>0.002969663919139998</v>
+        <v>0.004307709718459618</v>
       </c>
       <c r="M20" t="n">
-        <v>7.055665582687349</v>
+        <v>7.096725672757343</v>
       </c>
       <c r="N20" t="n">
-        <v>81.33380970229253</v>
+        <v>81.74440886571195</v>
       </c>
       <c r="O20" t="n">
-        <v>9.018525916262176</v>
+        <v>9.041261464293129</v>
       </c>
       <c r="P20" t="n">
-        <v>344.5983271336278</v>
+        <v>344.4511685154661</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -32416,28 +32590,28 @@
         <v>0.0304</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2845071477093423</v>
+        <v>0.2898035525403303</v>
       </c>
       <c r="J21" t="n">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="K21" t="n">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="L21" t="n">
-        <v>0.02005134846516343</v>
+        <v>0.02106023354002817</v>
       </c>
       <c r="M21" t="n">
-        <v>11.93820430682746</v>
+        <v>11.89486824822854</v>
       </c>
       <c r="N21" t="n">
-        <v>216.9552061003389</v>
+        <v>215.2394125970729</v>
       </c>
       <c r="O21" t="n">
-        <v>14.72939938016275</v>
+        <v>14.67103992895776</v>
       </c>
       <c r="P21" t="n">
-        <v>321.5331159030276</v>
+        <v>321.4749106311808</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -32494,28 +32668,28 @@
         <v>0.0447</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3553336985831205</v>
+        <v>0.3888804682776781</v>
       </c>
       <c r="J22" t="n">
+        <v>334</v>
+      </c>
+      <c r="K22" t="n">
         <v>332</v>
       </c>
-      <c r="K22" t="n">
-        <v>330</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.01966723183893793</v>
+        <v>0.02336163996345897</v>
       </c>
       <c r="M22" t="n">
-        <v>14.96049106026969</v>
+        <v>15.05795526960886</v>
       </c>
       <c r="N22" t="n">
-        <v>348.6399773415525</v>
+        <v>352.0826953563559</v>
       </c>
       <c r="O22" t="n">
-        <v>18.67190342042162</v>
+        <v>18.76386674852377</v>
       </c>
       <c r="P22" t="n">
-        <v>302.3995511587278</v>
+        <v>302.0363803199345</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -32572,28 +32746,28 @@
         <v>0.0592</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4908145990210932</v>
+        <v>0.4951134074803258</v>
       </c>
       <c r="J23" t="n">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="K23" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1171776430399549</v>
+        <v>0.1200943463269799</v>
       </c>
       <c r="M23" t="n">
-        <v>7.794393176719508</v>
+        <v>7.764207953606012</v>
       </c>
       <c r="N23" t="n">
-        <v>100.1615046070183</v>
+        <v>99.651127577488</v>
       </c>
       <c r="O23" t="n">
-        <v>10.0080719725139</v>
+        <v>9.982541138281775</v>
       </c>
       <c r="P23" t="n">
-        <v>323.1009776653952</v>
+        <v>323.0543458909248</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -32650,28 +32824,28 @@
         <v>0.07870000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1574776732998431</v>
+        <v>0.1583451340181976</v>
       </c>
       <c r="J24" t="n">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="K24" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="L24" t="n">
-        <v>0.04264658183234304</v>
+        <v>0.04355860814276813</v>
       </c>
       <c r="M24" t="n">
-        <v>3.926047870726676</v>
+        <v>3.906814235700673</v>
       </c>
       <c r="N24" t="n">
-        <v>30.64723012482555</v>
+        <v>30.47085145230751</v>
       </c>
       <c r="O24" t="n">
-        <v>5.535994050288128</v>
+        <v>5.520040892267693</v>
       </c>
       <c r="P24" t="n">
-        <v>340.0964591874609</v>
+        <v>340.0870248490329</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -32713,7 +32887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y333"/>
+  <dimension ref="A1:Y335"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74091,11 +74265,7 @@
           <t>-38.57776258977076,174.62986275738925</t>
         </is>
       </c>
-      <c r="M331" t="inlineStr">
-        <is>
-          <t>-38.57709565600294,174.63159835144864</t>
-        </is>
-      </c>
+      <c r="M331" t="inlineStr"/>
       <c r="N331" t="inlineStr">
         <is>
           <t>-38.57636494160804,174.63008072237875</t>
@@ -74218,11 +74388,7 @@
           <t>-38.57776258977076,174.62986275738925</t>
         </is>
       </c>
-      <c r="M332" t="inlineStr">
-        <is>
-          <t>-38.57709565600294,174.63159835144864</t>
-        </is>
-      </c>
+      <c r="M332" t="inlineStr"/>
       <c r="N332" t="inlineStr">
         <is>
           <t>-38.576363914245924,174.63003310894445</t>
@@ -74260,7 +74426,7 @@
       </c>
       <c r="U332" t="inlineStr">
         <is>
-          <t>-38.571455143207984,174.6302481124233</t>
+          <t>-38.571456491295386,174.63029456119708</t>
         </is>
       </c>
       <c r="V332" t="inlineStr">
@@ -74307,7 +74473,7 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>-38.58268146855177,174.62979384105176</t>
+          <t>-38.582693450777846,174.63015164341857</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
@@ -74332,7 +74498,7 @@
       </c>
       <c r="J333" t="inlineStr">
         <is>
-          <t>-38.579164530128146,174.62998167788274</t>
+          <t>-38.579164994601065,174.62990259739112</t>
         </is>
       </c>
       <c r="K333" t="inlineStr">
@@ -74342,14 +74508,10 @@
       </c>
       <c r="L333" t="inlineStr">
         <is>
-          <t>-38.57776265023625,174.62987389046586</t>
-        </is>
-      </c>
-      <c r="M333" t="inlineStr">
-        <is>
-          <t>-38.57709565600294,174.63159835144864</t>
-        </is>
-      </c>
+          <t>-38.57776319874085,174.62997489157246</t>
+        </is>
+      </c>
+      <c r="M333" t="inlineStr"/>
       <c r="N333" t="inlineStr">
         <is>
           <t>-38.57636522134425,174.63009368700074</t>
@@ -74387,7 +74549,7 @@
       </c>
       <c r="U333" t="inlineStr">
         <is>
-          <t>-38.57145501006255,174.63024352489012</t>
+          <t>-38.57145803574811,174.63034777658373</t>
         </is>
       </c>
       <c r="V333" t="inlineStr">
@@ -74408,6 +74570,256 @@
       <c r="Y333" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:42+00:00</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>-38.58478168701692,174.62953519303923</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>-38.584085175255574,174.6296792048515</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>-38.5833893808182,174.6298381087415</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>-38.582693450777846,174.63015164341857</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>-38.58197709083923,174.6299866753915</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>-38.58127154310918,174.62992008476434</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>-38.580569259503555,174.6299325816718</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>-38.57986721104644,174.629903873513</t>
+        </is>
+      </c>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>-38.57916532219422,174.62984681637494</t>
+        </is>
+      </c>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>-38.57846155037126,174.6301091782196</t>
+        </is>
+      </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>-38.57776309153999,174.6299551504472</t>
+        </is>
+      </c>
+      <c r="M334" t="inlineStr"/>
+      <c r="N334" t="inlineStr">
+        <is>
+          <t>-38.576365122322734,174.63008909775402</t>
+        </is>
+      </c>
+      <c r="O334" t="inlineStr">
+        <is>
+          <t>-38.57566331875085,174.63012167428522</t>
+        </is>
+      </c>
+      <c r="P334" t="inlineStr">
+        <is>
+          <t>-38.574956613962826,174.62992743177603</t>
+        </is>
+      </c>
+      <c r="Q334" t="inlineStr">
+        <is>
+          <t>-38.57426040335226,174.63008456843042</t>
+        </is>
+      </c>
+      <c r="R334" t="inlineStr">
+        <is>
+          <t>-38.57357315540251,174.63032865608636</t>
+        </is>
+      </c>
+      <c r="S334" t="inlineStr">
+        <is>
+          <t>-38.57285228699844,174.63000438867957</t>
+        </is>
+      </c>
+      <c r="T334" t="inlineStr">
+        <is>
+          <t>-38.572152012265704,174.63006991653572</t>
+        </is>
+      </c>
+      <c r="U334" t="inlineStr">
+        <is>
+          <t>-38.571457123725075,174.63031635198024</t>
+        </is>
+      </c>
+      <c r="V334" t="inlineStr">
+        <is>
+          <t>-38.57075242441854,174.63030242778183</t>
+        </is>
+      </c>
+      <c r="W334" t="inlineStr">
+        <is>
+          <t>-38.57005218744862,174.63039888160668</t>
+        </is>
+      </c>
+      <c r="X334" t="inlineStr">
+        <is>
+          <t>-38.56934973878593,174.63038131159325</t>
+        </is>
+      </c>
+      <c r="Y334" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:54+00:00</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>-38.58478067304713,174.62951434161673</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>-38.58408504711902,174.629676569807</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>-38.583392979685996,174.62991211841256</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>-38.58269762893716,174.63027641554478</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>-38.58197769894781,174.63008412345096</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>-38.581271198595154,174.6299787368861</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>-38.580568788239326,174.63001281148263</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>-38.57986659621183,174.63000855001573</t>
+        </is>
+      </c>
+      <c r="J335" t="inlineStr">
+        <is>
+          <t>-38.5791644107992,174.63000199319</t>
+        </is>
+      </c>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>-38.578461140394836,174.63017896118924</t>
+        </is>
+      </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>-38.57776309153999,174.6299551504472</t>
+        </is>
+      </c>
+      <c r="M335" t="inlineStr">
+        <is>
+          <t>-38.577082841571915,174.63092906435486</t>
+        </is>
+      </c>
+      <c r="N335" t="inlineStr">
+        <is>
+          <t>-38.57636662743008,174.63015885430497</t>
+        </is>
+      </c>
+      <c r="O335" t="inlineStr">
+        <is>
+          <t>-38.57566491297485,174.63019556043832</t>
+        </is>
+      </c>
+      <c r="P335" t="inlineStr">
+        <is>
+          <t>-38.57495889656735,174.63003321184613</t>
+        </is>
+      </c>
+      <c r="Q335" t="inlineStr">
+        <is>
+          <t>-38.57426313153577,174.63016196096748</t>
+        </is>
+      </c>
+      <c r="R335" t="inlineStr">
+        <is>
+          <t>-38.573573185480335,174.6303292286561</t>
+        </is>
+      </c>
+      <c r="S335" t="inlineStr">
+        <is>
+          <t>-38.572852813809526,174.63001377577427</t>
+        </is>
+      </c>
+      <c r="T335" t="inlineStr">
+        <is>
+          <t>-38.57215110395352,174.63005113021336</t>
+        </is>
+      </c>
+      <c r="U335" t="inlineStr">
+        <is>
+          <t>-38.571457782779056,174.63033906027027</t>
+        </is>
+      </c>
+      <c r="V335" t="inlineStr">
+        <is>
+          <t>-38.5707536115921,174.63037035216112</t>
+        </is>
+      </c>
+      <c r="W335" t="inlineStr">
+        <is>
+          <t>-38.570051942998376,174.630386835364</t>
+        </is>
+      </c>
+      <c r="X335" t="inlineStr">
+        <is>
+          <t>-38.56934929873792,174.63036226912922</t>
+        </is>
+      </c>
+      <c r="Y335" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
